--- a/backend/product_database/選機表-.xlsx
+++ b/backend/product_database/選機表-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417A2669-F67C-4EA0-996B-3416EC12E6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2792EBAD-A26E-4A1C-9D9F-234F7722D413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B12BA144-AC3D-4CE9-9615-9201C80CE143}"/>
   </bookViews>
@@ -3456,11 +3456,11 @@
     <numFmt numFmtId="184" formatCode="0.0"/>
     <numFmt numFmtId="185" formatCode="0.000"/>
     <numFmt numFmtId="186" formatCode="&quot;製表日期：&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="188" formatCode="&quot;FXDQ-&quot;General"/>
-    <numFmt numFmtId="189" formatCode="0.000_);[Red]\(0.000\)"/>
-    <numFmt numFmtId="190" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;HT0&quot;General"/>
-    <numFmt numFmtId="193" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="187" formatCode="&quot;FXDQ-&quot;General"/>
+    <numFmt numFmtId="188" formatCode="0.000_);[Red]\(0.000\)"/>
+    <numFmt numFmtId="189" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="190" formatCode="&quot;HT0&quot;General"/>
+    <numFmt numFmtId="191" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -3681,7 +3681,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3731,12 +3731,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3900,7 +3894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4085,15 +4079,6 @@
     <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4106,9 +4091,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4119,9 +4101,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4169,37 +4148,13 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="7" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="3" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="11" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="184" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4211,55 +4166,28 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="3" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="191" fontId="3" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="190" fontId="3" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="3" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="3" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="3" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4268,11 +4196,50 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="3" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="21" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="21" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4294,9 +4261,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4340,24 +4304,6 @@
     <xf numFmtId="178" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4370,14 +4316,41 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="191" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="193" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -19979,15 +19952,15 @@
       <c r="BF5" s="19"/>
     </row>
     <row r="6" spans="1:58" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="149" t="s">
+      <c r="A6" s="111" t="s">
         <v>736</v>
       </c>
-      <c r="B6" s="150"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="150"/>
-      <c r="G6" s="150"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
       <c r="H6" s="60"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -20041,4155 +20014,4155 @@
       <c r="BF6" s="10"/>
     </row>
     <row r="7" spans="1:58" ht="39.75" customHeight="1">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="113" t="s">
         <v>691</v>
       </c>
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="115" t="s">
         <v>692</v>
       </c>
-      <c r="C7" s="154" t="s">
+      <c r="C7" s="117" t="s">
         <v>693</v>
       </c>
-      <c r="D7" s="134" t="s">
+      <c r="D7" s="114" t="s">
         <v>694</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="105" t="s">
         <v>695</v>
       </c>
-      <c r="F7" s="65" t="s">
+      <c r="F7" s="106" t="s">
         <v>696</v>
       </c>
-      <c r="G7" s="65" t="s">
+      <c r="G7" s="106" t="s">
         <v>697</v>
       </c>
-      <c r="H7" s="147" t="s">
+      <c r="H7" s="137" t="s">
         <v>738</v>
       </c>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="148"/>
-      <c r="L7" s="140" t="s">
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="130" t="s">
         <v>698</v>
       </c>
-      <c r="M7" s="140"/>
-      <c r="N7" s="141" t="s">
+      <c r="M7" s="130"/>
+      <c r="N7" s="131" t="s">
         <v>699</v>
       </c>
-      <c r="O7" s="142"/>
-      <c r="P7" s="142"/>
-      <c r="Q7" s="142"/>
-      <c r="R7" s="142"/>
-      <c r="S7" s="142"/>
-      <c r="T7" s="142"/>
-      <c r="U7" s="142"/>
-      <c r="V7" s="143"/>
-      <c r="W7" s="144" t="s">
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="132"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="132"/>
+      <c r="U7" s="132"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="134" t="s">
         <v>700</v>
       </c>
-      <c r="X7" s="143"/>
-      <c r="Y7" s="145" t="s">
+      <c r="X7" s="133"/>
+      <c r="Y7" s="135" t="s">
         <v>701</v>
       </c>
-      <c r="Z7" s="66" t="s">
+      <c r="Z7" s="108" t="s">
         <v>702</v>
       </c>
-      <c r="AA7" s="144" t="s">
+      <c r="AA7" s="134" t="s">
         <v>703</v>
       </c>
-      <c r="AB7" s="142"/>
-      <c r="AC7" s="142"/>
-      <c r="AD7" s="143"/>
-      <c r="AE7" s="133" t="s">
+      <c r="AB7" s="132"/>
+      <c r="AC7" s="132"/>
+      <c r="AD7" s="133"/>
+      <c r="AE7" s="124" t="s">
         <v>704</v>
       </c>
-      <c r="AF7" s="133"/>
-      <c r="AG7" s="134"/>
-      <c r="AH7" s="134"/>
-      <c r="AI7" s="134"/>
-      <c r="AJ7" s="134"/>
-      <c r="AK7" s="134"/>
-      <c r="AL7" s="134"/>
-      <c r="AM7" s="134"/>
-      <c r="AN7" s="134"/>
-      <c r="AO7" s="134"/>
-      <c r="AP7" s="138" t="s">
+      <c r="AF7" s="124"/>
+      <c r="AG7" s="114"/>
+      <c r="AH7" s="114"/>
+      <c r="AI7" s="114"/>
+      <c r="AJ7" s="114"/>
+      <c r="AK7" s="114"/>
+      <c r="AL7" s="114"/>
+      <c r="AM7" s="114"/>
+      <c r="AN7" s="114"/>
+      <c r="AO7" s="114"/>
+      <c r="AP7" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="AQ7" s="127" t="s">
+      <c r="AQ7" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="AR7" s="128"/>
-      <c r="AS7" s="128"/>
-      <c r="AT7" s="128"/>
-      <c r="AU7" s="128"/>
-      <c r="AV7" s="128"/>
-      <c r="AW7" s="128"/>
-      <c r="AX7" s="128"/>
-      <c r="AY7" s="128"/>
-      <c r="AZ7" s="129"/>
-      <c r="BA7" s="130" t="s">
+      <c r="AR7" s="119"/>
+      <c r="AS7" s="119"/>
+      <c r="AT7" s="119"/>
+      <c r="AU7" s="119"/>
+      <c r="AV7" s="119"/>
+      <c r="AW7" s="119"/>
+      <c r="AX7" s="119"/>
+      <c r="AY7" s="119"/>
+      <c r="AZ7" s="120"/>
+      <c r="BA7" s="121" t="s">
         <v>705</v>
       </c>
-      <c r="BB7" s="131"/>
-      <c r="BC7" s="131"/>
-      <c r="BD7" s="132"/>
-      <c r="BE7" s="130" t="s">
+      <c r="BB7" s="122"/>
+      <c r="BC7" s="122"/>
+      <c r="BD7" s="123"/>
+      <c r="BE7" s="121" t="s">
         <v>706</v>
       </c>
-      <c r="BF7" s="132"/>
+      <c r="BF7" s="123"/>
     </row>
     <row r="8" spans="1:58" ht="51.75" customHeight="1">
-      <c r="A8" s="134"/>
-      <c r="B8" s="153"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="134"/>
-      <c r="E8" s="64" t="s">
+      <c r="A8" s="114"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="114"/>
+      <c r="E8" s="105" t="s">
         <v>707</v>
       </c>
-      <c r="F8" s="65" t="s">
+      <c r="F8" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="68" t="s">
+      <c r="H8" s="65" t="s">
         <v>737</v>
       </c>
-      <c r="I8" s="68" t="s">
+      <c r="I8" s="65" t="s">
         <v>719</v>
       </c>
-      <c r="J8" s="68" t="s">
+      <c r="J8" s="65" t="s">
         <v>709</v>
       </c>
-      <c r="K8" s="68" t="s">
+      <c r="K8" s="65" t="s">
         <v>710</v>
       </c>
-      <c r="L8" s="68" t="s">
+      <c r="L8" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="70" t="s">
+      <c r="N8" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="70" t="s">
+      <c r="O8" s="67" t="s">
         <v>711</v>
       </c>
-      <c r="P8" s="69" t="s">
+      <c r="P8" s="66" t="s">
         <v>712</v>
       </c>
-      <c r="Q8" s="69" t="s">
+      <c r="Q8" s="66" t="s">
         <v>713</v>
       </c>
-      <c r="R8" s="70" t="s">
+      <c r="R8" s="67" t="s">
         <v>714</v>
       </c>
-      <c r="S8" s="69" t="s">
+      <c r="S8" s="66" t="s">
         <v>715</v>
       </c>
-      <c r="T8" s="69" t="s">
+      <c r="T8" s="66" t="s">
         <v>716</v>
       </c>
-      <c r="U8" s="71" t="s">
+      <c r="U8" s="107" t="s">
         <v>717</v>
       </c>
-      <c r="V8" s="72" t="s">
+      <c r="V8" s="68" t="s">
         <v>718</v>
       </c>
-      <c r="W8" s="69" t="s">
+      <c r="W8" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="69" t="s">
+      <c r="X8" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="Y8" s="146"/>
-      <c r="Z8" s="73" t="s">
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="AA8" s="74" t="s">
+      <c r="AA8" s="70" t="s">
         <v>719</v>
       </c>
-      <c r="AB8" s="74" t="s">
+      <c r="AB8" s="70" t="s">
         <v>708</v>
       </c>
-      <c r="AC8" s="64" t="s">
+      <c r="AC8" s="105" t="s">
         <v>710</v>
       </c>
-      <c r="AD8" s="64" t="s">
+      <c r="AD8" s="105" t="s">
         <v>720</v>
       </c>
-      <c r="AE8" s="75" t="s">
+      <c r="AE8" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="AF8" s="75" t="s">
+      <c r="AF8" s="71" t="s">
         <v>721</v>
       </c>
-      <c r="AG8" s="76" t="s">
+      <c r="AG8" s="104" t="s">
         <v>712</v>
       </c>
-      <c r="AH8" s="76" t="s">
+      <c r="AH8" s="104" t="s">
         <v>713</v>
       </c>
-      <c r="AI8" s="66" t="s">
+      <c r="AI8" s="108" t="s">
         <v>722</v>
       </c>
-      <c r="AJ8" s="77" t="s">
+      <c r="AJ8" s="72" t="s">
         <v>723</v>
       </c>
-      <c r="AK8" s="76" t="s">
+      <c r="AK8" s="104" t="s">
         <v>724</v>
       </c>
-      <c r="AL8" s="78" t="s">
+      <c r="AL8" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="AM8" s="71" t="s">
+      <c r="AM8" s="107" t="s">
         <v>725</v>
       </c>
-      <c r="AN8" s="72" t="s">
+      <c r="AN8" s="68" t="s">
         <v>726</v>
       </c>
-      <c r="AO8" s="76" t="s">
+      <c r="AO8" s="104" t="s">
         <v>718</v>
       </c>
-      <c r="AP8" s="139"/>
-      <c r="AQ8" s="79" t="s">
+      <c r="AP8" s="129"/>
+      <c r="AQ8" s="74" t="s">
         <v>727</v>
       </c>
-      <c r="AR8" s="79" t="s">
+      <c r="AR8" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="AS8" s="79" t="s">
+      <c r="AS8" s="74" t="s">
         <v>728</v>
       </c>
-      <c r="AT8" s="80" t="s">
+      <c r="AT8" s="75" t="s">
         <v>729</v>
       </c>
-      <c r="AU8" s="80" t="s">
+      <c r="AU8" s="75" t="s">
         <v>730</v>
       </c>
-      <c r="AV8" s="81" t="s">
+      <c r="AV8" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="AW8" s="82" t="s">
+      <c r="AW8" s="77" t="s">
         <v>731</v>
       </c>
-      <c r="AX8" s="80" t="s">
+      <c r="AX8" s="75" t="s">
         <v>716</v>
       </c>
-      <c r="AY8" s="83" t="s">
+      <c r="AY8" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="AZ8" s="84" t="s">
+      <c r="AZ8" s="79" t="s">
         <v>718</v>
       </c>
-      <c r="BA8" s="85" t="s">
+      <c r="BA8" s="80" t="s">
         <v>732</v>
       </c>
-      <c r="BB8" s="86" t="s">
+      <c r="BB8" s="81" t="s">
         <v>733</v>
       </c>
-      <c r="BC8" s="87" t="s">
+      <c r="BC8" s="82" t="s">
         <v>716</v>
       </c>
-      <c r="BD8" s="85" t="s">
+      <c r="BD8" s="80" t="s">
         <v>715</v>
       </c>
-      <c r="BE8" s="85" t="s">
+      <c r="BE8" s="80" t="s">
         <v>732</v>
       </c>
-      <c r="BF8" s="86" t="s">
+      <c r="BF8" s="81" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="9" spans="1:58" ht="30" customHeight="1">
-      <c r="A9" s="88"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="95">
+      <c r="A9" s="83"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="146">
         <f>H9*0.3025</f>
         <v>0</v>
       </c>
-      <c r="J9" s="161">
+      <c r="J9" s="147">
         <f>H9/0.86*0.3025</f>
         <v>0</v>
       </c>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="97"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="100"/>
-      <c r="S9" s="101"/>
-      <c r="T9" s="102"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="98"/>
-      <c r="X9" s="88"/>
+      <c r="K9" s="145"/>
+      <c r="L9" s="145"/>
+      <c r="M9" s="145"/>
+      <c r="N9" s="148"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="100"/>
+      <c r="R9" s="87"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="89"/>
+      <c r="U9" s="100"/>
+      <c r="V9" s="100"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="83"/>
       <c r="Y9" s="53">
         <f>R9*O9</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="160">
+      <c r="Z9" s="110">
         <f>O9*T9</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="159">
+      <c r="AA9" s="109">
         <f>AB9*0.3025</f>
         <v>0</v>
       </c>
-      <c r="AB9" s="104"/>
-      <c r="AC9" s="103"/>
-      <c r="AD9" s="105"/>
-      <c r="AE9" s="106"/>
-      <c r="AF9" s="107"/>
-      <c r="AG9" s="108">
+      <c r="AB9" s="91"/>
+      <c r="AC9" s="90"/>
+      <c r="AD9" s="92"/>
+      <c r="AE9" s="150"/>
+      <c r="AF9" s="151"/>
+      <c r="AG9" s="101">
         <f>AH9*860</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="109"/>
-      <c r="AI9" s="101"/>
-      <c r="AJ9" s="110"/>
-      <c r="AK9" s="111"/>
-      <c r="AL9" s="111"/>
-      <c r="AM9" s="99"/>
-      <c r="AN9" s="99"/>
-      <c r="AO9" s="99"/>
-      <c r="AP9" s="88"/>
-      <c r="AQ9" s="112"/>
-      <c r="AR9" s="113"/>
-      <c r="AS9" s="88"/>
-      <c r="AT9" s="88"/>
-      <c r="AU9" s="113"/>
-      <c r="AV9" s="112"/>
-      <c r="AW9" s="113"/>
-      <c r="AX9" s="102"/>
-      <c r="AY9" s="102"/>
-      <c r="AZ9" s="102"/>
-      <c r="BA9" s="114"/>
-      <c r="BB9" s="113"/>
-      <c r="BC9" s="102"/>
-      <c r="BD9" s="102"/>
-      <c r="BE9" s="113"/>
-      <c r="BF9" s="113"/>
+      <c r="AH9" s="102"/>
+      <c r="AI9" s="88"/>
+      <c r="AJ9" s="152"/>
+      <c r="AK9" s="93"/>
+      <c r="AL9" s="93"/>
+      <c r="AM9" s="100"/>
+      <c r="AN9" s="100"/>
+      <c r="AO9" s="100"/>
+      <c r="AP9" s="83"/>
+      <c r="AQ9" s="94"/>
+      <c r="AR9" s="95"/>
+      <c r="AS9" s="83"/>
+      <c r="AT9" s="83"/>
+      <c r="AU9" s="95"/>
+      <c r="AV9" s="94"/>
+      <c r="AW9" s="95"/>
+      <c r="AX9" s="89"/>
+      <c r="AY9" s="89"/>
+      <c r="AZ9" s="89"/>
+      <c r="BA9" s="96"/>
+      <c r="BB9" s="95"/>
+      <c r="BC9" s="89"/>
+      <c r="BD9" s="89"/>
+      <c r="BE9" s="95"/>
+      <c r="BF9" s="95"/>
     </row>
     <row r="10" spans="1:58" ht="30" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="95">
+      <c r="A10" s="83"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="146">
         <f t="shared" ref="I10:I57" si="0">H10*0.3025</f>
         <v>0</v>
       </c>
-      <c r="J10" s="161">
+      <c r="J10" s="147">
         <f t="shared" ref="J10:J57" si="1">H10/0.86*0.3025</f>
         <v>0</v>
       </c>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="120"/>
-      <c r="Q10" s="121"/>
-      <c r="R10" s="100"/>
-      <c r="S10" s="101"/>
-      <c r="T10" s="102"/>
-      <c r="U10" s="121"/>
-      <c r="V10" s="121"/>
-      <c r="W10" s="120"/>
-      <c r="X10" s="88"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="145"/>
+      <c r="M10" s="145"/>
+      <c r="N10" s="148"/>
+      <c r="O10" s="88"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="87"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="100"/>
+      <c r="V10" s="100"/>
+      <c r="W10" s="99"/>
+      <c r="X10" s="83"/>
       <c r="Y10" s="53">
         <f t="shared" ref="Y10:Y57" si="2">R10*O10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="160">
+      <c r="Z10" s="110">
         <f t="shared" ref="Z10:Z57" si="3">O10*T10</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="159">
+      <c r="AA10" s="109">
         <f t="shared" ref="AA10:AA57" si="4">AB10*0.3025</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="104"/>
-      <c r="AC10" s="103"/>
-      <c r="AD10" s="105"/>
-      <c r="AE10" s="122"/>
-      <c r="AF10" s="107"/>
-      <c r="AG10" s="123">
+      <c r="AB10" s="91"/>
+      <c r="AC10" s="90"/>
+      <c r="AD10" s="92"/>
+      <c r="AE10" s="150"/>
+      <c r="AF10" s="151"/>
+      <c r="AG10" s="101">
         <f t="shared" ref="AG10:AG57" si="5">AH10*860</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="124"/>
-      <c r="AI10" s="101"/>
-      <c r="AJ10" s="110"/>
-      <c r="AK10" s="111"/>
-      <c r="AL10" s="111"/>
-      <c r="AM10" s="121"/>
-      <c r="AN10" s="121"/>
-      <c r="AO10" s="121"/>
-      <c r="AP10" s="88"/>
-      <c r="AQ10" s="112"/>
-      <c r="AR10" s="113"/>
-      <c r="AS10" s="88"/>
-      <c r="AT10" s="88"/>
-      <c r="AU10" s="113"/>
-      <c r="AV10" s="112"/>
-      <c r="AW10" s="113"/>
-      <c r="AX10" s="102"/>
-      <c r="AY10" s="102"/>
-      <c r="AZ10" s="102"/>
-      <c r="BA10" s="114"/>
-      <c r="BB10" s="113"/>
-      <c r="BC10" s="102"/>
-      <c r="BD10" s="102"/>
-      <c r="BE10" s="113"/>
-      <c r="BF10" s="113"/>
+      <c r="AH10" s="102"/>
+      <c r="AI10" s="88"/>
+      <c r="AJ10" s="152"/>
+      <c r="AK10" s="93"/>
+      <c r="AL10" s="93"/>
+      <c r="AM10" s="100"/>
+      <c r="AN10" s="100"/>
+      <c r="AO10" s="100"/>
+      <c r="AP10" s="83"/>
+      <c r="AQ10" s="94"/>
+      <c r="AR10" s="95"/>
+      <c r="AS10" s="83"/>
+      <c r="AT10" s="83"/>
+      <c r="AU10" s="95"/>
+      <c r="AV10" s="94"/>
+      <c r="AW10" s="95"/>
+      <c r="AX10" s="89"/>
+      <c r="AY10" s="89"/>
+      <c r="AZ10" s="89"/>
+      <c r="BA10" s="96"/>
+      <c r="BB10" s="95"/>
+      <c r="BC10" s="89"/>
+      <c r="BD10" s="89"/>
+      <c r="BE10" s="95"/>
+      <c r="BF10" s="95"/>
     </row>
     <row r="11" spans="1:58" ht="30" customHeight="1">
-      <c r="A11" s="88"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="95">
+      <c r="A11" s="83"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="161">
+      <c r="J11" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="119"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="120"/>
-      <c r="Q11" s="121"/>
-      <c r="R11" s="100"/>
-      <c r="S11" s="101"/>
-      <c r="T11" s="102"/>
-      <c r="U11" s="121"/>
-      <c r="V11" s="121"/>
-      <c r="W11" s="120"/>
-      <c r="X11" s="88"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="148"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="87"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="89"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="100"/>
+      <c r="W11" s="99"/>
+      <c r="X11" s="83"/>
       <c r="Y11" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="160">
+      <c r="Z11" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="159">
+      <c r="AA11" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB11" s="104"/>
-      <c r="AC11" s="103"/>
-      <c r="AD11" s="105"/>
-      <c r="AE11" s="122"/>
-      <c r="AF11" s="107"/>
-      <c r="AG11" s="123">
+      <c r="AB11" s="91"/>
+      <c r="AC11" s="90"/>
+      <c r="AD11" s="92"/>
+      <c r="AE11" s="150"/>
+      <c r="AF11" s="151"/>
+      <c r="AG11" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="124"/>
-      <c r="AI11" s="101"/>
-      <c r="AJ11" s="110"/>
-      <c r="AK11" s="111"/>
-      <c r="AL11" s="111"/>
-      <c r="AM11" s="121"/>
-      <c r="AN11" s="121"/>
-      <c r="AO11" s="121"/>
-      <c r="AP11" s="88"/>
-      <c r="AQ11" s="112"/>
-      <c r="AR11" s="113"/>
-      <c r="AS11" s="88"/>
-      <c r="AT11" s="88"/>
-      <c r="AU11" s="113"/>
-      <c r="AV11" s="112"/>
-      <c r="AW11" s="113"/>
-      <c r="AX11" s="102"/>
-      <c r="AY11" s="102"/>
-      <c r="AZ11" s="102"/>
-      <c r="BA11" s="114"/>
-      <c r="BB11" s="113"/>
-      <c r="BC11" s="102"/>
-      <c r="BD11" s="102"/>
-      <c r="BE11" s="113"/>
-      <c r="BF11" s="113"/>
+      <c r="AH11" s="102"/>
+      <c r="AI11" s="88"/>
+      <c r="AJ11" s="152"/>
+      <c r="AK11" s="93"/>
+      <c r="AL11" s="93"/>
+      <c r="AM11" s="100"/>
+      <c r="AN11" s="100"/>
+      <c r="AO11" s="100"/>
+      <c r="AP11" s="83"/>
+      <c r="AQ11" s="94"/>
+      <c r="AR11" s="95"/>
+      <c r="AS11" s="83"/>
+      <c r="AT11" s="83"/>
+      <c r="AU11" s="95"/>
+      <c r="AV11" s="94"/>
+      <c r="AW11" s="95"/>
+      <c r="AX11" s="89"/>
+      <c r="AY11" s="89"/>
+      <c r="AZ11" s="89"/>
+      <c r="BA11" s="96"/>
+      <c r="BB11" s="95"/>
+      <c r="BC11" s="89"/>
+      <c r="BD11" s="89"/>
+      <c r="BE11" s="95"/>
+      <c r="BF11" s="95"/>
     </row>
     <row r="12" spans="1:58" ht="30" customHeight="1">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="95">
+      <c r="A12" s="83"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="161">
+      <c r="J12" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="119"/>
-      <c r="O12" s="97"/>
-      <c r="P12" s="120"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="100"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="102"/>
-      <c r="U12" s="121"/>
-      <c r="V12" s="121"/>
-      <c r="W12" s="120"/>
-      <c r="X12" s="88"/>
+      <c r="K12" s="145"/>
+      <c r="L12" s="145"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="148"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="99"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="100"/>
+      <c r="V12" s="100"/>
+      <c r="W12" s="99"/>
+      <c r="X12" s="83"/>
       <c r="Y12" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="160">
+      <c r="Z12" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="159">
+      <c r="AA12" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="104"/>
-      <c r="AC12" s="103"/>
-      <c r="AD12" s="105"/>
-      <c r="AE12" s="122"/>
-      <c r="AF12" s="107"/>
-      <c r="AG12" s="123">
+      <c r="AB12" s="91"/>
+      <c r="AC12" s="90"/>
+      <c r="AD12" s="92"/>
+      <c r="AE12" s="150"/>
+      <c r="AF12" s="151"/>
+      <c r="AG12" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="124"/>
-      <c r="AI12" s="101"/>
-      <c r="AJ12" s="110"/>
-      <c r="AK12" s="111"/>
-      <c r="AL12" s="111"/>
-      <c r="AM12" s="121"/>
-      <c r="AN12" s="121"/>
-      <c r="AO12" s="121"/>
-      <c r="AP12" s="88"/>
-      <c r="AQ12" s="112"/>
-      <c r="AR12" s="113"/>
-      <c r="AS12" s="88"/>
-      <c r="AT12" s="88"/>
-      <c r="AU12" s="113"/>
-      <c r="AV12" s="112"/>
-      <c r="AW12" s="113"/>
-      <c r="AX12" s="102"/>
-      <c r="AY12" s="102"/>
-      <c r="AZ12" s="102"/>
-      <c r="BA12" s="114"/>
-      <c r="BB12" s="113"/>
-      <c r="BC12" s="102"/>
-      <c r="BD12" s="102"/>
-      <c r="BE12" s="113"/>
-      <c r="BF12" s="113"/>
+      <c r="AH12" s="102"/>
+      <c r="AI12" s="88"/>
+      <c r="AJ12" s="152"/>
+      <c r="AK12" s="93"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="100"/>
+      <c r="AN12" s="100"/>
+      <c r="AO12" s="100"/>
+      <c r="AP12" s="83"/>
+      <c r="AQ12" s="94"/>
+      <c r="AR12" s="95"/>
+      <c r="AS12" s="83"/>
+      <c r="AT12" s="83"/>
+      <c r="AU12" s="95"/>
+      <c r="AV12" s="94"/>
+      <c r="AW12" s="95"/>
+      <c r="AX12" s="89"/>
+      <c r="AY12" s="89"/>
+      <c r="AZ12" s="89"/>
+      <c r="BA12" s="96"/>
+      <c r="BB12" s="95"/>
+      <c r="BC12" s="89"/>
+      <c r="BD12" s="89"/>
+      <c r="BE12" s="95"/>
+      <c r="BF12" s="95"/>
     </row>
     <row r="13" spans="1:58" ht="30" customHeight="1">
-      <c r="A13" s="88"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="92"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="95">
+      <c r="A13" s="83"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="161">
+      <c r="J13" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="119"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="120"/>
-      <c r="Q13" s="121"/>
-      <c r="R13" s="100"/>
-      <c r="S13" s="101"/>
-      <c r="T13" s="102"/>
-      <c r="U13" s="121"/>
-      <c r="V13" s="121"/>
-      <c r="W13" s="120"/>
-      <c r="X13" s="88"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+      <c r="M13" s="145"/>
+      <c r="N13" s="148"/>
+      <c r="O13" s="88"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="100"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="89"/>
+      <c r="U13" s="100"/>
+      <c r="V13" s="100"/>
+      <c r="W13" s="99"/>
+      <c r="X13" s="83"/>
       <c r="Y13" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="160">
+      <c r="Z13" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="159">
+      <c r="AA13" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB13" s="104"/>
-      <c r="AC13" s="103"/>
-      <c r="AD13" s="105"/>
-      <c r="AE13" s="122"/>
-      <c r="AF13" s="107"/>
-      <c r="AG13" s="123">
+      <c r="AB13" s="91"/>
+      <c r="AC13" s="90"/>
+      <c r="AD13" s="92"/>
+      <c r="AE13" s="150"/>
+      <c r="AF13" s="151"/>
+      <c r="AG13" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH13" s="124"/>
-      <c r="AI13" s="101"/>
-      <c r="AJ13" s="110"/>
-      <c r="AK13" s="111"/>
-      <c r="AL13" s="111"/>
-      <c r="AM13" s="121"/>
-      <c r="AN13" s="121"/>
-      <c r="AO13" s="121"/>
-      <c r="AP13" s="88"/>
-      <c r="AQ13" s="112"/>
-      <c r="AR13" s="113"/>
-      <c r="AS13" s="88"/>
-      <c r="AT13" s="88"/>
-      <c r="AU13" s="113"/>
-      <c r="AV13" s="112"/>
-      <c r="AW13" s="113"/>
-      <c r="AX13" s="102"/>
-      <c r="AY13" s="102"/>
-      <c r="AZ13" s="102"/>
-      <c r="BA13" s="114"/>
-      <c r="BB13" s="113"/>
-      <c r="BC13" s="102"/>
-      <c r="BD13" s="102"/>
-      <c r="BE13" s="113"/>
-      <c r="BF13" s="113"/>
+      <c r="AH13" s="102"/>
+      <c r="AI13" s="88"/>
+      <c r="AJ13" s="152"/>
+      <c r="AK13" s="93"/>
+      <c r="AL13" s="93"/>
+      <c r="AM13" s="100"/>
+      <c r="AN13" s="100"/>
+      <c r="AO13" s="100"/>
+      <c r="AP13" s="83"/>
+      <c r="AQ13" s="94"/>
+      <c r="AR13" s="95"/>
+      <c r="AS13" s="83"/>
+      <c r="AT13" s="83"/>
+      <c r="AU13" s="95"/>
+      <c r="AV13" s="94"/>
+      <c r="AW13" s="95"/>
+      <c r="AX13" s="89"/>
+      <c r="AY13" s="89"/>
+      <c r="AZ13" s="89"/>
+      <c r="BA13" s="96"/>
+      <c r="BB13" s="95"/>
+      <c r="BC13" s="89"/>
+      <c r="BD13" s="89"/>
+      <c r="BE13" s="95"/>
+      <c r="BF13" s="95"/>
     </row>
     <row r="14" spans="1:58" ht="30" customHeight="1">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="95">
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="145"/>
+      <c r="I14" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="119"/>
-      <c r="O14" s="97"/>
-      <c r="P14" s="120"/>
-      <c r="Q14" s="121"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="101"/>
-      <c r="T14" s="102"/>
-      <c r="U14" s="121"/>
-      <c r="V14" s="121"/>
-      <c r="W14" s="120"/>
-      <c r="X14" s="88"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="145"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="89"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="99"/>
+      <c r="X14" s="83"/>
       <c r="Y14" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="160">
+      <c r="Z14" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="159">
+      <c r="AA14" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="104"/>
-      <c r="AC14" s="103"/>
-      <c r="AD14" s="105"/>
-      <c r="AE14" s="122"/>
-      <c r="AF14" s="107"/>
-      <c r="AG14" s="123">
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="90"/>
+      <c r="AD14" s="92"/>
+      <c r="AE14" s="150"/>
+      <c r="AF14" s="151"/>
+      <c r="AG14" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="124"/>
-      <c r="AI14" s="101"/>
-      <c r="AJ14" s="110"/>
-      <c r="AK14" s="111"/>
-      <c r="AL14" s="111"/>
-      <c r="AM14" s="121"/>
-      <c r="AN14" s="121"/>
-      <c r="AO14" s="121"/>
-      <c r="AP14" s="88"/>
-      <c r="AQ14" s="112"/>
-      <c r="AR14" s="113"/>
-      <c r="AS14" s="88"/>
-      <c r="AT14" s="88"/>
-      <c r="AU14" s="113"/>
-      <c r="AV14" s="112"/>
-      <c r="AW14" s="113"/>
-      <c r="AX14" s="102"/>
-      <c r="AY14" s="102"/>
-      <c r="AZ14" s="102"/>
-      <c r="BA14" s="114"/>
-      <c r="BB14" s="113"/>
-      <c r="BC14" s="102"/>
-      <c r="BD14" s="102"/>
-      <c r="BE14" s="113"/>
-      <c r="BF14" s="113"/>
+      <c r="AH14" s="102"/>
+      <c r="AI14" s="88"/>
+      <c r="AJ14" s="152"/>
+      <c r="AK14" s="93"/>
+      <c r="AL14" s="93"/>
+      <c r="AM14" s="100"/>
+      <c r="AN14" s="100"/>
+      <c r="AO14" s="100"/>
+      <c r="AP14" s="83"/>
+      <c r="AQ14" s="94"/>
+      <c r="AR14" s="95"/>
+      <c r="AS14" s="83"/>
+      <c r="AT14" s="83"/>
+      <c r="AU14" s="95"/>
+      <c r="AV14" s="94"/>
+      <c r="AW14" s="95"/>
+      <c r="AX14" s="89"/>
+      <c r="AY14" s="89"/>
+      <c r="AZ14" s="89"/>
+      <c r="BA14" s="96"/>
+      <c r="BB14" s="95"/>
+      <c r="BC14" s="89"/>
+      <c r="BD14" s="89"/>
+      <c r="BE14" s="95"/>
+      <c r="BF14" s="95"/>
     </row>
     <row r="15" spans="1:58" ht="30" customHeight="1">
-      <c r="A15" s="88"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="95">
+      <c r="A15" s="83"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="161">
+      <c r="J15" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="94"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="119"/>
-      <c r="O15" s="97"/>
-      <c r="P15" s="120"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="100"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="102"/>
-      <c r="U15" s="121"/>
-      <c r="V15" s="121"/>
-      <c r="W15" s="120"/>
-      <c r="X15" s="88"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="145"/>
+      <c r="M15" s="145"/>
+      <c r="N15" s="148"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="100"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="89"/>
+      <c r="U15" s="100"/>
+      <c r="V15" s="100"/>
+      <c r="W15" s="99"/>
+      <c r="X15" s="83"/>
       <c r="Y15" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="160">
+      <c r="Z15" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="159">
+      <c r="AA15" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="104"/>
-      <c r="AC15" s="103"/>
-      <c r="AD15" s="105"/>
-      <c r="AE15" s="122"/>
-      <c r="AF15" s="107"/>
-      <c r="AG15" s="123">
+      <c r="AB15" s="91"/>
+      <c r="AC15" s="90"/>
+      <c r="AD15" s="92"/>
+      <c r="AE15" s="150"/>
+      <c r="AF15" s="151"/>
+      <c r="AG15" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="124"/>
-      <c r="AI15" s="101"/>
-      <c r="AJ15" s="110"/>
-      <c r="AK15" s="111"/>
-      <c r="AL15" s="111"/>
-      <c r="AM15" s="121"/>
-      <c r="AN15" s="121"/>
-      <c r="AO15" s="121"/>
-      <c r="AP15" s="88"/>
-      <c r="AQ15" s="112"/>
-      <c r="AR15" s="113"/>
-      <c r="AS15" s="88"/>
-      <c r="AT15" s="88"/>
-      <c r="AU15" s="113"/>
-      <c r="AV15" s="112"/>
-      <c r="AW15" s="113"/>
-      <c r="AX15" s="102"/>
-      <c r="AY15" s="102"/>
-      <c r="AZ15" s="102"/>
-      <c r="BA15" s="114"/>
-      <c r="BB15" s="113"/>
-      <c r="BC15" s="102"/>
-      <c r="BD15" s="102"/>
-      <c r="BE15" s="113"/>
-      <c r="BF15" s="113"/>
+      <c r="AH15" s="102"/>
+      <c r="AI15" s="88"/>
+      <c r="AJ15" s="152"/>
+      <c r="AK15" s="93"/>
+      <c r="AL15" s="93"/>
+      <c r="AM15" s="100"/>
+      <c r="AN15" s="100"/>
+      <c r="AO15" s="100"/>
+      <c r="AP15" s="83"/>
+      <c r="AQ15" s="94"/>
+      <c r="AR15" s="95"/>
+      <c r="AS15" s="83"/>
+      <c r="AT15" s="83"/>
+      <c r="AU15" s="95"/>
+      <c r="AV15" s="94"/>
+      <c r="AW15" s="95"/>
+      <c r="AX15" s="89"/>
+      <c r="AY15" s="89"/>
+      <c r="AZ15" s="89"/>
+      <c r="BA15" s="96"/>
+      <c r="BB15" s="95"/>
+      <c r="BC15" s="89"/>
+      <c r="BD15" s="89"/>
+      <c r="BE15" s="95"/>
+      <c r="BF15" s="95"/>
     </row>
     <row r="16" spans="1:58" ht="30" customHeight="1">
-      <c r="A16" s="88"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="95">
+      <c r="A16" s="83"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="161">
+      <c r="J16" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="94"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="97"/>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="121"/>
-      <c r="R16" s="100"/>
-      <c r="S16" s="101"/>
-      <c r="T16" s="102"/>
-      <c r="U16" s="121"/>
-      <c r="V16" s="121"/>
-      <c r="W16" s="120"/>
-      <c r="X16" s="88"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="145"/>
+      <c r="N16" s="148"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="100"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="89"/>
+      <c r="U16" s="100"/>
+      <c r="V16" s="100"/>
+      <c r="W16" s="99"/>
+      <c r="X16" s="83"/>
       <c r="Y16" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="160">
+      <c r="Z16" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="159">
+      <c r="AA16" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="104"/>
-      <c r="AC16" s="103"/>
-      <c r="AD16" s="105"/>
-      <c r="AE16" s="122"/>
-      <c r="AF16" s="107"/>
-      <c r="AG16" s="123">
+      <c r="AB16" s="91"/>
+      <c r="AC16" s="90"/>
+      <c r="AD16" s="92"/>
+      <c r="AE16" s="150"/>
+      <c r="AF16" s="151"/>
+      <c r="AG16" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="101"/>
-      <c r="AJ16" s="110"/>
-      <c r="AK16" s="111"/>
-      <c r="AL16" s="111"/>
-      <c r="AM16" s="121"/>
-      <c r="AN16" s="121"/>
-      <c r="AO16" s="121"/>
-      <c r="AP16" s="88"/>
-      <c r="AQ16" s="112"/>
-      <c r="AR16" s="113"/>
-      <c r="AS16" s="88"/>
-      <c r="AT16" s="88"/>
-      <c r="AU16" s="113"/>
-      <c r="AV16" s="112"/>
-      <c r="AW16" s="113"/>
-      <c r="AX16" s="102"/>
-      <c r="AY16" s="102"/>
-      <c r="AZ16" s="102"/>
-      <c r="BA16" s="114"/>
-      <c r="BB16" s="113"/>
-      <c r="BC16" s="102"/>
-      <c r="BD16" s="102"/>
-      <c r="BE16" s="113"/>
-      <c r="BF16" s="113"/>
+      <c r="AH16" s="102"/>
+      <c r="AI16" s="88"/>
+      <c r="AJ16" s="152"/>
+      <c r="AK16" s="93"/>
+      <c r="AL16" s="93"/>
+      <c r="AM16" s="100"/>
+      <c r="AN16" s="100"/>
+      <c r="AO16" s="100"/>
+      <c r="AP16" s="83"/>
+      <c r="AQ16" s="94"/>
+      <c r="AR16" s="95"/>
+      <c r="AS16" s="83"/>
+      <c r="AT16" s="83"/>
+      <c r="AU16" s="95"/>
+      <c r="AV16" s="94"/>
+      <c r="AW16" s="95"/>
+      <c r="AX16" s="89"/>
+      <c r="AY16" s="89"/>
+      <c r="AZ16" s="89"/>
+      <c r="BA16" s="96"/>
+      <c r="BB16" s="95"/>
+      <c r="BC16" s="89"/>
+      <c r="BD16" s="89"/>
+      <c r="BE16" s="95"/>
+      <c r="BF16" s="95"/>
     </row>
     <row r="17" spans="1:58" ht="30" customHeight="1">
-      <c r="A17" s="88"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="95">
+      <c r="A17" s="83"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="161">
+      <c r="J17" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="119"/>
-      <c r="O17" s="97"/>
-      <c r="P17" s="120"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="100"/>
-      <c r="S17" s="101"/>
-      <c r="T17" s="102"/>
-      <c r="U17" s="121"/>
-      <c r="V17" s="121"/>
-      <c r="W17" s="120"/>
-      <c r="X17" s="88"/>
+      <c r="K17" s="145"/>
+      <c r="L17" s="145"/>
+      <c r="M17" s="145"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="88"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="100"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="83"/>
       <c r="Y17" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="160">
+      <c r="Z17" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="159">
+      <c r="AA17" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="104"/>
-      <c r="AC17" s="103"/>
-      <c r="AD17" s="105"/>
-      <c r="AE17" s="122"/>
-      <c r="AF17" s="107"/>
-      <c r="AG17" s="123">
+      <c r="AB17" s="91"/>
+      <c r="AC17" s="90"/>
+      <c r="AD17" s="92"/>
+      <c r="AE17" s="150"/>
+      <c r="AF17" s="151"/>
+      <c r="AG17" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="101"/>
-      <c r="AJ17" s="110"/>
-      <c r="AK17" s="111"/>
-      <c r="AL17" s="111"/>
-      <c r="AM17" s="121"/>
-      <c r="AN17" s="121"/>
-      <c r="AO17" s="121"/>
-      <c r="AP17" s="88"/>
-      <c r="AQ17" s="112"/>
-      <c r="AR17" s="113"/>
-      <c r="AS17" s="88"/>
-      <c r="AT17" s="88"/>
-      <c r="AU17" s="113"/>
-      <c r="AV17" s="112"/>
-      <c r="AW17" s="113"/>
-      <c r="AX17" s="102"/>
-      <c r="AY17" s="102"/>
-      <c r="AZ17" s="102"/>
-      <c r="BA17" s="114"/>
-      <c r="BB17" s="113"/>
-      <c r="BC17" s="102"/>
-      <c r="BD17" s="102"/>
-      <c r="BE17" s="113"/>
-      <c r="BF17" s="113"/>
+      <c r="AH17" s="102"/>
+      <c r="AI17" s="88"/>
+      <c r="AJ17" s="152"/>
+      <c r="AK17" s="93"/>
+      <c r="AL17" s="93"/>
+      <c r="AM17" s="100"/>
+      <c r="AN17" s="100"/>
+      <c r="AO17" s="100"/>
+      <c r="AP17" s="83"/>
+      <c r="AQ17" s="94"/>
+      <c r="AR17" s="95"/>
+      <c r="AS17" s="83"/>
+      <c r="AT17" s="83"/>
+      <c r="AU17" s="95"/>
+      <c r="AV17" s="94"/>
+      <c r="AW17" s="95"/>
+      <c r="AX17" s="89"/>
+      <c r="AY17" s="89"/>
+      <c r="AZ17" s="89"/>
+      <c r="BA17" s="96"/>
+      <c r="BB17" s="95"/>
+      <c r="BC17" s="89"/>
+      <c r="BD17" s="89"/>
+      <c r="BE17" s="95"/>
+      <c r="BF17" s="95"/>
     </row>
     <row r="18" spans="1:58" ht="30.75" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="95">
+      <c r="A18" s="83"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="161">
+      <c r="J18" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="119"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="101"/>
-      <c r="T18" s="102"/>
-      <c r="U18" s="121"/>
-      <c r="V18" s="121"/>
-      <c r="W18" s="120"/>
-      <c r="X18" s="88"/>
+      <c r="K18" s="149"/>
+      <c r="L18" s="149"/>
+      <c r="M18" s="149"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="99"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="99"/>
+      <c r="X18" s="83"/>
       <c r="Y18" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="160">
+      <c r="Z18" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="159">
+      <c r="AA18" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB18" s="104"/>
-      <c r="AC18" s="103"/>
-      <c r="AD18" s="105"/>
-      <c r="AE18" s="125"/>
-      <c r="AF18" s="117"/>
-      <c r="AG18" s="123">
+      <c r="AB18" s="91"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="92"/>
+      <c r="AE18" s="153"/>
+      <c r="AF18" s="154"/>
+      <c r="AG18" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="126"/>
-      <c r="AI18" s="101"/>
-      <c r="AJ18" s="110"/>
-      <c r="AK18" s="111"/>
-      <c r="AL18" s="111"/>
-      <c r="AM18" s="121"/>
-      <c r="AN18" s="121"/>
-      <c r="AO18" s="121"/>
-      <c r="AP18" s="88"/>
-      <c r="AQ18" s="112"/>
-      <c r="AR18" s="113"/>
-      <c r="AS18" s="88"/>
-      <c r="AT18" s="88"/>
-      <c r="AU18" s="113"/>
-      <c r="AV18" s="112"/>
-      <c r="AW18" s="113"/>
-      <c r="AX18" s="102"/>
-      <c r="AY18" s="102"/>
-      <c r="AZ18" s="102"/>
-      <c r="BA18" s="114"/>
-      <c r="BB18" s="113"/>
-      <c r="BC18" s="102"/>
-      <c r="BD18" s="102"/>
-      <c r="BE18" s="113"/>
-      <c r="BF18" s="113"/>
+      <c r="AH18" s="103"/>
+      <c r="AI18" s="88"/>
+      <c r="AJ18" s="152"/>
+      <c r="AK18" s="93"/>
+      <c r="AL18" s="93"/>
+      <c r="AM18" s="100"/>
+      <c r="AN18" s="100"/>
+      <c r="AO18" s="100"/>
+      <c r="AP18" s="83"/>
+      <c r="AQ18" s="94"/>
+      <c r="AR18" s="95"/>
+      <c r="AS18" s="83"/>
+      <c r="AT18" s="83"/>
+      <c r="AU18" s="95"/>
+      <c r="AV18" s="94"/>
+      <c r="AW18" s="95"/>
+      <c r="AX18" s="89"/>
+      <c r="AY18" s="89"/>
+      <c r="AZ18" s="89"/>
+      <c r="BA18" s="96"/>
+      <c r="BB18" s="95"/>
+      <c r="BC18" s="89"/>
+      <c r="BD18" s="89"/>
+      <c r="BE18" s="95"/>
+      <c r="BF18" s="95"/>
     </row>
     <row r="19" spans="1:58" ht="30" customHeight="1">
-      <c r="A19" s="88"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="95">
+      <c r="A19" s="83"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="161">
+      <c r="J19" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="120"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="101"/>
-      <c r="T19" s="102"/>
-      <c r="U19" s="121"/>
-      <c r="V19" s="121"/>
-      <c r="W19" s="120"/>
-      <c r="X19" s="88"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="148"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="89"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="99"/>
+      <c r="X19" s="83"/>
       <c r="Y19" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z19" s="160">
+      <c r="Z19" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="159">
+      <c r="AA19" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="104"/>
-      <c r="AC19" s="103"/>
-      <c r="AD19" s="105"/>
-      <c r="AE19" s="125"/>
-      <c r="AF19" s="117"/>
-      <c r="AG19" s="123">
+      <c r="AB19" s="91"/>
+      <c r="AC19" s="90"/>
+      <c r="AD19" s="92"/>
+      <c r="AE19" s="153"/>
+      <c r="AF19" s="154"/>
+      <c r="AG19" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="126"/>
-      <c r="AI19" s="101"/>
-      <c r="AJ19" s="110"/>
-      <c r="AK19" s="111"/>
-      <c r="AL19" s="111"/>
-      <c r="AM19" s="121"/>
-      <c r="AN19" s="121"/>
-      <c r="AO19" s="121"/>
-      <c r="AP19" s="88"/>
-      <c r="AQ19" s="112"/>
-      <c r="AR19" s="113"/>
-      <c r="AS19" s="88"/>
-      <c r="AT19" s="88"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="112"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="102"/>
-      <c r="AY19" s="102"/>
-      <c r="AZ19" s="102"/>
-      <c r="BA19" s="114"/>
-      <c r="BB19" s="113"/>
-      <c r="BC19" s="102"/>
-      <c r="BD19" s="102"/>
-      <c r="BE19" s="113"/>
-      <c r="BF19" s="113"/>
+      <c r="AH19" s="103"/>
+      <c r="AI19" s="88"/>
+      <c r="AJ19" s="152"/>
+      <c r="AK19" s="93"/>
+      <c r="AL19" s="93"/>
+      <c r="AM19" s="100"/>
+      <c r="AN19" s="100"/>
+      <c r="AO19" s="100"/>
+      <c r="AP19" s="83"/>
+      <c r="AQ19" s="94"/>
+      <c r="AR19" s="95"/>
+      <c r="AS19" s="83"/>
+      <c r="AT19" s="83"/>
+      <c r="AU19" s="95"/>
+      <c r="AV19" s="94"/>
+      <c r="AW19" s="95"/>
+      <c r="AX19" s="89"/>
+      <c r="AY19" s="89"/>
+      <c r="AZ19" s="89"/>
+      <c r="BA19" s="96"/>
+      <c r="BB19" s="95"/>
+      <c r="BC19" s="89"/>
+      <c r="BD19" s="89"/>
+      <c r="BE19" s="95"/>
+      <c r="BF19" s="95"/>
     </row>
     <row r="20" spans="1:58" ht="30" customHeight="1">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="95">
+      <c r="A20" s="83"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="161">
+      <c r="J20" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="119"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="120"/>
-      <c r="Q20" s="121"/>
-      <c r="R20" s="100"/>
-      <c r="S20" s="101"/>
-      <c r="T20" s="102"/>
-      <c r="U20" s="121"/>
-      <c r="V20" s="121"/>
-      <c r="W20" s="120"/>
-      <c r="X20" s="88"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="148"/>
+      <c r="O20" s="88"/>
+      <c r="P20" s="99"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="89"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="100"/>
+      <c r="W20" s="99"/>
+      <c r="X20" s="83"/>
       <c r="Y20" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="160">
+      <c r="Z20" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="159">
+      <c r="AA20" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="104"/>
-      <c r="AC20" s="103"/>
-      <c r="AD20" s="105"/>
-      <c r="AE20" s="125"/>
-      <c r="AF20" s="117"/>
-      <c r="AG20" s="123">
+      <c r="AB20" s="91"/>
+      <c r="AC20" s="90"/>
+      <c r="AD20" s="92"/>
+      <c r="AE20" s="153"/>
+      <c r="AF20" s="154"/>
+      <c r="AG20" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="126"/>
-      <c r="AI20" s="101"/>
-      <c r="AJ20" s="110"/>
-      <c r="AK20" s="111"/>
-      <c r="AL20" s="111"/>
-      <c r="AM20" s="121"/>
-      <c r="AN20" s="121"/>
-      <c r="AO20" s="121"/>
-      <c r="AP20" s="88"/>
-      <c r="AQ20" s="112"/>
-      <c r="AR20" s="113"/>
-      <c r="AS20" s="88"/>
-      <c r="AT20" s="88"/>
-      <c r="AU20" s="113"/>
-      <c r="AV20" s="112"/>
-      <c r="AW20" s="113"/>
-      <c r="AX20" s="102"/>
-      <c r="AY20" s="102"/>
-      <c r="AZ20" s="88"/>
-      <c r="BA20" s="114"/>
-      <c r="BB20" s="113"/>
-      <c r="BC20" s="102"/>
-      <c r="BD20" s="102"/>
-      <c r="BE20" s="113"/>
-      <c r="BF20" s="113"/>
+      <c r="AH20" s="103"/>
+      <c r="AI20" s="88"/>
+      <c r="AJ20" s="152"/>
+      <c r="AK20" s="93"/>
+      <c r="AL20" s="93"/>
+      <c r="AM20" s="100"/>
+      <c r="AN20" s="100"/>
+      <c r="AO20" s="100"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="94"/>
+      <c r="AR20" s="95"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="95"/>
+      <c r="AV20" s="94"/>
+      <c r="AW20" s="95"/>
+      <c r="AX20" s="89"/>
+      <c r="AY20" s="89"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="96"/>
+      <c r="BB20" s="95"/>
+      <c r="BC20" s="89"/>
+      <c r="BD20" s="89"/>
+      <c r="BE20" s="95"/>
+      <c r="BF20" s="95"/>
     </row>
     <row r="21" spans="1:58" ht="30" customHeight="1">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="95">
+      <c r="A21" s="83"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="149"/>
+      <c r="I21" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="161">
+      <c r="J21" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="120"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="100"/>
-      <c r="S21" s="101"/>
-      <c r="T21" s="102"/>
-      <c r="U21" s="121"/>
-      <c r="V21" s="121"/>
-      <c r="W21" s="120"/>
-      <c r="X21" s="88"/>
+      <c r="K21" s="149"/>
+      <c r="L21" s="149"/>
+      <c r="M21" s="149"/>
+      <c r="N21" s="148"/>
+      <c r="O21" s="88"/>
+      <c r="P21" s="99"/>
+      <c r="Q21" s="100"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="100"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="99"/>
+      <c r="X21" s="83"/>
       <c r="Y21" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="160">
+      <c r="Z21" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="159">
+      <c r="AA21" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="104"/>
-      <c r="AC21" s="103"/>
-      <c r="AD21" s="105"/>
-      <c r="AE21" s="125"/>
-      <c r="AF21" s="117"/>
-      <c r="AG21" s="123">
+      <c r="AB21" s="91"/>
+      <c r="AC21" s="90"/>
+      <c r="AD21" s="92"/>
+      <c r="AE21" s="153"/>
+      <c r="AF21" s="154"/>
+      <c r="AG21" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="126"/>
-      <c r="AI21" s="101"/>
-      <c r="AJ21" s="110"/>
-      <c r="AK21" s="111"/>
-      <c r="AL21" s="111"/>
-      <c r="AM21" s="121"/>
-      <c r="AN21" s="121"/>
-      <c r="AO21" s="121"/>
-      <c r="AP21" s="88"/>
-      <c r="AQ21" s="112"/>
-      <c r="AR21" s="113"/>
-      <c r="AS21" s="88"/>
-      <c r="AT21" s="88"/>
-      <c r="AU21" s="113"/>
-      <c r="AV21" s="112"/>
-      <c r="AW21" s="113"/>
-      <c r="AX21" s="102"/>
-      <c r="AY21" s="102"/>
-      <c r="AZ21" s="88"/>
-      <c r="BA21" s="114"/>
-      <c r="BB21" s="113"/>
-      <c r="BC21" s="102"/>
-      <c r="BD21" s="102"/>
-      <c r="BE21" s="113"/>
-      <c r="BF21" s="113"/>
+      <c r="AH21" s="103"/>
+      <c r="AI21" s="88"/>
+      <c r="AJ21" s="152"/>
+      <c r="AK21" s="93"/>
+      <c r="AL21" s="93"/>
+      <c r="AM21" s="100"/>
+      <c r="AN21" s="100"/>
+      <c r="AO21" s="100"/>
+      <c r="AP21" s="83"/>
+      <c r="AQ21" s="94"/>
+      <c r="AR21" s="95"/>
+      <c r="AS21" s="83"/>
+      <c r="AT21" s="83"/>
+      <c r="AU21" s="95"/>
+      <c r="AV21" s="94"/>
+      <c r="AW21" s="95"/>
+      <c r="AX21" s="89"/>
+      <c r="AY21" s="89"/>
+      <c r="AZ21" s="83"/>
+      <c r="BA21" s="96"/>
+      <c r="BB21" s="95"/>
+      <c r="BC21" s="89"/>
+      <c r="BD21" s="89"/>
+      <c r="BE21" s="95"/>
+      <c r="BF21" s="95"/>
     </row>
     <row r="22" spans="1:58" ht="30" customHeight="1">
-      <c r="A22" s="88"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="95">
+      <c r="A22" s="83"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="161">
+      <c r="J22" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="120"/>
-      <c r="Q22" s="121"/>
-      <c r="R22" s="100"/>
-      <c r="S22" s="101"/>
-      <c r="T22" s="102"/>
-      <c r="U22" s="121"/>
-      <c r="V22" s="121"/>
-      <c r="W22" s="120"/>
-      <c r="X22" s="88"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="145"/>
+      <c r="N22" s="148"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="99"/>
+      <c r="Q22" s="100"/>
+      <c r="R22" s="87"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="100"/>
+      <c r="V22" s="100"/>
+      <c r="W22" s="99"/>
+      <c r="X22" s="83"/>
       <c r="Y22" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z22" s="160">
+      <c r="Z22" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA22" s="159">
+      <c r="AA22" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB22" s="104"/>
-      <c r="AC22" s="103"/>
-      <c r="AD22" s="105"/>
-      <c r="AE22" s="122"/>
-      <c r="AF22" s="107"/>
-      <c r="AG22" s="123">
+      <c r="AB22" s="91"/>
+      <c r="AC22" s="90"/>
+      <c r="AD22" s="92"/>
+      <c r="AE22" s="150"/>
+      <c r="AF22" s="151"/>
+      <c r="AG22" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="124"/>
-      <c r="AI22" s="101"/>
-      <c r="AJ22" s="110"/>
-      <c r="AK22" s="111"/>
-      <c r="AL22" s="111"/>
-      <c r="AM22" s="121"/>
-      <c r="AN22" s="121"/>
-      <c r="AO22" s="121"/>
-      <c r="AP22" s="88"/>
-      <c r="AQ22" s="112"/>
-      <c r="AR22" s="113"/>
-      <c r="AS22" s="88"/>
-      <c r="AT22" s="88"/>
-      <c r="AU22" s="113"/>
-      <c r="AV22" s="112"/>
-      <c r="AW22" s="113"/>
-      <c r="AX22" s="102"/>
-      <c r="AY22" s="102"/>
-      <c r="AZ22" s="102"/>
-      <c r="BA22" s="114"/>
-      <c r="BB22" s="113"/>
-      <c r="BC22" s="102"/>
-      <c r="BD22" s="102"/>
-      <c r="BE22" s="113"/>
-      <c r="BF22" s="113"/>
+      <c r="AH22" s="102"/>
+      <c r="AI22" s="88"/>
+      <c r="AJ22" s="152"/>
+      <c r="AK22" s="93"/>
+      <c r="AL22" s="93"/>
+      <c r="AM22" s="100"/>
+      <c r="AN22" s="100"/>
+      <c r="AO22" s="100"/>
+      <c r="AP22" s="83"/>
+      <c r="AQ22" s="94"/>
+      <c r="AR22" s="95"/>
+      <c r="AS22" s="83"/>
+      <c r="AT22" s="83"/>
+      <c r="AU22" s="95"/>
+      <c r="AV22" s="94"/>
+      <c r="AW22" s="95"/>
+      <c r="AX22" s="89"/>
+      <c r="AY22" s="89"/>
+      <c r="AZ22" s="89"/>
+      <c r="BA22" s="96"/>
+      <c r="BB22" s="95"/>
+      <c r="BC22" s="89"/>
+      <c r="BD22" s="89"/>
+      <c r="BE22" s="95"/>
+      <c r="BF22" s="95"/>
     </row>
     <row r="23" spans="1:58" ht="30" customHeight="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="90"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="95">
+      <c r="A23" s="83"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="161">
+      <c r="J23" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="120"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="100"/>
-      <c r="S23" s="101"/>
-      <c r="T23" s="102"/>
-      <c r="U23" s="121"/>
-      <c r="V23" s="121"/>
-      <c r="W23" s="120"/>
-      <c r="X23" s="88"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="88"/>
+      <c r="P23" s="99"/>
+      <c r="Q23" s="100"/>
+      <c r="R23" s="87"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="89"/>
+      <c r="U23" s="100"/>
+      <c r="V23" s="100"/>
+      <c r="W23" s="99"/>
+      <c r="X23" s="83"/>
       <c r="Y23" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="160">
+      <c r="Z23" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="159">
+      <c r="AA23" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="104"/>
-      <c r="AC23" s="103"/>
-      <c r="AD23" s="105"/>
-      <c r="AE23" s="122"/>
-      <c r="AF23" s="107"/>
-      <c r="AG23" s="123">
+      <c r="AB23" s="91"/>
+      <c r="AC23" s="90"/>
+      <c r="AD23" s="92"/>
+      <c r="AE23" s="150"/>
+      <c r="AF23" s="151"/>
+      <c r="AG23" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="124"/>
-      <c r="AI23" s="101"/>
-      <c r="AJ23" s="110"/>
-      <c r="AK23" s="111"/>
-      <c r="AL23" s="111"/>
-      <c r="AM23" s="121"/>
-      <c r="AN23" s="121"/>
-      <c r="AO23" s="121"/>
-      <c r="AP23" s="88"/>
-      <c r="AQ23" s="112"/>
-      <c r="AR23" s="113"/>
-      <c r="AS23" s="88"/>
-      <c r="AT23" s="88"/>
-      <c r="AU23" s="113"/>
-      <c r="AV23" s="112"/>
-      <c r="AW23" s="113"/>
-      <c r="AX23" s="102"/>
-      <c r="AY23" s="102"/>
-      <c r="AZ23" s="102"/>
-      <c r="BA23" s="114"/>
-      <c r="BB23" s="113"/>
-      <c r="BC23" s="102"/>
-      <c r="BD23" s="102"/>
-      <c r="BE23" s="113"/>
-      <c r="BF23" s="113"/>
+      <c r="AH23" s="102"/>
+      <c r="AI23" s="88"/>
+      <c r="AJ23" s="152"/>
+      <c r="AK23" s="93"/>
+      <c r="AL23" s="93"/>
+      <c r="AM23" s="100"/>
+      <c r="AN23" s="100"/>
+      <c r="AO23" s="100"/>
+      <c r="AP23" s="83"/>
+      <c r="AQ23" s="94"/>
+      <c r="AR23" s="95"/>
+      <c r="AS23" s="83"/>
+      <c r="AT23" s="83"/>
+      <c r="AU23" s="95"/>
+      <c r="AV23" s="94"/>
+      <c r="AW23" s="95"/>
+      <c r="AX23" s="89"/>
+      <c r="AY23" s="89"/>
+      <c r="AZ23" s="89"/>
+      <c r="BA23" s="96"/>
+      <c r="BB23" s="95"/>
+      <c r="BC23" s="89"/>
+      <c r="BD23" s="89"/>
+      <c r="BE23" s="95"/>
+      <c r="BF23" s="95"/>
     </row>
     <row r="24" spans="1:58" ht="30" customHeight="1">
-      <c r="A24" s="88"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="95">
+      <c r="A24" s="83"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="143"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="161">
+      <c r="J24" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="120"/>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="100"/>
-      <c r="S24" s="101"/>
-      <c r="T24" s="102"/>
-      <c r="U24" s="121"/>
-      <c r="V24" s="121"/>
-      <c r="W24" s="120"/>
-      <c r="X24" s="88"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="145"/>
+      <c r="N24" s="148"/>
+      <c r="O24" s="88"/>
+      <c r="P24" s="99"/>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="87"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="89"/>
+      <c r="U24" s="100"/>
+      <c r="V24" s="100"/>
+      <c r="W24" s="99"/>
+      <c r="X24" s="83"/>
       <c r="Y24" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z24" s="160">
+      <c r="Z24" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA24" s="159">
+      <c r="AA24" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB24" s="104"/>
-      <c r="AC24" s="103"/>
-      <c r="AD24" s="105"/>
-      <c r="AE24" s="122"/>
-      <c r="AF24" s="107"/>
-      <c r="AG24" s="123">
+      <c r="AB24" s="91"/>
+      <c r="AC24" s="90"/>
+      <c r="AD24" s="92"/>
+      <c r="AE24" s="150"/>
+      <c r="AF24" s="151"/>
+      <c r="AG24" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="124"/>
-      <c r="AI24" s="101"/>
-      <c r="AJ24" s="110"/>
-      <c r="AK24" s="111"/>
-      <c r="AL24" s="111"/>
-      <c r="AM24" s="121"/>
-      <c r="AN24" s="121"/>
-      <c r="AO24" s="121"/>
-      <c r="AP24" s="88"/>
-      <c r="AQ24" s="112"/>
-      <c r="AR24" s="113"/>
-      <c r="AS24" s="88"/>
-      <c r="AT24" s="88"/>
-      <c r="AU24" s="113"/>
-      <c r="AV24" s="112"/>
-      <c r="AW24" s="113"/>
-      <c r="AX24" s="102"/>
-      <c r="AY24" s="102"/>
-      <c r="AZ24" s="102"/>
-      <c r="BA24" s="114"/>
-      <c r="BB24" s="113"/>
-      <c r="BC24" s="102"/>
-      <c r="BD24" s="102"/>
-      <c r="BE24" s="113"/>
-      <c r="BF24" s="113"/>
+      <c r="AH24" s="102"/>
+      <c r="AI24" s="88"/>
+      <c r="AJ24" s="152"/>
+      <c r="AK24" s="93"/>
+      <c r="AL24" s="93"/>
+      <c r="AM24" s="100"/>
+      <c r="AN24" s="100"/>
+      <c r="AO24" s="100"/>
+      <c r="AP24" s="83"/>
+      <c r="AQ24" s="94"/>
+      <c r="AR24" s="95"/>
+      <c r="AS24" s="83"/>
+      <c r="AT24" s="83"/>
+      <c r="AU24" s="95"/>
+      <c r="AV24" s="94"/>
+      <c r="AW24" s="95"/>
+      <c r="AX24" s="89"/>
+      <c r="AY24" s="89"/>
+      <c r="AZ24" s="89"/>
+      <c r="BA24" s="96"/>
+      <c r="BB24" s="95"/>
+      <c r="BC24" s="89"/>
+      <c r="BD24" s="89"/>
+      <c r="BE24" s="95"/>
+      <c r="BF24" s="95"/>
     </row>
     <row r="25" spans="1:58" ht="30" customHeight="1">
-      <c r="A25" s="88"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="95">
+      <c r="A25" s="83"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="145"/>
+      <c r="I25" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="161">
+      <c r="J25" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="94"/>
-      <c r="N25" s="119"/>
-      <c r="O25" s="97"/>
-      <c r="P25" s="120"/>
-      <c r="Q25" s="121"/>
-      <c r="R25" s="100"/>
-      <c r="S25" s="101"/>
-      <c r="T25" s="102"/>
-      <c r="U25" s="121"/>
-      <c r="V25" s="121"/>
-      <c r="W25" s="120"/>
-      <c r="X25" s="88"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="145"/>
+      <c r="N25" s="148"/>
+      <c r="O25" s="88"/>
+      <c r="P25" s="99"/>
+      <c r="Q25" s="100"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="100"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="99"/>
+      <c r="X25" s="83"/>
       <c r="Y25" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z25" s="160">
+      <c r="Z25" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA25" s="159">
+      <c r="AA25" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB25" s="104"/>
-      <c r="AC25" s="103"/>
-      <c r="AD25" s="105"/>
-      <c r="AE25" s="122"/>
-      <c r="AF25" s="107"/>
-      <c r="AG25" s="123">
+      <c r="AB25" s="91"/>
+      <c r="AC25" s="90"/>
+      <c r="AD25" s="92"/>
+      <c r="AE25" s="150"/>
+      <c r="AF25" s="151"/>
+      <c r="AG25" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="124"/>
-      <c r="AI25" s="101"/>
-      <c r="AJ25" s="110"/>
-      <c r="AK25" s="111"/>
-      <c r="AL25" s="111"/>
-      <c r="AM25" s="121"/>
-      <c r="AN25" s="121"/>
-      <c r="AO25" s="121"/>
-      <c r="AP25" s="88"/>
-      <c r="AQ25" s="112"/>
-      <c r="AR25" s="113"/>
-      <c r="AS25" s="88"/>
-      <c r="AT25" s="88"/>
-      <c r="AU25" s="113"/>
-      <c r="AV25" s="112"/>
-      <c r="AW25" s="113"/>
-      <c r="AX25" s="102"/>
-      <c r="AY25" s="102"/>
-      <c r="AZ25" s="102"/>
-      <c r="BA25" s="114"/>
-      <c r="BB25" s="113"/>
-      <c r="BC25" s="102"/>
-      <c r="BD25" s="102"/>
-      <c r="BE25" s="113"/>
-      <c r="BF25" s="113"/>
+      <c r="AH25" s="102"/>
+      <c r="AI25" s="88"/>
+      <c r="AJ25" s="152"/>
+      <c r="AK25" s="93"/>
+      <c r="AL25" s="93"/>
+      <c r="AM25" s="100"/>
+      <c r="AN25" s="100"/>
+      <c r="AO25" s="100"/>
+      <c r="AP25" s="83"/>
+      <c r="AQ25" s="94"/>
+      <c r="AR25" s="95"/>
+      <c r="AS25" s="83"/>
+      <c r="AT25" s="83"/>
+      <c r="AU25" s="95"/>
+      <c r="AV25" s="94"/>
+      <c r="AW25" s="95"/>
+      <c r="AX25" s="89"/>
+      <c r="AY25" s="89"/>
+      <c r="AZ25" s="89"/>
+      <c r="BA25" s="96"/>
+      <c r="BB25" s="95"/>
+      <c r="BC25" s="89"/>
+      <c r="BD25" s="89"/>
+      <c r="BE25" s="95"/>
+      <c r="BF25" s="95"/>
     </row>
     <row r="26" spans="1:58" ht="30" customHeight="1">
-      <c r="A26" s="88"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="95">
+      <c r="A26" s="83"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="144"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="145"/>
+      <c r="I26" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="161">
+      <c r="J26" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="94"/>
-      <c r="L26" s="94"/>
-      <c r="M26" s="94"/>
-      <c r="N26" s="119"/>
-      <c r="O26" s="97"/>
-      <c r="P26" s="120"/>
-      <c r="Q26" s="121"/>
-      <c r="R26" s="100"/>
-      <c r="S26" s="101"/>
-      <c r="T26" s="102"/>
-      <c r="U26" s="121"/>
-      <c r="V26" s="121"/>
-      <c r="W26" s="120"/>
-      <c r="X26" s="88"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="145"/>
+      <c r="N26" s="148"/>
+      <c r="O26" s="88"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="100"/>
+      <c r="R26" s="87"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="89"/>
+      <c r="U26" s="100"/>
+      <c r="V26" s="100"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="83"/>
       <c r="Y26" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z26" s="160">
+      <c r="Z26" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="159">
+      <c r="AA26" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB26" s="104"/>
-      <c r="AC26" s="103"/>
-      <c r="AD26" s="105"/>
-      <c r="AE26" s="122"/>
-      <c r="AF26" s="107"/>
-      <c r="AG26" s="123">
+      <c r="AB26" s="91"/>
+      <c r="AC26" s="90"/>
+      <c r="AD26" s="92"/>
+      <c r="AE26" s="150"/>
+      <c r="AF26" s="151"/>
+      <c r="AG26" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="124"/>
-      <c r="AI26" s="101"/>
-      <c r="AJ26" s="110"/>
-      <c r="AK26" s="111"/>
-      <c r="AL26" s="111"/>
-      <c r="AM26" s="121"/>
-      <c r="AN26" s="121"/>
-      <c r="AO26" s="121"/>
-      <c r="AP26" s="88"/>
-      <c r="AQ26" s="112"/>
-      <c r="AR26" s="113"/>
-      <c r="AS26" s="88"/>
-      <c r="AT26" s="88"/>
-      <c r="AU26" s="113"/>
-      <c r="AV26" s="112"/>
-      <c r="AW26" s="113"/>
-      <c r="AX26" s="102"/>
-      <c r="AY26" s="102"/>
-      <c r="AZ26" s="102"/>
-      <c r="BA26" s="114"/>
-      <c r="BB26" s="113"/>
-      <c r="BC26" s="102"/>
-      <c r="BD26" s="102"/>
-      <c r="BE26" s="113"/>
-      <c r="BF26" s="113"/>
+      <c r="AH26" s="102"/>
+      <c r="AI26" s="88"/>
+      <c r="AJ26" s="152"/>
+      <c r="AK26" s="93"/>
+      <c r="AL26" s="93"/>
+      <c r="AM26" s="100"/>
+      <c r="AN26" s="100"/>
+      <c r="AO26" s="100"/>
+      <c r="AP26" s="83"/>
+      <c r="AQ26" s="94"/>
+      <c r="AR26" s="95"/>
+      <c r="AS26" s="83"/>
+      <c r="AT26" s="83"/>
+      <c r="AU26" s="95"/>
+      <c r="AV26" s="94"/>
+      <c r="AW26" s="95"/>
+      <c r="AX26" s="89"/>
+      <c r="AY26" s="89"/>
+      <c r="AZ26" s="89"/>
+      <c r="BA26" s="96"/>
+      <c r="BB26" s="95"/>
+      <c r="BC26" s="89"/>
+      <c r="BD26" s="89"/>
+      <c r="BE26" s="95"/>
+      <c r="BF26" s="95"/>
     </row>
     <row r="27" spans="1:58" ht="30" customHeight="1">
-      <c r="A27" s="88"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="95">
+      <c r="A27" s="83"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="144"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="145"/>
+      <c r="I27" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="161">
+      <c r="J27" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="94"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="94"/>
-      <c r="N27" s="119"/>
-      <c r="O27" s="97"/>
-      <c r="P27" s="120"/>
-      <c r="Q27" s="121"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="101"/>
-      <c r="T27" s="102"/>
-      <c r="U27" s="121"/>
-      <c r="V27" s="121"/>
-      <c r="W27" s="120"/>
-      <c r="X27" s="88"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="145"/>
+      <c r="N27" s="148"/>
+      <c r="O27" s="88"/>
+      <c r="P27" s="99"/>
+      <c r="Q27" s="100"/>
+      <c r="R27" s="87"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="89"/>
+      <c r="U27" s="100"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="99"/>
+      <c r="X27" s="83"/>
       <c r="Y27" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="160">
+      <c r="Z27" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="159">
+      <c r="AA27" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="104"/>
-      <c r="AC27" s="103"/>
-      <c r="AD27" s="105"/>
-      <c r="AE27" s="122"/>
-      <c r="AF27" s="107"/>
-      <c r="AG27" s="123">
+      <c r="AB27" s="91"/>
+      <c r="AC27" s="90"/>
+      <c r="AD27" s="92"/>
+      <c r="AE27" s="150"/>
+      <c r="AF27" s="151"/>
+      <c r="AG27" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="124"/>
-      <c r="AI27" s="101"/>
-      <c r="AJ27" s="110"/>
-      <c r="AK27" s="111"/>
-      <c r="AL27" s="111"/>
-      <c r="AM27" s="121"/>
-      <c r="AN27" s="121"/>
-      <c r="AO27" s="121"/>
-      <c r="AP27" s="88"/>
-      <c r="AQ27" s="112"/>
-      <c r="AR27" s="113"/>
-      <c r="AS27" s="88"/>
-      <c r="AT27" s="88"/>
-      <c r="AU27" s="113"/>
-      <c r="AV27" s="112"/>
-      <c r="AW27" s="113"/>
-      <c r="AX27" s="102"/>
-      <c r="AY27" s="102"/>
-      <c r="AZ27" s="102"/>
-      <c r="BA27" s="114"/>
-      <c r="BB27" s="113"/>
-      <c r="BC27" s="102"/>
-      <c r="BD27" s="102"/>
-      <c r="BE27" s="113"/>
-      <c r="BF27" s="113"/>
+      <c r="AH27" s="102"/>
+      <c r="AI27" s="88"/>
+      <c r="AJ27" s="152"/>
+      <c r="AK27" s="93"/>
+      <c r="AL27" s="93"/>
+      <c r="AM27" s="100"/>
+      <c r="AN27" s="100"/>
+      <c r="AO27" s="100"/>
+      <c r="AP27" s="83"/>
+      <c r="AQ27" s="94"/>
+      <c r="AR27" s="95"/>
+      <c r="AS27" s="83"/>
+      <c r="AT27" s="83"/>
+      <c r="AU27" s="95"/>
+      <c r="AV27" s="94"/>
+      <c r="AW27" s="95"/>
+      <c r="AX27" s="89"/>
+      <c r="AY27" s="89"/>
+      <c r="AZ27" s="89"/>
+      <c r="BA27" s="96"/>
+      <c r="BB27" s="95"/>
+      <c r="BC27" s="89"/>
+      <c r="BD27" s="89"/>
+      <c r="BE27" s="95"/>
+      <c r="BF27" s="95"/>
     </row>
     <row r="28" spans="1:58" ht="30" customHeight="1">
-      <c r="A28" s="88"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="95">
+      <c r="A28" s="83"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="161">
+      <c r="J28" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="94"/>
-      <c r="L28" s="94"/>
-      <c r="M28" s="94"/>
-      <c r="N28" s="119"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="121"/>
-      <c r="R28" s="100"/>
-      <c r="S28" s="101"/>
-      <c r="T28" s="102"/>
-      <c r="U28" s="121"/>
-      <c r="V28" s="121"/>
-      <c r="W28" s="120"/>
-      <c r="X28" s="88"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="145"/>
+      <c r="N28" s="148"/>
+      <c r="O28" s="88"/>
+      <c r="P28" s="99"/>
+      <c r="Q28" s="100"/>
+      <c r="R28" s="87"/>
+      <c r="S28" s="88"/>
+      <c r="T28" s="89"/>
+      <c r="U28" s="100"/>
+      <c r="V28" s="100"/>
+      <c r="W28" s="99"/>
+      <c r="X28" s="83"/>
       <c r="Y28" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="160">
+      <c r="Z28" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="159">
+      <c r="AA28" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="104"/>
-      <c r="AC28" s="103"/>
-      <c r="AD28" s="105"/>
-      <c r="AE28" s="122"/>
-      <c r="AF28" s="107"/>
-      <c r="AG28" s="123">
+      <c r="AB28" s="91"/>
+      <c r="AC28" s="90"/>
+      <c r="AD28" s="92"/>
+      <c r="AE28" s="150"/>
+      <c r="AF28" s="151"/>
+      <c r="AG28" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="124"/>
-      <c r="AI28" s="101"/>
-      <c r="AJ28" s="110"/>
-      <c r="AK28" s="111"/>
-      <c r="AL28" s="111"/>
-      <c r="AM28" s="121"/>
-      <c r="AN28" s="121"/>
-      <c r="AO28" s="121"/>
-      <c r="AP28" s="88"/>
-      <c r="AQ28" s="112"/>
-      <c r="AR28" s="113"/>
-      <c r="AS28" s="88"/>
-      <c r="AT28" s="88"/>
-      <c r="AU28" s="113"/>
-      <c r="AV28" s="112"/>
-      <c r="AW28" s="113"/>
-      <c r="AX28" s="102"/>
-      <c r="AY28" s="102"/>
-      <c r="AZ28" s="102"/>
-      <c r="BA28" s="114"/>
-      <c r="BB28" s="113"/>
-      <c r="BC28" s="102"/>
-      <c r="BD28" s="102"/>
-      <c r="BE28" s="113"/>
-      <c r="BF28" s="113"/>
+      <c r="AH28" s="102"/>
+      <c r="AI28" s="88"/>
+      <c r="AJ28" s="152"/>
+      <c r="AK28" s="93"/>
+      <c r="AL28" s="93"/>
+      <c r="AM28" s="100"/>
+      <c r="AN28" s="100"/>
+      <c r="AO28" s="100"/>
+      <c r="AP28" s="83"/>
+      <c r="AQ28" s="94"/>
+      <c r="AR28" s="95"/>
+      <c r="AS28" s="83"/>
+      <c r="AT28" s="83"/>
+      <c r="AU28" s="95"/>
+      <c r="AV28" s="94"/>
+      <c r="AW28" s="95"/>
+      <c r="AX28" s="89"/>
+      <c r="AY28" s="89"/>
+      <c r="AZ28" s="89"/>
+      <c r="BA28" s="96"/>
+      <c r="BB28" s="95"/>
+      <c r="BC28" s="89"/>
+      <c r="BD28" s="89"/>
+      <c r="BE28" s="95"/>
+      <c r="BF28" s="95"/>
     </row>
     <row r="29" spans="1:58" ht="30" customHeight="1">
-      <c r="A29" s="88"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="95">
+      <c r="A29" s="83"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="143"/>
+      <c r="F29" s="144"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="161">
+      <c r="J29" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94"/>
-      <c r="M29" s="94"/>
-      <c r="N29" s="119"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="120"/>
-      <c r="Q29" s="121"/>
-      <c r="R29" s="100"/>
-      <c r="S29" s="101"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="121"/>
-      <c r="V29" s="121"/>
-      <c r="W29" s="120"/>
-      <c r="X29" s="88"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="145"/>
+      <c r="N29" s="148"/>
+      <c r="O29" s="88"/>
+      <c r="P29" s="99"/>
+      <c r="Q29" s="100"/>
+      <c r="R29" s="87"/>
+      <c r="S29" s="88"/>
+      <c r="T29" s="89"/>
+      <c r="U29" s="100"/>
+      <c r="V29" s="100"/>
+      <c r="W29" s="99"/>
+      <c r="X29" s="83"/>
       <c r="Y29" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="160">
+      <c r="Z29" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="159">
+      <c r="AA29" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="104"/>
-      <c r="AC29" s="103"/>
-      <c r="AD29" s="105"/>
-      <c r="AE29" s="122"/>
-      <c r="AF29" s="107"/>
-      <c r="AG29" s="123">
+      <c r="AB29" s="91"/>
+      <c r="AC29" s="90"/>
+      <c r="AD29" s="92"/>
+      <c r="AE29" s="150"/>
+      <c r="AF29" s="151"/>
+      <c r="AG29" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="124"/>
-      <c r="AI29" s="101"/>
-      <c r="AJ29" s="110"/>
-      <c r="AK29" s="111"/>
-      <c r="AL29" s="111"/>
-      <c r="AM29" s="121"/>
-      <c r="AN29" s="121"/>
-      <c r="AO29" s="121"/>
-      <c r="AP29" s="88"/>
-      <c r="AQ29" s="112"/>
-      <c r="AR29" s="113"/>
-      <c r="AS29" s="88"/>
-      <c r="AT29" s="88"/>
-      <c r="AU29" s="113"/>
-      <c r="AV29" s="112"/>
-      <c r="AW29" s="113"/>
-      <c r="AX29" s="102"/>
-      <c r="AY29" s="102"/>
-      <c r="AZ29" s="102"/>
-      <c r="BA29" s="114"/>
-      <c r="BB29" s="113"/>
-      <c r="BC29" s="102"/>
-      <c r="BD29" s="102"/>
-      <c r="BE29" s="113"/>
-      <c r="BF29" s="113"/>
+      <c r="AH29" s="102"/>
+      <c r="AI29" s="88"/>
+      <c r="AJ29" s="152"/>
+      <c r="AK29" s="93"/>
+      <c r="AL29" s="93"/>
+      <c r="AM29" s="100"/>
+      <c r="AN29" s="100"/>
+      <c r="AO29" s="100"/>
+      <c r="AP29" s="83"/>
+      <c r="AQ29" s="94"/>
+      <c r="AR29" s="95"/>
+      <c r="AS29" s="83"/>
+      <c r="AT29" s="83"/>
+      <c r="AU29" s="95"/>
+      <c r="AV29" s="94"/>
+      <c r="AW29" s="95"/>
+      <c r="AX29" s="89"/>
+      <c r="AY29" s="89"/>
+      <c r="AZ29" s="89"/>
+      <c r="BA29" s="96"/>
+      <c r="BB29" s="95"/>
+      <c r="BC29" s="89"/>
+      <c r="BD29" s="89"/>
+      <c r="BE29" s="95"/>
+      <c r="BF29" s="95"/>
     </row>
     <row r="30" spans="1:58" ht="30.75" customHeight="1">
-      <c r="A30" s="88"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="116"/>
-      <c r="I30" s="95">
+      <c r="A30" s="83"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="144"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="149"/>
+      <c r="I30" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="161">
+      <c r="J30" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="116"/>
-      <c r="L30" s="116"/>
-      <c r="M30" s="116"/>
-      <c r="N30" s="119"/>
-      <c r="O30" s="97"/>
-      <c r="P30" s="120"/>
-      <c r="Q30" s="121"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="101"/>
-      <c r="T30" s="102"/>
-      <c r="U30" s="121"/>
-      <c r="V30" s="121"/>
-      <c r="W30" s="120"/>
-      <c r="X30" s="88"/>
+      <c r="K30" s="149"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="149"/>
+      <c r="N30" s="148"/>
+      <c r="O30" s="88"/>
+      <c r="P30" s="99"/>
+      <c r="Q30" s="100"/>
+      <c r="R30" s="87"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="89"/>
+      <c r="U30" s="100"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="99"/>
+      <c r="X30" s="83"/>
       <c r="Y30" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="160">
+      <c r="Z30" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="159">
+      <c r="AA30" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="104"/>
-      <c r="AC30" s="103"/>
-      <c r="AD30" s="105"/>
-      <c r="AE30" s="125"/>
-      <c r="AF30" s="117"/>
-      <c r="AG30" s="123">
+      <c r="AB30" s="91"/>
+      <c r="AC30" s="90"/>
+      <c r="AD30" s="92"/>
+      <c r="AE30" s="153"/>
+      <c r="AF30" s="154"/>
+      <c r="AG30" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="126"/>
-      <c r="AI30" s="101"/>
-      <c r="AJ30" s="110"/>
-      <c r="AK30" s="111"/>
-      <c r="AL30" s="111"/>
-      <c r="AM30" s="121"/>
-      <c r="AN30" s="121"/>
-      <c r="AO30" s="121"/>
-      <c r="AP30" s="88"/>
-      <c r="AQ30" s="112"/>
-      <c r="AR30" s="113"/>
-      <c r="AS30" s="88"/>
-      <c r="AT30" s="88"/>
-      <c r="AU30" s="113"/>
-      <c r="AV30" s="112"/>
-      <c r="AW30" s="113"/>
-      <c r="AX30" s="102"/>
-      <c r="AY30" s="102"/>
-      <c r="AZ30" s="102"/>
-      <c r="BA30" s="114"/>
-      <c r="BB30" s="113"/>
-      <c r="BC30" s="102"/>
-      <c r="BD30" s="102"/>
-      <c r="BE30" s="113"/>
-      <c r="BF30" s="113"/>
+      <c r="AH30" s="103"/>
+      <c r="AI30" s="88"/>
+      <c r="AJ30" s="152"/>
+      <c r="AK30" s="93"/>
+      <c r="AL30" s="93"/>
+      <c r="AM30" s="100"/>
+      <c r="AN30" s="100"/>
+      <c r="AO30" s="100"/>
+      <c r="AP30" s="83"/>
+      <c r="AQ30" s="94"/>
+      <c r="AR30" s="95"/>
+      <c r="AS30" s="83"/>
+      <c r="AT30" s="83"/>
+      <c r="AU30" s="95"/>
+      <c r="AV30" s="94"/>
+      <c r="AW30" s="95"/>
+      <c r="AX30" s="89"/>
+      <c r="AY30" s="89"/>
+      <c r="AZ30" s="89"/>
+      <c r="BA30" s="96"/>
+      <c r="BB30" s="95"/>
+      <c r="BC30" s="89"/>
+      <c r="BD30" s="89"/>
+      <c r="BE30" s="95"/>
+      <c r="BF30" s="95"/>
     </row>
     <row r="31" spans="1:58" ht="30" customHeight="1">
-      <c r="A31" s="88"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="95">
+      <c r="A31" s="83"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J31" s="161">
+      <c r="J31" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K31" s="94"/>
-      <c r="L31" s="94"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="119"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="120"/>
-      <c r="Q31" s="121"/>
-      <c r="R31" s="100"/>
-      <c r="S31" s="101"/>
-      <c r="T31" s="102"/>
-      <c r="U31" s="121"/>
-      <c r="V31" s="121"/>
-      <c r="W31" s="120"/>
-      <c r="X31" s="88"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="145"/>
+      <c r="M31" s="145"/>
+      <c r="N31" s="148"/>
+      <c r="O31" s="88"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="100"/>
+      <c r="R31" s="87"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="89"/>
+      <c r="U31" s="100"/>
+      <c r="V31" s="100"/>
+      <c r="W31" s="99"/>
+      <c r="X31" s="83"/>
       <c r="Y31" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z31" s="160">
+      <c r="Z31" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="159">
+      <c r="AA31" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB31" s="104"/>
-      <c r="AC31" s="103"/>
-      <c r="AD31" s="105"/>
-      <c r="AE31" s="125"/>
-      <c r="AF31" s="117"/>
-      <c r="AG31" s="123">
+      <c r="AB31" s="91"/>
+      <c r="AC31" s="90"/>
+      <c r="AD31" s="92"/>
+      <c r="AE31" s="153"/>
+      <c r="AF31" s="154"/>
+      <c r="AG31" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="126"/>
-      <c r="AI31" s="101"/>
-      <c r="AJ31" s="110"/>
-      <c r="AK31" s="111"/>
-      <c r="AL31" s="111"/>
-      <c r="AM31" s="121"/>
-      <c r="AN31" s="121"/>
-      <c r="AO31" s="121"/>
-      <c r="AP31" s="88"/>
-      <c r="AQ31" s="112"/>
-      <c r="AR31" s="113"/>
-      <c r="AS31" s="88"/>
-      <c r="AT31" s="88"/>
-      <c r="AU31" s="113"/>
-      <c r="AV31" s="112"/>
-      <c r="AW31" s="113"/>
-      <c r="AX31" s="102"/>
-      <c r="AY31" s="102"/>
-      <c r="AZ31" s="102"/>
-      <c r="BA31" s="114"/>
-      <c r="BB31" s="113"/>
-      <c r="BC31" s="102"/>
-      <c r="BD31" s="102"/>
-      <c r="BE31" s="113"/>
-      <c r="BF31" s="113"/>
+      <c r="AH31" s="103"/>
+      <c r="AI31" s="88"/>
+      <c r="AJ31" s="152"/>
+      <c r="AK31" s="93"/>
+      <c r="AL31" s="93"/>
+      <c r="AM31" s="100"/>
+      <c r="AN31" s="100"/>
+      <c r="AO31" s="100"/>
+      <c r="AP31" s="83"/>
+      <c r="AQ31" s="94"/>
+      <c r="AR31" s="95"/>
+      <c r="AS31" s="83"/>
+      <c r="AT31" s="83"/>
+      <c r="AU31" s="95"/>
+      <c r="AV31" s="94"/>
+      <c r="AW31" s="95"/>
+      <c r="AX31" s="89"/>
+      <c r="AY31" s="89"/>
+      <c r="AZ31" s="89"/>
+      <c r="BA31" s="96"/>
+      <c r="BB31" s="95"/>
+      <c r="BC31" s="89"/>
+      <c r="BD31" s="89"/>
+      <c r="BE31" s="95"/>
+      <c r="BF31" s="95"/>
     </row>
     <row r="32" spans="1:58" ht="30" customHeight="1">
-      <c r="A32" s="88"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="95">
+      <c r="A32" s="83"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="144"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="161">
+      <c r="J32" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K32" s="94"/>
-      <c r="L32" s="94"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="119"/>
-      <c r="O32" s="97"/>
-      <c r="P32" s="120"/>
-      <c r="Q32" s="121"/>
-      <c r="R32" s="100"/>
-      <c r="S32" s="101"/>
-      <c r="T32" s="102"/>
-      <c r="U32" s="121"/>
-      <c r="V32" s="121"/>
-      <c r="W32" s="120"/>
-      <c r="X32" s="88"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="145"/>
+      <c r="M32" s="145"/>
+      <c r="N32" s="148"/>
+      <c r="O32" s="88"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="100"/>
+      <c r="R32" s="87"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="89"/>
+      <c r="U32" s="100"/>
+      <c r="V32" s="100"/>
+      <c r="W32" s="99"/>
+      <c r="X32" s="83"/>
       <c r="Y32" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="160">
+      <c r="Z32" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="159">
+      <c r="AA32" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB32" s="104"/>
-      <c r="AC32" s="103"/>
-      <c r="AD32" s="105"/>
-      <c r="AE32" s="125"/>
-      <c r="AF32" s="117"/>
-      <c r="AG32" s="123">
+      <c r="AB32" s="91"/>
+      <c r="AC32" s="90"/>
+      <c r="AD32" s="92"/>
+      <c r="AE32" s="153"/>
+      <c r="AF32" s="154"/>
+      <c r="AG32" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="126"/>
-      <c r="AI32" s="101"/>
-      <c r="AJ32" s="110"/>
-      <c r="AK32" s="111"/>
-      <c r="AL32" s="111"/>
-      <c r="AM32" s="121"/>
-      <c r="AN32" s="121"/>
-      <c r="AO32" s="121"/>
-      <c r="AP32" s="88"/>
-      <c r="AQ32" s="112"/>
-      <c r="AR32" s="113"/>
-      <c r="AS32" s="88"/>
-      <c r="AT32" s="88"/>
-      <c r="AU32" s="113"/>
-      <c r="AV32" s="112"/>
-      <c r="AW32" s="113"/>
-      <c r="AX32" s="102"/>
-      <c r="AY32" s="102"/>
-      <c r="AZ32" s="88"/>
-      <c r="BA32" s="114"/>
-      <c r="BB32" s="113"/>
-      <c r="BC32" s="102"/>
-      <c r="BD32" s="102"/>
-      <c r="BE32" s="113"/>
-      <c r="BF32" s="113"/>
+      <c r="AH32" s="103"/>
+      <c r="AI32" s="88"/>
+      <c r="AJ32" s="152"/>
+      <c r="AK32" s="93"/>
+      <c r="AL32" s="93"/>
+      <c r="AM32" s="100"/>
+      <c r="AN32" s="100"/>
+      <c r="AO32" s="100"/>
+      <c r="AP32" s="83"/>
+      <c r="AQ32" s="94"/>
+      <c r="AR32" s="95"/>
+      <c r="AS32" s="83"/>
+      <c r="AT32" s="83"/>
+      <c r="AU32" s="95"/>
+      <c r="AV32" s="94"/>
+      <c r="AW32" s="95"/>
+      <c r="AX32" s="89"/>
+      <c r="AY32" s="89"/>
+      <c r="AZ32" s="83"/>
+      <c r="BA32" s="96"/>
+      <c r="BB32" s="95"/>
+      <c r="BC32" s="89"/>
+      <c r="BD32" s="89"/>
+      <c r="BE32" s="95"/>
+      <c r="BF32" s="95"/>
     </row>
     <row r="33" spans="1:58" ht="30" customHeight="1">
-      <c r="A33" s="88"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="116"/>
-      <c r="I33" s="95">
+      <c r="A33" s="83"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="149"/>
+      <c r="I33" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="161">
+      <c r="J33" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K33" s="116"/>
-      <c r="L33" s="116"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="119"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="120"/>
-      <c r="Q33" s="121"/>
-      <c r="R33" s="100"/>
-      <c r="S33" s="101"/>
-      <c r="T33" s="102"/>
-      <c r="U33" s="121"/>
-      <c r="V33" s="121"/>
-      <c r="W33" s="120"/>
-      <c r="X33" s="88"/>
+      <c r="K33" s="149"/>
+      <c r="L33" s="149"/>
+      <c r="M33" s="149"/>
+      <c r="N33" s="148"/>
+      <c r="O33" s="88"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="100"/>
+      <c r="R33" s="87"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="89"/>
+      <c r="U33" s="100"/>
+      <c r="V33" s="100"/>
+      <c r="W33" s="99"/>
+      <c r="X33" s="83"/>
       <c r="Y33" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="160">
+      <c r="Z33" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="159">
+      <c r="AA33" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB33" s="104"/>
-      <c r="AC33" s="103"/>
-      <c r="AD33" s="105"/>
-      <c r="AE33" s="125"/>
-      <c r="AF33" s="117"/>
-      <c r="AG33" s="123">
+      <c r="AB33" s="91"/>
+      <c r="AC33" s="90"/>
+      <c r="AD33" s="92"/>
+      <c r="AE33" s="153"/>
+      <c r="AF33" s="154"/>
+      <c r="AG33" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="126"/>
-      <c r="AI33" s="101"/>
-      <c r="AJ33" s="110"/>
-      <c r="AK33" s="111"/>
-      <c r="AL33" s="111"/>
-      <c r="AM33" s="121"/>
-      <c r="AN33" s="121"/>
-      <c r="AO33" s="121"/>
-      <c r="AP33" s="88"/>
-      <c r="AQ33" s="112"/>
-      <c r="AR33" s="113"/>
-      <c r="AS33" s="88"/>
-      <c r="AT33" s="88"/>
-      <c r="AU33" s="113"/>
-      <c r="AV33" s="112"/>
-      <c r="AW33" s="113"/>
-      <c r="AX33" s="102"/>
-      <c r="AY33" s="102"/>
-      <c r="AZ33" s="88"/>
-      <c r="BA33" s="114"/>
-      <c r="BB33" s="113"/>
-      <c r="BC33" s="102"/>
-      <c r="BD33" s="102"/>
-      <c r="BE33" s="113"/>
-      <c r="BF33" s="113"/>
+      <c r="AH33" s="103"/>
+      <c r="AI33" s="88"/>
+      <c r="AJ33" s="152"/>
+      <c r="AK33" s="93"/>
+      <c r="AL33" s="93"/>
+      <c r="AM33" s="100"/>
+      <c r="AN33" s="100"/>
+      <c r="AO33" s="100"/>
+      <c r="AP33" s="83"/>
+      <c r="AQ33" s="94"/>
+      <c r="AR33" s="95"/>
+      <c r="AS33" s="83"/>
+      <c r="AT33" s="83"/>
+      <c r="AU33" s="95"/>
+      <c r="AV33" s="94"/>
+      <c r="AW33" s="95"/>
+      <c r="AX33" s="89"/>
+      <c r="AY33" s="89"/>
+      <c r="AZ33" s="83"/>
+      <c r="BA33" s="96"/>
+      <c r="BB33" s="95"/>
+      <c r="BC33" s="89"/>
+      <c r="BD33" s="89"/>
+      <c r="BE33" s="95"/>
+      <c r="BF33" s="95"/>
     </row>
     <row r="34" spans="1:58" ht="30" customHeight="1">
-      <c r="A34" s="88"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="95">
+      <c r="A34" s="83"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="143"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="143"/>
+      <c r="H34" s="145"/>
+      <c r="I34" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J34" s="161">
+      <c r="J34" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="119"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="120"/>
-      <c r="Q34" s="121"/>
-      <c r="R34" s="100"/>
-      <c r="S34" s="101"/>
-      <c r="T34" s="102"/>
-      <c r="U34" s="121"/>
-      <c r="V34" s="121"/>
-      <c r="W34" s="120"/>
-      <c r="X34" s="88"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+      <c r="M34" s="145"/>
+      <c r="N34" s="148"/>
+      <c r="O34" s="88"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="100"/>
+      <c r="R34" s="87"/>
+      <c r="S34" s="88"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="100"/>
+      <c r="V34" s="100"/>
+      <c r="W34" s="99"/>
+      <c r="X34" s="83"/>
       <c r="Y34" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z34" s="160">
+      <c r="Z34" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="159">
+      <c r="AA34" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="104"/>
-      <c r="AC34" s="103"/>
-      <c r="AD34" s="105"/>
-      <c r="AE34" s="122"/>
-      <c r="AF34" s="107"/>
-      <c r="AG34" s="123">
+      <c r="AB34" s="91"/>
+      <c r="AC34" s="90"/>
+      <c r="AD34" s="92"/>
+      <c r="AE34" s="150"/>
+      <c r="AF34" s="151"/>
+      <c r="AG34" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="124"/>
-      <c r="AI34" s="101"/>
-      <c r="AJ34" s="110"/>
-      <c r="AK34" s="111"/>
-      <c r="AL34" s="111"/>
-      <c r="AM34" s="121"/>
-      <c r="AN34" s="121"/>
-      <c r="AO34" s="121"/>
-      <c r="AP34" s="88"/>
-      <c r="AQ34" s="112"/>
-      <c r="AR34" s="113"/>
-      <c r="AS34" s="88"/>
-      <c r="AT34" s="88"/>
-      <c r="AU34" s="113"/>
-      <c r="AV34" s="112"/>
-      <c r="AW34" s="113"/>
-      <c r="AX34" s="102"/>
-      <c r="AY34" s="102"/>
-      <c r="AZ34" s="102"/>
-      <c r="BA34" s="114"/>
-      <c r="BB34" s="113"/>
-      <c r="BC34" s="102"/>
-      <c r="BD34" s="102"/>
-      <c r="BE34" s="113"/>
-      <c r="BF34" s="113"/>
+      <c r="AH34" s="102"/>
+      <c r="AI34" s="88"/>
+      <c r="AJ34" s="152"/>
+      <c r="AK34" s="93"/>
+      <c r="AL34" s="93"/>
+      <c r="AM34" s="100"/>
+      <c r="AN34" s="100"/>
+      <c r="AO34" s="100"/>
+      <c r="AP34" s="83"/>
+      <c r="AQ34" s="94"/>
+      <c r="AR34" s="95"/>
+      <c r="AS34" s="83"/>
+      <c r="AT34" s="83"/>
+      <c r="AU34" s="95"/>
+      <c r="AV34" s="94"/>
+      <c r="AW34" s="95"/>
+      <c r="AX34" s="89"/>
+      <c r="AY34" s="89"/>
+      <c r="AZ34" s="89"/>
+      <c r="BA34" s="96"/>
+      <c r="BB34" s="95"/>
+      <c r="BC34" s="89"/>
+      <c r="BD34" s="89"/>
+      <c r="BE34" s="95"/>
+      <c r="BF34" s="95"/>
     </row>
     <row r="35" spans="1:58" ht="30" customHeight="1">
-      <c r="A35" s="88"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="95">
+      <c r="A35" s="83"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="143"/>
+      <c r="F35" s="144"/>
+      <c r="G35" s="143"/>
+      <c r="H35" s="145"/>
+      <c r="I35" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="161">
+      <c r="J35" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K35" s="94"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="94"/>
-      <c r="N35" s="119"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="120"/>
-      <c r="Q35" s="121"/>
-      <c r="R35" s="100"/>
-      <c r="S35" s="101"/>
-      <c r="T35" s="102"/>
-      <c r="U35" s="121"/>
-      <c r="V35" s="121"/>
-      <c r="W35" s="120"/>
-      <c r="X35" s="88"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="145"/>
+      <c r="M35" s="145"/>
+      <c r="N35" s="148"/>
+      <c r="O35" s="88"/>
+      <c r="P35" s="99"/>
+      <c r="Q35" s="100"/>
+      <c r="R35" s="87"/>
+      <c r="S35" s="88"/>
+      <c r="T35" s="89"/>
+      <c r="U35" s="100"/>
+      <c r="V35" s="100"/>
+      <c r="W35" s="99"/>
+      <c r="X35" s="83"/>
       <c r="Y35" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="160">
+      <c r="Z35" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA35" s="159">
+      <c r="AA35" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="104"/>
-      <c r="AC35" s="103"/>
-      <c r="AD35" s="105"/>
-      <c r="AE35" s="122"/>
-      <c r="AF35" s="107"/>
-      <c r="AG35" s="123">
+      <c r="AB35" s="91"/>
+      <c r="AC35" s="90"/>
+      <c r="AD35" s="92"/>
+      <c r="AE35" s="150"/>
+      <c r="AF35" s="151"/>
+      <c r="AG35" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="124"/>
-      <c r="AI35" s="101"/>
-      <c r="AJ35" s="110"/>
-      <c r="AK35" s="111"/>
-      <c r="AL35" s="111"/>
-      <c r="AM35" s="121"/>
-      <c r="AN35" s="121"/>
-      <c r="AO35" s="121"/>
-      <c r="AP35" s="88"/>
-      <c r="AQ35" s="112"/>
-      <c r="AR35" s="113"/>
-      <c r="AS35" s="88"/>
-      <c r="AT35" s="88"/>
-      <c r="AU35" s="113"/>
-      <c r="AV35" s="112"/>
-      <c r="AW35" s="113"/>
-      <c r="AX35" s="102"/>
-      <c r="AY35" s="102"/>
-      <c r="AZ35" s="102"/>
-      <c r="BA35" s="114"/>
-      <c r="BB35" s="113"/>
-      <c r="BC35" s="102"/>
-      <c r="BD35" s="102"/>
-      <c r="BE35" s="113"/>
-      <c r="BF35" s="113"/>
+      <c r="AH35" s="102"/>
+      <c r="AI35" s="88"/>
+      <c r="AJ35" s="152"/>
+      <c r="AK35" s="93"/>
+      <c r="AL35" s="93"/>
+      <c r="AM35" s="100"/>
+      <c r="AN35" s="100"/>
+      <c r="AO35" s="100"/>
+      <c r="AP35" s="83"/>
+      <c r="AQ35" s="94"/>
+      <c r="AR35" s="95"/>
+      <c r="AS35" s="83"/>
+      <c r="AT35" s="83"/>
+      <c r="AU35" s="95"/>
+      <c r="AV35" s="94"/>
+      <c r="AW35" s="95"/>
+      <c r="AX35" s="89"/>
+      <c r="AY35" s="89"/>
+      <c r="AZ35" s="89"/>
+      <c r="BA35" s="96"/>
+      <c r="BB35" s="95"/>
+      <c r="BC35" s="89"/>
+      <c r="BD35" s="89"/>
+      <c r="BE35" s="95"/>
+      <c r="BF35" s="95"/>
     </row>
     <row r="36" spans="1:58" ht="30" customHeight="1">
-      <c r="A36" s="88"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="88"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="95">
+      <c r="A36" s="83"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="143"/>
+      <c r="F36" s="144"/>
+      <c r="G36" s="143"/>
+      <c r="H36" s="145"/>
+      <c r="I36" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="161">
+      <c r="J36" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K36" s="94"/>
-      <c r="L36" s="94"/>
-      <c r="M36" s="94"/>
-      <c r="N36" s="119"/>
-      <c r="O36" s="97"/>
-      <c r="P36" s="120"/>
-      <c r="Q36" s="121"/>
-      <c r="R36" s="100"/>
-      <c r="S36" s="101"/>
-      <c r="T36" s="102"/>
-      <c r="U36" s="121"/>
-      <c r="V36" s="121"/>
-      <c r="W36" s="120"/>
-      <c r="X36" s="88"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+      <c r="M36" s="145"/>
+      <c r="N36" s="148"/>
+      <c r="O36" s="88"/>
+      <c r="P36" s="99"/>
+      <c r="Q36" s="100"/>
+      <c r="R36" s="87"/>
+      <c r="S36" s="88"/>
+      <c r="T36" s="89"/>
+      <c r="U36" s="100"/>
+      <c r="V36" s="100"/>
+      <c r="W36" s="99"/>
+      <c r="X36" s="83"/>
       <c r="Y36" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="160">
+      <c r="Z36" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="159">
+      <c r="AA36" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="104"/>
-      <c r="AC36" s="103"/>
-      <c r="AD36" s="105"/>
-      <c r="AE36" s="122"/>
-      <c r="AF36" s="107"/>
-      <c r="AG36" s="123">
+      <c r="AB36" s="91"/>
+      <c r="AC36" s="90"/>
+      <c r="AD36" s="92"/>
+      <c r="AE36" s="150"/>
+      <c r="AF36" s="151"/>
+      <c r="AG36" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="124"/>
-      <c r="AI36" s="101"/>
-      <c r="AJ36" s="110"/>
-      <c r="AK36" s="111"/>
-      <c r="AL36" s="111"/>
-      <c r="AM36" s="121"/>
-      <c r="AN36" s="121"/>
-      <c r="AO36" s="121"/>
-      <c r="AP36" s="88"/>
-      <c r="AQ36" s="112"/>
-      <c r="AR36" s="113"/>
-      <c r="AS36" s="88"/>
-      <c r="AT36" s="88"/>
-      <c r="AU36" s="113"/>
-      <c r="AV36" s="112"/>
-      <c r="AW36" s="113"/>
-      <c r="AX36" s="102"/>
-      <c r="AY36" s="102"/>
-      <c r="AZ36" s="102"/>
-      <c r="BA36" s="114"/>
-      <c r="BB36" s="113"/>
-      <c r="BC36" s="102"/>
-      <c r="BD36" s="102"/>
-      <c r="BE36" s="113"/>
-      <c r="BF36" s="113"/>
+      <c r="AH36" s="102"/>
+      <c r="AI36" s="88"/>
+      <c r="AJ36" s="152"/>
+      <c r="AK36" s="93"/>
+      <c r="AL36" s="93"/>
+      <c r="AM36" s="100"/>
+      <c r="AN36" s="100"/>
+      <c r="AO36" s="100"/>
+      <c r="AP36" s="83"/>
+      <c r="AQ36" s="94"/>
+      <c r="AR36" s="95"/>
+      <c r="AS36" s="83"/>
+      <c r="AT36" s="83"/>
+      <c r="AU36" s="95"/>
+      <c r="AV36" s="94"/>
+      <c r="AW36" s="95"/>
+      <c r="AX36" s="89"/>
+      <c r="AY36" s="89"/>
+      <c r="AZ36" s="89"/>
+      <c r="BA36" s="96"/>
+      <c r="BB36" s="95"/>
+      <c r="BC36" s="89"/>
+      <c r="BD36" s="89"/>
+      <c r="BE36" s="95"/>
+      <c r="BF36" s="95"/>
     </row>
     <row r="37" spans="1:58" ht="30" customHeight="1">
-      <c r="A37" s="88"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="95">
+      <c r="A37" s="83"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="143"/>
+      <c r="F37" s="144"/>
+      <c r="G37" s="143"/>
+      <c r="H37" s="145"/>
+      <c r="I37" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J37" s="161">
+      <c r="J37" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K37" s="94"/>
-      <c r="L37" s="94"/>
-      <c r="M37" s="94"/>
-      <c r="N37" s="119"/>
-      <c r="O37" s="97"/>
-      <c r="P37" s="120"/>
-      <c r="Q37" s="121"/>
-      <c r="R37" s="100"/>
-      <c r="S37" s="101"/>
-      <c r="T37" s="102"/>
-      <c r="U37" s="121"/>
-      <c r="V37" s="121"/>
-      <c r="W37" s="120"/>
-      <c r="X37" s="88"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+      <c r="M37" s="145"/>
+      <c r="N37" s="148"/>
+      <c r="O37" s="88"/>
+      <c r="P37" s="99"/>
+      <c r="Q37" s="100"/>
+      <c r="R37" s="87"/>
+      <c r="S37" s="88"/>
+      <c r="T37" s="89"/>
+      <c r="U37" s="100"/>
+      <c r="V37" s="100"/>
+      <c r="W37" s="99"/>
+      <c r="X37" s="83"/>
       <c r="Y37" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="160">
+      <c r="Z37" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="159">
+      <c r="AA37" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="104"/>
-      <c r="AC37" s="103"/>
-      <c r="AD37" s="105"/>
-      <c r="AE37" s="122"/>
-      <c r="AF37" s="107"/>
-      <c r="AG37" s="123">
+      <c r="AB37" s="91"/>
+      <c r="AC37" s="90"/>
+      <c r="AD37" s="92"/>
+      <c r="AE37" s="150"/>
+      <c r="AF37" s="151"/>
+      <c r="AG37" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="124"/>
-      <c r="AI37" s="101"/>
-      <c r="AJ37" s="110"/>
-      <c r="AK37" s="111"/>
-      <c r="AL37" s="111"/>
-      <c r="AM37" s="121"/>
-      <c r="AN37" s="121"/>
-      <c r="AO37" s="121"/>
-      <c r="AP37" s="88"/>
-      <c r="AQ37" s="112"/>
-      <c r="AR37" s="113"/>
-      <c r="AS37" s="88"/>
-      <c r="AT37" s="88"/>
-      <c r="AU37" s="113"/>
-      <c r="AV37" s="112"/>
-      <c r="AW37" s="113"/>
-      <c r="AX37" s="102"/>
-      <c r="AY37" s="102"/>
-      <c r="AZ37" s="102"/>
-      <c r="BA37" s="114"/>
-      <c r="BB37" s="113"/>
-      <c r="BC37" s="102"/>
-      <c r="BD37" s="102"/>
-      <c r="BE37" s="113"/>
-      <c r="BF37" s="113"/>
+      <c r="AH37" s="102"/>
+      <c r="AI37" s="88"/>
+      <c r="AJ37" s="152"/>
+      <c r="AK37" s="93"/>
+      <c r="AL37" s="93"/>
+      <c r="AM37" s="100"/>
+      <c r="AN37" s="100"/>
+      <c r="AO37" s="100"/>
+      <c r="AP37" s="83"/>
+      <c r="AQ37" s="94"/>
+      <c r="AR37" s="95"/>
+      <c r="AS37" s="83"/>
+      <c r="AT37" s="83"/>
+      <c r="AU37" s="95"/>
+      <c r="AV37" s="94"/>
+      <c r="AW37" s="95"/>
+      <c r="AX37" s="89"/>
+      <c r="AY37" s="89"/>
+      <c r="AZ37" s="89"/>
+      <c r="BA37" s="96"/>
+      <c r="BB37" s="95"/>
+      <c r="BC37" s="89"/>
+      <c r="BD37" s="89"/>
+      <c r="BE37" s="95"/>
+      <c r="BF37" s="95"/>
     </row>
     <row r="38" spans="1:58" ht="30" customHeight="1">
-      <c r="A38" s="88"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="92"/>
-      <c r="F38" s="93"/>
-      <c r="G38" s="88"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="95">
+      <c r="A38" s="83"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="86"/>
+      <c r="E38" s="143"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="143"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J38" s="161">
+      <c r="J38" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K38" s="94"/>
-      <c r="L38" s="94"/>
-      <c r="M38" s="94"/>
-      <c r="N38" s="119"/>
-      <c r="O38" s="97"/>
-      <c r="P38" s="120"/>
-      <c r="Q38" s="121"/>
-      <c r="R38" s="100"/>
-      <c r="S38" s="101"/>
-      <c r="T38" s="102"/>
-      <c r="U38" s="121"/>
-      <c r="V38" s="121"/>
-      <c r="W38" s="120"/>
-      <c r="X38" s="88"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="145"/>
+      <c r="N38" s="148"/>
+      <c r="O38" s="88"/>
+      <c r="P38" s="99"/>
+      <c r="Q38" s="100"/>
+      <c r="R38" s="87"/>
+      <c r="S38" s="88"/>
+      <c r="T38" s="89"/>
+      <c r="U38" s="100"/>
+      <c r="V38" s="100"/>
+      <c r="W38" s="99"/>
+      <c r="X38" s="83"/>
       <c r="Y38" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z38" s="160">
+      <c r="Z38" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA38" s="159">
+      <c r="AA38" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB38" s="104"/>
-      <c r="AC38" s="103"/>
-      <c r="AD38" s="105"/>
-      <c r="AE38" s="122"/>
-      <c r="AF38" s="107"/>
-      <c r="AG38" s="123">
+      <c r="AB38" s="91"/>
+      <c r="AC38" s="90"/>
+      <c r="AD38" s="92"/>
+      <c r="AE38" s="150"/>
+      <c r="AF38" s="151"/>
+      <c r="AG38" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="124"/>
-      <c r="AI38" s="101"/>
-      <c r="AJ38" s="110"/>
-      <c r="AK38" s="111"/>
-      <c r="AL38" s="111"/>
-      <c r="AM38" s="121"/>
-      <c r="AN38" s="121"/>
-      <c r="AO38" s="121"/>
-      <c r="AP38" s="88"/>
-      <c r="AQ38" s="112"/>
-      <c r="AR38" s="113"/>
-      <c r="AS38" s="88"/>
-      <c r="AT38" s="88"/>
-      <c r="AU38" s="113"/>
-      <c r="AV38" s="112"/>
-      <c r="AW38" s="113"/>
-      <c r="AX38" s="102"/>
-      <c r="AY38" s="102"/>
-      <c r="AZ38" s="102"/>
-      <c r="BA38" s="114"/>
-      <c r="BB38" s="113"/>
-      <c r="BC38" s="102"/>
-      <c r="BD38" s="102"/>
-      <c r="BE38" s="113"/>
-      <c r="BF38" s="113"/>
+      <c r="AH38" s="102"/>
+      <c r="AI38" s="88"/>
+      <c r="AJ38" s="152"/>
+      <c r="AK38" s="93"/>
+      <c r="AL38" s="93"/>
+      <c r="AM38" s="100"/>
+      <c r="AN38" s="100"/>
+      <c r="AO38" s="100"/>
+      <c r="AP38" s="83"/>
+      <c r="AQ38" s="94"/>
+      <c r="AR38" s="95"/>
+      <c r="AS38" s="83"/>
+      <c r="AT38" s="83"/>
+      <c r="AU38" s="95"/>
+      <c r="AV38" s="94"/>
+      <c r="AW38" s="95"/>
+      <c r="AX38" s="89"/>
+      <c r="AY38" s="89"/>
+      <c r="AZ38" s="89"/>
+      <c r="BA38" s="96"/>
+      <c r="BB38" s="95"/>
+      <c r="BC38" s="89"/>
+      <c r="BD38" s="89"/>
+      <c r="BE38" s="95"/>
+      <c r="BF38" s="95"/>
     </row>
     <row r="39" spans="1:58" ht="30" customHeight="1">
-      <c r="A39" s="88"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="95">
+      <c r="A39" s="83"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="144"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="145"/>
+      <c r="I39" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J39" s="161">
+      <c r="J39" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K39" s="94"/>
-      <c r="L39" s="94"/>
-      <c r="M39" s="94"/>
-      <c r="N39" s="119"/>
-      <c r="O39" s="97"/>
-      <c r="P39" s="120"/>
-      <c r="Q39" s="121"/>
-      <c r="R39" s="100"/>
-      <c r="S39" s="101"/>
-      <c r="T39" s="102"/>
-      <c r="U39" s="121"/>
-      <c r="V39" s="121"/>
-      <c r="W39" s="120"/>
-      <c r="X39" s="88"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="145"/>
+      <c r="N39" s="148"/>
+      <c r="O39" s="88"/>
+      <c r="P39" s="99"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="87"/>
+      <c r="S39" s="88"/>
+      <c r="T39" s="89"/>
+      <c r="U39" s="100"/>
+      <c r="V39" s="100"/>
+      <c r="W39" s="99"/>
+      <c r="X39" s="83"/>
       <c r="Y39" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z39" s="160">
+      <c r="Z39" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA39" s="159">
+      <c r="AA39" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB39" s="104"/>
-      <c r="AC39" s="103"/>
-      <c r="AD39" s="105"/>
-      <c r="AE39" s="122"/>
-      <c r="AF39" s="107"/>
-      <c r="AG39" s="123">
+      <c r="AB39" s="91"/>
+      <c r="AC39" s="90"/>
+      <c r="AD39" s="92"/>
+      <c r="AE39" s="150"/>
+      <c r="AF39" s="151"/>
+      <c r="AG39" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="124"/>
-      <c r="AI39" s="101"/>
-      <c r="AJ39" s="110"/>
-      <c r="AK39" s="111"/>
-      <c r="AL39" s="111"/>
-      <c r="AM39" s="121"/>
-      <c r="AN39" s="121"/>
-      <c r="AO39" s="121"/>
-      <c r="AP39" s="88"/>
-      <c r="AQ39" s="112"/>
-      <c r="AR39" s="113"/>
-      <c r="AS39" s="88"/>
-      <c r="AT39" s="88"/>
-      <c r="AU39" s="113"/>
-      <c r="AV39" s="112"/>
-      <c r="AW39" s="113"/>
-      <c r="AX39" s="102"/>
-      <c r="AY39" s="102"/>
-      <c r="AZ39" s="102"/>
-      <c r="BA39" s="114"/>
-      <c r="BB39" s="113"/>
-      <c r="BC39" s="102"/>
-      <c r="BD39" s="102"/>
-      <c r="BE39" s="113"/>
-      <c r="BF39" s="113"/>
+      <c r="AH39" s="102"/>
+      <c r="AI39" s="88"/>
+      <c r="AJ39" s="152"/>
+      <c r="AK39" s="93"/>
+      <c r="AL39" s="93"/>
+      <c r="AM39" s="100"/>
+      <c r="AN39" s="100"/>
+      <c r="AO39" s="100"/>
+      <c r="AP39" s="83"/>
+      <c r="AQ39" s="94"/>
+      <c r="AR39" s="95"/>
+      <c r="AS39" s="83"/>
+      <c r="AT39" s="83"/>
+      <c r="AU39" s="95"/>
+      <c r="AV39" s="94"/>
+      <c r="AW39" s="95"/>
+      <c r="AX39" s="89"/>
+      <c r="AY39" s="89"/>
+      <c r="AZ39" s="89"/>
+      <c r="BA39" s="96"/>
+      <c r="BB39" s="95"/>
+      <c r="BC39" s="89"/>
+      <c r="BD39" s="89"/>
+      <c r="BE39" s="95"/>
+      <c r="BF39" s="95"/>
     </row>
     <row r="40" spans="1:58" ht="30" customHeight="1">
-      <c r="A40" s="88"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="90"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="93"/>
-      <c r="G40" s="88"/>
-      <c r="H40" s="94"/>
-      <c r="I40" s="95">
+      <c r="A40" s="83"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="145"/>
+      <c r="I40" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J40" s="161">
+      <c r="J40" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K40" s="94"/>
-      <c r="L40" s="94"/>
-      <c r="M40" s="94"/>
-      <c r="N40" s="119"/>
-      <c r="O40" s="97"/>
-      <c r="P40" s="120"/>
-      <c r="Q40" s="121"/>
-      <c r="R40" s="100"/>
-      <c r="S40" s="101"/>
-      <c r="T40" s="102"/>
-      <c r="U40" s="121"/>
-      <c r="V40" s="121"/>
-      <c r="W40" s="120"/>
-      <c r="X40" s="88"/>
+      <c r="K40" s="145"/>
+      <c r="L40" s="145"/>
+      <c r="M40" s="145"/>
+      <c r="N40" s="148"/>
+      <c r="O40" s="88"/>
+      <c r="P40" s="99"/>
+      <c r="Q40" s="100"/>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
+      <c r="T40" s="89"/>
+      <c r="U40" s="100"/>
+      <c r="V40" s="100"/>
+      <c r="W40" s="99"/>
+      <c r="X40" s="83"/>
       <c r="Y40" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z40" s="160">
+      <c r="Z40" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA40" s="159">
+      <c r="AA40" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="104"/>
-      <c r="AC40" s="103"/>
-      <c r="AD40" s="105"/>
-      <c r="AE40" s="122"/>
-      <c r="AF40" s="107"/>
-      <c r="AG40" s="123">
+      <c r="AB40" s="91"/>
+      <c r="AC40" s="90"/>
+      <c r="AD40" s="92"/>
+      <c r="AE40" s="150"/>
+      <c r="AF40" s="151"/>
+      <c r="AG40" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="124"/>
-      <c r="AI40" s="101"/>
-      <c r="AJ40" s="110"/>
-      <c r="AK40" s="111"/>
-      <c r="AL40" s="111"/>
-      <c r="AM40" s="121"/>
-      <c r="AN40" s="121"/>
-      <c r="AO40" s="121"/>
-      <c r="AP40" s="88"/>
-      <c r="AQ40" s="112"/>
-      <c r="AR40" s="113"/>
-      <c r="AS40" s="88"/>
-      <c r="AT40" s="88"/>
-      <c r="AU40" s="113"/>
-      <c r="AV40" s="112"/>
-      <c r="AW40" s="113"/>
-      <c r="AX40" s="102"/>
-      <c r="AY40" s="102"/>
-      <c r="AZ40" s="102"/>
-      <c r="BA40" s="114"/>
-      <c r="BB40" s="113"/>
-      <c r="BC40" s="102"/>
-      <c r="BD40" s="102"/>
-      <c r="BE40" s="113"/>
-      <c r="BF40" s="113"/>
+      <c r="AH40" s="102"/>
+      <c r="AI40" s="88"/>
+      <c r="AJ40" s="152"/>
+      <c r="AK40" s="93"/>
+      <c r="AL40" s="93"/>
+      <c r="AM40" s="100"/>
+      <c r="AN40" s="100"/>
+      <c r="AO40" s="100"/>
+      <c r="AP40" s="83"/>
+      <c r="AQ40" s="94"/>
+      <c r="AR40" s="95"/>
+      <c r="AS40" s="83"/>
+      <c r="AT40" s="83"/>
+      <c r="AU40" s="95"/>
+      <c r="AV40" s="94"/>
+      <c r="AW40" s="95"/>
+      <c r="AX40" s="89"/>
+      <c r="AY40" s="89"/>
+      <c r="AZ40" s="89"/>
+      <c r="BA40" s="96"/>
+      <c r="BB40" s="95"/>
+      <c r="BC40" s="89"/>
+      <c r="BD40" s="89"/>
+      <c r="BE40" s="95"/>
+      <c r="BF40" s="95"/>
     </row>
     <row r="41" spans="1:58" ht="30" customHeight="1">
-      <c r="A41" s="88"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="88"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="95">
+      <c r="A41" s="83"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="143"/>
+      <c r="F41" s="144"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="145"/>
+      <c r="I41" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J41" s="161">
+      <c r="J41" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
-      <c r="N41" s="119"/>
-      <c r="O41" s="97"/>
-      <c r="P41" s="120"/>
-      <c r="Q41" s="121"/>
-      <c r="R41" s="100"/>
-      <c r="S41" s="101"/>
-      <c r="T41" s="102"/>
-      <c r="U41" s="121"/>
-      <c r="V41" s="121"/>
-      <c r="W41" s="120"/>
-      <c r="X41" s="88"/>
+      <c r="K41" s="145"/>
+      <c r="L41" s="145"/>
+      <c r="M41" s="145"/>
+      <c r="N41" s="148"/>
+      <c r="O41" s="88"/>
+      <c r="P41" s="99"/>
+      <c r="Q41" s="100"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="89"/>
+      <c r="U41" s="100"/>
+      <c r="V41" s="100"/>
+      <c r="W41" s="99"/>
+      <c r="X41" s="83"/>
       <c r="Y41" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z41" s="160">
+      <c r="Z41" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA41" s="159">
+      <c r="AA41" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB41" s="104"/>
-      <c r="AC41" s="103"/>
-      <c r="AD41" s="105"/>
-      <c r="AE41" s="122"/>
-      <c r="AF41" s="107"/>
-      <c r="AG41" s="123">
+      <c r="AB41" s="91"/>
+      <c r="AC41" s="90"/>
+      <c r="AD41" s="92"/>
+      <c r="AE41" s="150"/>
+      <c r="AF41" s="151"/>
+      <c r="AG41" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="124"/>
-      <c r="AI41" s="101"/>
-      <c r="AJ41" s="110"/>
-      <c r="AK41" s="111"/>
-      <c r="AL41" s="111"/>
-      <c r="AM41" s="121"/>
-      <c r="AN41" s="121"/>
-      <c r="AO41" s="121"/>
-      <c r="AP41" s="88"/>
-      <c r="AQ41" s="112"/>
-      <c r="AR41" s="113"/>
-      <c r="AS41" s="88"/>
-      <c r="AT41" s="88"/>
-      <c r="AU41" s="113"/>
-      <c r="AV41" s="112"/>
-      <c r="AW41" s="113"/>
-      <c r="AX41" s="102"/>
-      <c r="AY41" s="102"/>
-      <c r="AZ41" s="102"/>
-      <c r="BA41" s="114"/>
-      <c r="BB41" s="113"/>
-      <c r="BC41" s="102"/>
-      <c r="BD41" s="102"/>
-      <c r="BE41" s="113"/>
-      <c r="BF41" s="113"/>
+      <c r="AH41" s="102"/>
+      <c r="AI41" s="88"/>
+      <c r="AJ41" s="152"/>
+      <c r="AK41" s="93"/>
+      <c r="AL41" s="93"/>
+      <c r="AM41" s="100"/>
+      <c r="AN41" s="100"/>
+      <c r="AO41" s="100"/>
+      <c r="AP41" s="83"/>
+      <c r="AQ41" s="94"/>
+      <c r="AR41" s="95"/>
+      <c r="AS41" s="83"/>
+      <c r="AT41" s="83"/>
+      <c r="AU41" s="95"/>
+      <c r="AV41" s="94"/>
+      <c r="AW41" s="95"/>
+      <c r="AX41" s="89"/>
+      <c r="AY41" s="89"/>
+      <c r="AZ41" s="89"/>
+      <c r="BA41" s="96"/>
+      <c r="BB41" s="95"/>
+      <c r="BC41" s="89"/>
+      <c r="BD41" s="89"/>
+      <c r="BE41" s="95"/>
+      <c r="BF41" s="95"/>
     </row>
     <row r="42" spans="1:58" ht="30.75" customHeight="1">
-      <c r="A42" s="88"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="88"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="93"/>
-      <c r="G42" s="88"/>
-      <c r="H42" s="116"/>
-      <c r="I42" s="95">
+      <c r="A42" s="83"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="143"/>
+      <c r="F42" s="144"/>
+      <c r="G42" s="143"/>
+      <c r="H42" s="149"/>
+      <c r="I42" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J42" s="161">
+      <c r="J42" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K42" s="116"/>
-      <c r="L42" s="116"/>
-      <c r="M42" s="116"/>
-      <c r="N42" s="119"/>
-      <c r="O42" s="97"/>
-      <c r="P42" s="120"/>
-      <c r="Q42" s="121"/>
-      <c r="R42" s="100"/>
-      <c r="S42" s="101"/>
-      <c r="T42" s="102"/>
-      <c r="U42" s="121"/>
-      <c r="V42" s="121"/>
-      <c r="W42" s="120"/>
-      <c r="X42" s="88"/>
+      <c r="K42" s="149"/>
+      <c r="L42" s="149"/>
+      <c r="M42" s="149"/>
+      <c r="N42" s="148"/>
+      <c r="O42" s="88"/>
+      <c r="P42" s="99"/>
+      <c r="Q42" s="100"/>
+      <c r="R42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="100"/>
+      <c r="V42" s="100"/>
+      <c r="W42" s="99"/>
+      <c r="X42" s="83"/>
       <c r="Y42" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z42" s="160">
+      <c r="Z42" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="159">
+      <c r="AA42" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="104"/>
-      <c r="AC42" s="103"/>
-      <c r="AD42" s="105"/>
-      <c r="AE42" s="125"/>
-      <c r="AF42" s="117"/>
-      <c r="AG42" s="123">
+      <c r="AB42" s="91"/>
+      <c r="AC42" s="90"/>
+      <c r="AD42" s="92"/>
+      <c r="AE42" s="153"/>
+      <c r="AF42" s="154"/>
+      <c r="AG42" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH42" s="126"/>
-      <c r="AI42" s="101"/>
-      <c r="AJ42" s="110"/>
-      <c r="AK42" s="111"/>
-      <c r="AL42" s="111"/>
-      <c r="AM42" s="121"/>
-      <c r="AN42" s="121"/>
-      <c r="AO42" s="121"/>
-      <c r="AP42" s="88"/>
-      <c r="AQ42" s="112"/>
-      <c r="AR42" s="113"/>
-      <c r="AS42" s="88"/>
-      <c r="AT42" s="88"/>
-      <c r="AU42" s="113"/>
-      <c r="AV42" s="112"/>
-      <c r="AW42" s="113"/>
-      <c r="AX42" s="102"/>
-      <c r="AY42" s="102"/>
-      <c r="AZ42" s="102"/>
-      <c r="BA42" s="114"/>
-      <c r="BB42" s="113"/>
-      <c r="BC42" s="102"/>
-      <c r="BD42" s="102"/>
-      <c r="BE42" s="113"/>
-      <c r="BF42" s="113"/>
+      <c r="AH42" s="103"/>
+      <c r="AI42" s="88"/>
+      <c r="AJ42" s="152"/>
+      <c r="AK42" s="93"/>
+      <c r="AL42" s="93"/>
+      <c r="AM42" s="100"/>
+      <c r="AN42" s="100"/>
+      <c r="AO42" s="100"/>
+      <c r="AP42" s="83"/>
+      <c r="AQ42" s="94"/>
+      <c r="AR42" s="95"/>
+      <c r="AS42" s="83"/>
+      <c r="AT42" s="83"/>
+      <c r="AU42" s="95"/>
+      <c r="AV42" s="94"/>
+      <c r="AW42" s="95"/>
+      <c r="AX42" s="89"/>
+      <c r="AY42" s="89"/>
+      <c r="AZ42" s="89"/>
+      <c r="BA42" s="96"/>
+      <c r="BB42" s="95"/>
+      <c r="BC42" s="89"/>
+      <c r="BD42" s="89"/>
+      <c r="BE42" s="95"/>
+      <c r="BF42" s="95"/>
     </row>
     <row r="43" spans="1:58" ht="30" customHeight="1">
-      <c r="A43" s="88"/>
-      <c r="B43" s="89"/>
-      <c r="C43" s="88"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="92"/>
-      <c r="F43" s="93"/>
-      <c r="G43" s="88"/>
-      <c r="H43" s="94"/>
-      <c r="I43" s="95">
+      <c r="A43" s="83"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="143"/>
+      <c r="F43" s="144"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="145"/>
+      <c r="I43" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J43" s="161">
+      <c r="J43" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K43" s="94"/>
-      <c r="L43" s="94"/>
-      <c r="M43" s="94"/>
-      <c r="N43" s="119"/>
-      <c r="O43" s="97"/>
-      <c r="P43" s="120"/>
-      <c r="Q43" s="121"/>
-      <c r="R43" s="100"/>
-      <c r="S43" s="101"/>
-      <c r="T43" s="102"/>
-      <c r="U43" s="121"/>
-      <c r="V43" s="121"/>
-      <c r="W43" s="120"/>
-      <c r="X43" s="88"/>
+      <c r="K43" s="145"/>
+      <c r="L43" s="145"/>
+      <c r="M43" s="145"/>
+      <c r="N43" s="148"/>
+      <c r="O43" s="88"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="100"/>
+      <c r="R43" s="87"/>
+      <c r="S43" s="88"/>
+      <c r="T43" s="89"/>
+      <c r="U43" s="100"/>
+      <c r="V43" s="100"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="83"/>
       <c r="Y43" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z43" s="160">
+      <c r="Z43" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA43" s="159">
+      <c r="AA43" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB43" s="104"/>
-      <c r="AC43" s="103"/>
-      <c r="AD43" s="105"/>
-      <c r="AE43" s="125"/>
-      <c r="AF43" s="117"/>
-      <c r="AG43" s="123">
+      <c r="AB43" s="91"/>
+      <c r="AC43" s="90"/>
+      <c r="AD43" s="92"/>
+      <c r="AE43" s="153"/>
+      <c r="AF43" s="154"/>
+      <c r="AG43" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="126"/>
-      <c r="AI43" s="101"/>
-      <c r="AJ43" s="110"/>
-      <c r="AK43" s="111"/>
-      <c r="AL43" s="111"/>
-      <c r="AM43" s="121"/>
-      <c r="AN43" s="121"/>
-      <c r="AO43" s="121"/>
-      <c r="AP43" s="88"/>
-      <c r="AQ43" s="112"/>
-      <c r="AR43" s="113"/>
-      <c r="AS43" s="88"/>
-      <c r="AT43" s="88"/>
-      <c r="AU43" s="113"/>
-      <c r="AV43" s="112"/>
-      <c r="AW43" s="113"/>
-      <c r="AX43" s="102"/>
-      <c r="AY43" s="102"/>
-      <c r="AZ43" s="102"/>
-      <c r="BA43" s="114"/>
-      <c r="BB43" s="113"/>
-      <c r="BC43" s="102"/>
-      <c r="BD43" s="102"/>
-      <c r="BE43" s="113"/>
-      <c r="BF43" s="113"/>
+      <c r="AH43" s="103"/>
+      <c r="AI43" s="88"/>
+      <c r="AJ43" s="152"/>
+      <c r="AK43" s="93"/>
+      <c r="AL43" s="93"/>
+      <c r="AM43" s="100"/>
+      <c r="AN43" s="100"/>
+      <c r="AO43" s="100"/>
+      <c r="AP43" s="83"/>
+      <c r="AQ43" s="94"/>
+      <c r="AR43" s="95"/>
+      <c r="AS43" s="83"/>
+      <c r="AT43" s="83"/>
+      <c r="AU43" s="95"/>
+      <c r="AV43" s="94"/>
+      <c r="AW43" s="95"/>
+      <c r="AX43" s="89"/>
+      <c r="AY43" s="89"/>
+      <c r="AZ43" s="89"/>
+      <c r="BA43" s="96"/>
+      <c r="BB43" s="95"/>
+      <c r="BC43" s="89"/>
+      <c r="BD43" s="89"/>
+      <c r="BE43" s="95"/>
+      <c r="BF43" s="95"/>
     </row>
     <row r="44" spans="1:58" ht="30" customHeight="1">
-      <c r="A44" s="88"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="118"/>
-      <c r="E44" s="92"/>
-      <c r="F44" s="93"/>
-      <c r="G44" s="88"/>
-      <c r="H44" s="94"/>
-      <c r="I44" s="95">
+      <c r="A44" s="83"/>
+      <c r="B44" s="84"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="143"/>
+      <c r="F44" s="144"/>
+      <c r="G44" s="143"/>
+      <c r="H44" s="145"/>
+      <c r="I44" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J44" s="161">
+      <c r="J44" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K44" s="94"/>
-      <c r="L44" s="94"/>
-      <c r="M44" s="94"/>
-      <c r="N44" s="119"/>
-      <c r="O44" s="97"/>
-      <c r="P44" s="120"/>
-      <c r="Q44" s="121"/>
-      <c r="R44" s="100"/>
-      <c r="S44" s="101"/>
-      <c r="T44" s="102"/>
-      <c r="U44" s="121"/>
-      <c r="V44" s="121"/>
-      <c r="W44" s="120"/>
-      <c r="X44" s="88"/>
+      <c r="K44" s="145"/>
+      <c r="L44" s="145"/>
+      <c r="M44" s="145"/>
+      <c r="N44" s="148"/>
+      <c r="O44" s="88"/>
+      <c r="P44" s="99"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="87"/>
+      <c r="S44" s="88"/>
+      <c r="T44" s="89"/>
+      <c r="U44" s="100"/>
+      <c r="V44" s="100"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="83"/>
       <c r="Y44" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z44" s="160">
+      <c r="Z44" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA44" s="159">
+      <c r="AA44" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB44" s="104"/>
-      <c r="AC44" s="103"/>
-      <c r="AD44" s="105"/>
-      <c r="AE44" s="125"/>
-      <c r="AF44" s="117"/>
-      <c r="AG44" s="123">
+      <c r="AB44" s="91"/>
+      <c r="AC44" s="90"/>
+      <c r="AD44" s="92"/>
+      <c r="AE44" s="153"/>
+      <c r="AF44" s="154"/>
+      <c r="AG44" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH44" s="126"/>
-      <c r="AI44" s="101"/>
-      <c r="AJ44" s="110"/>
-      <c r="AK44" s="111"/>
-      <c r="AL44" s="111"/>
-      <c r="AM44" s="121"/>
-      <c r="AN44" s="121"/>
-      <c r="AO44" s="121"/>
-      <c r="AP44" s="88"/>
-      <c r="AQ44" s="112"/>
-      <c r="AR44" s="113"/>
-      <c r="AS44" s="88"/>
-      <c r="AT44" s="88"/>
-      <c r="AU44" s="113"/>
-      <c r="AV44" s="112"/>
-      <c r="AW44" s="113"/>
-      <c r="AX44" s="102"/>
-      <c r="AY44" s="102"/>
-      <c r="AZ44" s="88"/>
-      <c r="BA44" s="114"/>
-      <c r="BB44" s="113"/>
-      <c r="BC44" s="102"/>
-      <c r="BD44" s="102"/>
-      <c r="BE44" s="113"/>
-      <c r="BF44" s="113"/>
+      <c r="AH44" s="103"/>
+      <c r="AI44" s="88"/>
+      <c r="AJ44" s="152"/>
+      <c r="AK44" s="93"/>
+      <c r="AL44" s="93"/>
+      <c r="AM44" s="100"/>
+      <c r="AN44" s="100"/>
+      <c r="AO44" s="100"/>
+      <c r="AP44" s="83"/>
+      <c r="AQ44" s="94"/>
+      <c r="AR44" s="95"/>
+      <c r="AS44" s="83"/>
+      <c r="AT44" s="83"/>
+      <c r="AU44" s="95"/>
+      <c r="AV44" s="94"/>
+      <c r="AW44" s="95"/>
+      <c r="AX44" s="89"/>
+      <c r="AY44" s="89"/>
+      <c r="AZ44" s="83"/>
+      <c r="BA44" s="96"/>
+      <c r="BB44" s="95"/>
+      <c r="BC44" s="89"/>
+      <c r="BD44" s="89"/>
+      <c r="BE44" s="95"/>
+      <c r="BF44" s="95"/>
     </row>
     <row r="45" spans="1:58" ht="30" customHeight="1">
-      <c r="A45" s="88"/>
-      <c r="B45" s="89"/>
-      <c r="C45" s="88"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="92"/>
-      <c r="F45" s="93"/>
-      <c r="G45" s="88"/>
-      <c r="H45" s="116"/>
-      <c r="I45" s="95">
+      <c r="A45" s="83"/>
+      <c r="B45" s="84"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="98"/>
+      <c r="E45" s="143"/>
+      <c r="F45" s="144"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="149"/>
+      <c r="I45" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J45" s="161">
+      <c r="J45" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K45" s="116"/>
-      <c r="L45" s="116"/>
-      <c r="M45" s="116"/>
-      <c r="N45" s="119"/>
-      <c r="O45" s="97"/>
-      <c r="P45" s="120"/>
-      <c r="Q45" s="121"/>
-      <c r="R45" s="100"/>
-      <c r="S45" s="101"/>
-      <c r="T45" s="102"/>
-      <c r="U45" s="121"/>
-      <c r="V45" s="121"/>
-      <c r="W45" s="120"/>
-      <c r="X45" s="88"/>
+      <c r="K45" s="149"/>
+      <c r="L45" s="149"/>
+      <c r="M45" s="149"/>
+      <c r="N45" s="148"/>
+      <c r="O45" s="88"/>
+      <c r="P45" s="99"/>
+      <c r="Q45" s="100"/>
+      <c r="R45" s="87"/>
+      <c r="S45" s="88"/>
+      <c r="T45" s="89"/>
+      <c r="U45" s="100"/>
+      <c r="V45" s="100"/>
+      <c r="W45" s="99"/>
+      <c r="X45" s="83"/>
       <c r="Y45" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z45" s="160">
+      <c r="Z45" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA45" s="159">
+      <c r="AA45" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="104"/>
-      <c r="AC45" s="103"/>
-      <c r="AD45" s="105"/>
-      <c r="AE45" s="125"/>
-      <c r="AF45" s="117"/>
-      <c r="AG45" s="123">
+      <c r="AB45" s="91"/>
+      <c r="AC45" s="90"/>
+      <c r="AD45" s="92"/>
+      <c r="AE45" s="153"/>
+      <c r="AF45" s="154"/>
+      <c r="AG45" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="126"/>
-      <c r="AI45" s="101"/>
-      <c r="AJ45" s="110"/>
-      <c r="AK45" s="111"/>
-      <c r="AL45" s="111"/>
-      <c r="AM45" s="121"/>
-      <c r="AN45" s="121"/>
-      <c r="AO45" s="121"/>
-      <c r="AP45" s="88"/>
-      <c r="AQ45" s="112"/>
-      <c r="AR45" s="113"/>
-      <c r="AS45" s="88"/>
-      <c r="AT45" s="88"/>
-      <c r="AU45" s="113"/>
-      <c r="AV45" s="112"/>
-      <c r="AW45" s="113"/>
-      <c r="AX45" s="102"/>
-      <c r="AY45" s="102"/>
-      <c r="AZ45" s="88"/>
-      <c r="BA45" s="114"/>
-      <c r="BB45" s="113"/>
-      <c r="BC45" s="102"/>
-      <c r="BD45" s="102"/>
-      <c r="BE45" s="113"/>
-      <c r="BF45" s="113"/>
+      <c r="AH45" s="103"/>
+      <c r="AI45" s="88"/>
+      <c r="AJ45" s="152"/>
+      <c r="AK45" s="93"/>
+      <c r="AL45" s="93"/>
+      <c r="AM45" s="100"/>
+      <c r="AN45" s="100"/>
+      <c r="AO45" s="100"/>
+      <c r="AP45" s="83"/>
+      <c r="AQ45" s="94"/>
+      <c r="AR45" s="95"/>
+      <c r="AS45" s="83"/>
+      <c r="AT45" s="83"/>
+      <c r="AU45" s="95"/>
+      <c r="AV45" s="94"/>
+      <c r="AW45" s="95"/>
+      <c r="AX45" s="89"/>
+      <c r="AY45" s="89"/>
+      <c r="AZ45" s="83"/>
+      <c r="BA45" s="96"/>
+      <c r="BB45" s="95"/>
+      <c r="BC45" s="89"/>
+      <c r="BD45" s="89"/>
+      <c r="BE45" s="95"/>
+      <c r="BF45" s="95"/>
     </row>
     <row r="46" spans="1:58" ht="30" customHeight="1">
-      <c r="A46" s="88"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="92"/>
-      <c r="F46" s="93"/>
-      <c r="G46" s="88"/>
-      <c r="H46" s="94"/>
-      <c r="I46" s="95">
+      <c r="A46" s="83"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="86"/>
+      <c r="E46" s="143"/>
+      <c r="F46" s="144"/>
+      <c r="G46" s="143"/>
+      <c r="H46" s="145"/>
+      <c r="I46" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J46" s="161">
+      <c r="J46" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K46" s="94"/>
-      <c r="L46" s="94"/>
-      <c r="M46" s="94"/>
-      <c r="N46" s="119"/>
-      <c r="O46" s="97"/>
-      <c r="P46" s="120"/>
-      <c r="Q46" s="121"/>
-      <c r="R46" s="100"/>
-      <c r="S46" s="101"/>
-      <c r="T46" s="102"/>
-      <c r="U46" s="121"/>
-      <c r="V46" s="121"/>
-      <c r="W46" s="120"/>
-      <c r="X46" s="88"/>
+      <c r="K46" s="145"/>
+      <c r="L46" s="145"/>
+      <c r="M46" s="145"/>
+      <c r="N46" s="148"/>
+      <c r="O46" s="88"/>
+      <c r="P46" s="99"/>
+      <c r="Q46" s="100"/>
+      <c r="R46" s="87"/>
+      <c r="S46" s="88"/>
+      <c r="T46" s="89"/>
+      <c r="U46" s="100"/>
+      <c r="V46" s="100"/>
+      <c r="W46" s="99"/>
+      <c r="X46" s="83"/>
       <c r="Y46" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z46" s="160">
+      <c r="Z46" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="159">
+      <c r="AA46" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB46" s="104"/>
-      <c r="AC46" s="103"/>
-      <c r="AD46" s="105"/>
-      <c r="AE46" s="122"/>
-      <c r="AF46" s="107"/>
-      <c r="AG46" s="123">
+      <c r="AB46" s="91"/>
+      <c r="AC46" s="90"/>
+      <c r="AD46" s="92"/>
+      <c r="AE46" s="150"/>
+      <c r="AF46" s="151"/>
+      <c r="AG46" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH46" s="124"/>
-      <c r="AI46" s="101"/>
-      <c r="AJ46" s="110"/>
-      <c r="AK46" s="111"/>
-      <c r="AL46" s="111"/>
-      <c r="AM46" s="121"/>
-      <c r="AN46" s="121"/>
-      <c r="AO46" s="121"/>
-      <c r="AP46" s="88"/>
-      <c r="AQ46" s="112"/>
-      <c r="AR46" s="113"/>
-      <c r="AS46" s="88"/>
-      <c r="AT46" s="88"/>
-      <c r="AU46" s="113"/>
-      <c r="AV46" s="112"/>
-      <c r="AW46" s="113"/>
-      <c r="AX46" s="102"/>
-      <c r="AY46" s="102"/>
-      <c r="AZ46" s="102"/>
-      <c r="BA46" s="114"/>
-      <c r="BB46" s="113"/>
-      <c r="BC46" s="102"/>
-      <c r="BD46" s="102"/>
-      <c r="BE46" s="113"/>
-      <c r="BF46" s="113"/>
+      <c r="AH46" s="102"/>
+      <c r="AI46" s="88"/>
+      <c r="AJ46" s="152"/>
+      <c r="AK46" s="93"/>
+      <c r="AL46" s="93"/>
+      <c r="AM46" s="100"/>
+      <c r="AN46" s="100"/>
+      <c r="AO46" s="100"/>
+      <c r="AP46" s="83"/>
+      <c r="AQ46" s="94"/>
+      <c r="AR46" s="95"/>
+      <c r="AS46" s="83"/>
+      <c r="AT46" s="83"/>
+      <c r="AU46" s="95"/>
+      <c r="AV46" s="94"/>
+      <c r="AW46" s="95"/>
+      <c r="AX46" s="89"/>
+      <c r="AY46" s="89"/>
+      <c r="AZ46" s="89"/>
+      <c r="BA46" s="96"/>
+      <c r="BB46" s="95"/>
+      <c r="BC46" s="89"/>
+      <c r="BD46" s="89"/>
+      <c r="BE46" s="95"/>
+      <c r="BF46" s="95"/>
     </row>
     <row r="47" spans="1:58" ht="30" customHeight="1">
-      <c r="A47" s="88"/>
-      <c r="B47" s="89"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="92"/>
-      <c r="F47" s="93"/>
-      <c r="G47" s="88"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="95">
+      <c r="A47" s="83"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="86"/>
+      <c r="E47" s="143"/>
+      <c r="F47" s="144"/>
+      <c r="G47" s="143"/>
+      <c r="H47" s="145"/>
+      <c r="I47" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J47" s="161">
+      <c r="J47" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K47" s="94"/>
-      <c r="L47" s="94"/>
-      <c r="M47" s="94"/>
-      <c r="N47" s="119"/>
-      <c r="O47" s="97"/>
-      <c r="P47" s="120"/>
-      <c r="Q47" s="121"/>
-      <c r="R47" s="100"/>
-      <c r="S47" s="101"/>
-      <c r="T47" s="102"/>
-      <c r="U47" s="121"/>
-      <c r="V47" s="121"/>
-      <c r="W47" s="120"/>
-      <c r="X47" s="88"/>
+      <c r="K47" s="145"/>
+      <c r="L47" s="145"/>
+      <c r="M47" s="145"/>
+      <c r="N47" s="148"/>
+      <c r="O47" s="88"/>
+      <c r="P47" s="99"/>
+      <c r="Q47" s="100"/>
+      <c r="R47" s="87"/>
+      <c r="S47" s="88"/>
+      <c r="T47" s="89"/>
+      <c r="U47" s="100"/>
+      <c r="V47" s="100"/>
+      <c r="W47" s="99"/>
+      <c r="X47" s="83"/>
       <c r="Y47" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z47" s="160">
+      <c r="Z47" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="159">
+      <c r="AA47" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB47" s="104"/>
-      <c r="AC47" s="103"/>
-      <c r="AD47" s="105"/>
-      <c r="AE47" s="122"/>
-      <c r="AF47" s="107"/>
-      <c r="AG47" s="123">
+      <c r="AB47" s="91"/>
+      <c r="AC47" s="90"/>
+      <c r="AD47" s="92"/>
+      <c r="AE47" s="150"/>
+      <c r="AF47" s="151"/>
+      <c r="AG47" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH47" s="124"/>
-      <c r="AI47" s="101"/>
-      <c r="AJ47" s="110"/>
-      <c r="AK47" s="111"/>
-      <c r="AL47" s="111"/>
-      <c r="AM47" s="121"/>
-      <c r="AN47" s="121"/>
-      <c r="AO47" s="121"/>
-      <c r="AP47" s="88"/>
-      <c r="AQ47" s="112"/>
-      <c r="AR47" s="113"/>
-      <c r="AS47" s="88"/>
-      <c r="AT47" s="88"/>
-      <c r="AU47" s="113"/>
-      <c r="AV47" s="112"/>
-      <c r="AW47" s="113"/>
-      <c r="AX47" s="102"/>
-      <c r="AY47" s="102"/>
-      <c r="AZ47" s="102"/>
-      <c r="BA47" s="114"/>
-      <c r="BB47" s="113"/>
-      <c r="BC47" s="102"/>
-      <c r="BD47" s="102"/>
-      <c r="BE47" s="113"/>
-      <c r="BF47" s="113"/>
+      <c r="AH47" s="102"/>
+      <c r="AI47" s="88"/>
+      <c r="AJ47" s="152"/>
+      <c r="AK47" s="93"/>
+      <c r="AL47" s="93"/>
+      <c r="AM47" s="100"/>
+      <c r="AN47" s="100"/>
+      <c r="AO47" s="100"/>
+      <c r="AP47" s="83"/>
+      <c r="AQ47" s="94"/>
+      <c r="AR47" s="95"/>
+      <c r="AS47" s="83"/>
+      <c r="AT47" s="83"/>
+      <c r="AU47" s="95"/>
+      <c r="AV47" s="94"/>
+      <c r="AW47" s="95"/>
+      <c r="AX47" s="89"/>
+      <c r="AY47" s="89"/>
+      <c r="AZ47" s="89"/>
+      <c r="BA47" s="96"/>
+      <c r="BB47" s="95"/>
+      <c r="BC47" s="89"/>
+      <c r="BD47" s="89"/>
+      <c r="BE47" s="95"/>
+      <c r="BF47" s="95"/>
     </row>
     <row r="48" spans="1:58" ht="30" customHeight="1">
-      <c r="A48" s="88"/>
-      <c r="B48" s="89"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="91"/>
-      <c r="E48" s="92"/>
-      <c r="F48" s="93"/>
-      <c r="G48" s="88"/>
-      <c r="H48" s="94"/>
-      <c r="I48" s="95">
+      <c r="A48" s="83"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="143"/>
+      <c r="F48" s="144"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="145"/>
+      <c r="I48" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="161">
+      <c r="J48" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K48" s="94"/>
-      <c r="L48" s="94"/>
-      <c r="M48" s="94"/>
-      <c r="N48" s="119"/>
-      <c r="O48" s="97"/>
-      <c r="P48" s="120"/>
-      <c r="Q48" s="121"/>
-      <c r="R48" s="100"/>
-      <c r="S48" s="101"/>
-      <c r="T48" s="102"/>
-      <c r="U48" s="121"/>
-      <c r="V48" s="121"/>
-      <c r="W48" s="120"/>
-      <c r="X48" s="88"/>
+      <c r="K48" s="145"/>
+      <c r="L48" s="145"/>
+      <c r="M48" s="145"/>
+      <c r="N48" s="148"/>
+      <c r="O48" s="88"/>
+      <c r="P48" s="99"/>
+      <c r="Q48" s="100"/>
+      <c r="R48" s="87"/>
+      <c r="S48" s="88"/>
+      <c r="T48" s="89"/>
+      <c r="U48" s="100"/>
+      <c r="V48" s="100"/>
+      <c r="W48" s="99"/>
+      <c r="X48" s="83"/>
       <c r="Y48" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z48" s="160">
+      <c r="Z48" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA48" s="159">
+      <c r="AA48" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB48" s="104"/>
-      <c r="AC48" s="103"/>
-      <c r="AD48" s="105"/>
-      <c r="AE48" s="122"/>
-      <c r="AF48" s="107"/>
-      <c r="AG48" s="123">
+      <c r="AB48" s="91"/>
+      <c r="AC48" s="90"/>
+      <c r="AD48" s="92"/>
+      <c r="AE48" s="150"/>
+      <c r="AF48" s="151"/>
+      <c r="AG48" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH48" s="124"/>
-      <c r="AI48" s="101"/>
-      <c r="AJ48" s="110"/>
-      <c r="AK48" s="111"/>
-      <c r="AL48" s="111"/>
-      <c r="AM48" s="121"/>
-      <c r="AN48" s="121"/>
-      <c r="AO48" s="121"/>
-      <c r="AP48" s="88"/>
-      <c r="AQ48" s="112"/>
-      <c r="AR48" s="113"/>
-      <c r="AS48" s="88"/>
-      <c r="AT48" s="88"/>
-      <c r="AU48" s="113"/>
-      <c r="AV48" s="112"/>
-      <c r="AW48" s="113"/>
-      <c r="AX48" s="102"/>
-      <c r="AY48" s="102"/>
-      <c r="AZ48" s="102"/>
-      <c r="BA48" s="114"/>
-      <c r="BB48" s="113"/>
-      <c r="BC48" s="102"/>
-      <c r="BD48" s="102"/>
-      <c r="BE48" s="113"/>
-      <c r="BF48" s="113"/>
+      <c r="AH48" s="102"/>
+      <c r="AI48" s="88"/>
+      <c r="AJ48" s="152"/>
+      <c r="AK48" s="93"/>
+      <c r="AL48" s="93"/>
+      <c r="AM48" s="100"/>
+      <c r="AN48" s="100"/>
+      <c r="AO48" s="100"/>
+      <c r="AP48" s="83"/>
+      <c r="AQ48" s="94"/>
+      <c r="AR48" s="95"/>
+      <c r="AS48" s="83"/>
+      <c r="AT48" s="83"/>
+      <c r="AU48" s="95"/>
+      <c r="AV48" s="94"/>
+      <c r="AW48" s="95"/>
+      <c r="AX48" s="89"/>
+      <c r="AY48" s="89"/>
+      <c r="AZ48" s="89"/>
+      <c r="BA48" s="96"/>
+      <c r="BB48" s="95"/>
+      <c r="BC48" s="89"/>
+      <c r="BD48" s="89"/>
+      <c r="BE48" s="95"/>
+      <c r="BF48" s="95"/>
     </row>
     <row r="49" spans="1:58" ht="30" customHeight="1">
-      <c r="A49" s="88"/>
-      <c r="B49" s="89"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="91"/>
-      <c r="E49" s="92"/>
-      <c r="F49" s="93"/>
-      <c r="G49" s="88"/>
-      <c r="H49" s="94"/>
-      <c r="I49" s="95">
+      <c r="A49" s="83"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="85"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="144"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J49" s="161">
+      <c r="J49" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K49" s="94"/>
-      <c r="L49" s="94"/>
-      <c r="M49" s="94"/>
-      <c r="N49" s="119"/>
-      <c r="O49" s="97"/>
-      <c r="P49" s="120"/>
-      <c r="Q49" s="121"/>
-      <c r="R49" s="100"/>
-      <c r="S49" s="101"/>
-      <c r="T49" s="102"/>
-      <c r="U49" s="121"/>
-      <c r="V49" s="121"/>
-      <c r="W49" s="120"/>
-      <c r="X49" s="88"/>
+      <c r="K49" s="145"/>
+      <c r="L49" s="145"/>
+      <c r="M49" s="145"/>
+      <c r="N49" s="148"/>
+      <c r="O49" s="88"/>
+      <c r="P49" s="99"/>
+      <c r="Q49" s="100"/>
+      <c r="R49" s="87"/>
+      <c r="S49" s="88"/>
+      <c r="T49" s="89"/>
+      <c r="U49" s="100"/>
+      <c r="V49" s="100"/>
+      <c r="W49" s="99"/>
+      <c r="X49" s="83"/>
       <c r="Y49" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z49" s="160">
+      <c r="Z49" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="159">
+      <c r="AA49" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB49" s="104"/>
-      <c r="AC49" s="103"/>
-      <c r="AD49" s="105"/>
-      <c r="AE49" s="122"/>
-      <c r="AF49" s="107"/>
-      <c r="AG49" s="123">
+      <c r="AB49" s="91"/>
+      <c r="AC49" s="90"/>
+      <c r="AD49" s="92"/>
+      <c r="AE49" s="150"/>
+      <c r="AF49" s="151"/>
+      <c r="AG49" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="124"/>
-      <c r="AI49" s="101"/>
-      <c r="AJ49" s="110"/>
-      <c r="AK49" s="111"/>
-      <c r="AL49" s="111"/>
-      <c r="AM49" s="121"/>
-      <c r="AN49" s="121"/>
-      <c r="AO49" s="121"/>
-      <c r="AP49" s="88"/>
-      <c r="AQ49" s="112"/>
-      <c r="AR49" s="113"/>
-      <c r="AS49" s="88"/>
-      <c r="AT49" s="88"/>
-      <c r="AU49" s="113"/>
-      <c r="AV49" s="112"/>
-      <c r="AW49" s="113"/>
-      <c r="AX49" s="102"/>
-      <c r="AY49" s="102"/>
-      <c r="AZ49" s="102"/>
-      <c r="BA49" s="114"/>
-      <c r="BB49" s="113"/>
-      <c r="BC49" s="102"/>
-      <c r="BD49" s="102"/>
-      <c r="BE49" s="113"/>
-      <c r="BF49" s="113"/>
+      <c r="AH49" s="102"/>
+      <c r="AI49" s="88"/>
+      <c r="AJ49" s="152"/>
+      <c r="AK49" s="93"/>
+      <c r="AL49" s="93"/>
+      <c r="AM49" s="100"/>
+      <c r="AN49" s="100"/>
+      <c r="AO49" s="100"/>
+      <c r="AP49" s="83"/>
+      <c r="AQ49" s="94"/>
+      <c r="AR49" s="95"/>
+      <c r="AS49" s="83"/>
+      <c r="AT49" s="83"/>
+      <c r="AU49" s="95"/>
+      <c r="AV49" s="94"/>
+      <c r="AW49" s="95"/>
+      <c r="AX49" s="89"/>
+      <c r="AY49" s="89"/>
+      <c r="AZ49" s="89"/>
+      <c r="BA49" s="96"/>
+      <c r="BB49" s="95"/>
+      <c r="BC49" s="89"/>
+      <c r="BD49" s="89"/>
+      <c r="BE49" s="95"/>
+      <c r="BF49" s="95"/>
     </row>
     <row r="50" spans="1:58" ht="30" customHeight="1">
-      <c r="A50" s="88"/>
-      <c r="B50" s="89"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="91"/>
-      <c r="E50" s="92"/>
-      <c r="F50" s="93"/>
-      <c r="G50" s="88"/>
-      <c r="H50" s="94"/>
-      <c r="I50" s="95">
+      <c r="A50" s="83"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="85"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="143"/>
+      <c r="F50" s="144"/>
+      <c r="G50" s="143"/>
+      <c r="H50" s="145"/>
+      <c r="I50" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J50" s="161">
+      <c r="J50" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K50" s="94"/>
-      <c r="L50" s="94"/>
-      <c r="M50" s="94"/>
-      <c r="N50" s="119"/>
-      <c r="O50" s="97"/>
-      <c r="P50" s="120"/>
-      <c r="Q50" s="121"/>
-      <c r="R50" s="100"/>
-      <c r="S50" s="101"/>
-      <c r="T50" s="102"/>
-      <c r="U50" s="121"/>
-      <c r="V50" s="121"/>
-      <c r="W50" s="120"/>
-      <c r="X50" s="88"/>
+      <c r="K50" s="145"/>
+      <c r="L50" s="145"/>
+      <c r="M50" s="145"/>
+      <c r="N50" s="148"/>
+      <c r="O50" s="88"/>
+      <c r="P50" s="99"/>
+      <c r="Q50" s="100"/>
+      <c r="R50" s="87"/>
+      <c r="S50" s="88"/>
+      <c r="T50" s="89"/>
+      <c r="U50" s="100"/>
+      <c r="V50" s="100"/>
+      <c r="W50" s="99"/>
+      <c r="X50" s="83"/>
       <c r="Y50" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z50" s="160">
+      <c r="Z50" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA50" s="159">
+      <c r="AA50" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB50" s="104"/>
-      <c r="AC50" s="103"/>
-      <c r="AD50" s="105"/>
-      <c r="AE50" s="122"/>
-      <c r="AF50" s="107"/>
-      <c r="AG50" s="123">
+      <c r="AB50" s="91"/>
+      <c r="AC50" s="90"/>
+      <c r="AD50" s="92"/>
+      <c r="AE50" s="150"/>
+      <c r="AF50" s="151"/>
+      <c r="AG50" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="124"/>
-      <c r="AI50" s="101"/>
-      <c r="AJ50" s="110"/>
-      <c r="AK50" s="111"/>
-      <c r="AL50" s="111"/>
-      <c r="AM50" s="121"/>
-      <c r="AN50" s="121"/>
-      <c r="AO50" s="121"/>
-      <c r="AP50" s="88"/>
-      <c r="AQ50" s="112"/>
-      <c r="AR50" s="113"/>
-      <c r="AS50" s="88"/>
-      <c r="AT50" s="88"/>
-      <c r="AU50" s="113"/>
-      <c r="AV50" s="112"/>
-      <c r="AW50" s="113"/>
-      <c r="AX50" s="102"/>
-      <c r="AY50" s="102"/>
-      <c r="AZ50" s="102"/>
-      <c r="BA50" s="114"/>
-      <c r="BB50" s="113"/>
-      <c r="BC50" s="102"/>
-      <c r="BD50" s="102"/>
-      <c r="BE50" s="113"/>
-      <c r="BF50" s="113"/>
+      <c r="AH50" s="102"/>
+      <c r="AI50" s="88"/>
+      <c r="AJ50" s="152"/>
+      <c r="AK50" s="93"/>
+      <c r="AL50" s="93"/>
+      <c r="AM50" s="100"/>
+      <c r="AN50" s="100"/>
+      <c r="AO50" s="100"/>
+      <c r="AP50" s="83"/>
+      <c r="AQ50" s="94"/>
+      <c r="AR50" s="95"/>
+      <c r="AS50" s="83"/>
+      <c r="AT50" s="83"/>
+      <c r="AU50" s="95"/>
+      <c r="AV50" s="94"/>
+      <c r="AW50" s="95"/>
+      <c r="AX50" s="89"/>
+      <c r="AY50" s="89"/>
+      <c r="AZ50" s="89"/>
+      <c r="BA50" s="96"/>
+      <c r="BB50" s="95"/>
+      <c r="BC50" s="89"/>
+      <c r="BD50" s="89"/>
+      <c r="BE50" s="95"/>
+      <c r="BF50" s="95"/>
     </row>
     <row r="51" spans="1:58" ht="30" customHeight="1">
-      <c r="A51" s="88"/>
-      <c r="B51" s="89"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="91"/>
-      <c r="E51" s="92"/>
-      <c r="F51" s="93"/>
-      <c r="G51" s="88"/>
-      <c r="H51" s="94"/>
-      <c r="I51" s="95">
+      <c r="A51" s="83"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="85"/>
+      <c r="D51" s="86"/>
+      <c r="E51" s="143"/>
+      <c r="F51" s="144"/>
+      <c r="G51" s="143"/>
+      <c r="H51" s="145"/>
+      <c r="I51" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J51" s="161">
+      <c r="J51" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K51" s="94"/>
-      <c r="L51" s="94"/>
-      <c r="M51" s="94"/>
-      <c r="N51" s="119"/>
-      <c r="O51" s="97"/>
-      <c r="P51" s="120"/>
-      <c r="Q51" s="121"/>
-      <c r="R51" s="100"/>
-      <c r="S51" s="101"/>
-      <c r="T51" s="102"/>
-      <c r="U51" s="121"/>
-      <c r="V51" s="121"/>
-      <c r="W51" s="120"/>
-      <c r="X51" s="88"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="145"/>
+      <c r="N51" s="148"/>
+      <c r="O51" s="88"/>
+      <c r="P51" s="99"/>
+      <c r="Q51" s="100"/>
+      <c r="R51" s="87"/>
+      <c r="S51" s="88"/>
+      <c r="T51" s="89"/>
+      <c r="U51" s="100"/>
+      <c r="V51" s="100"/>
+      <c r="W51" s="99"/>
+      <c r="X51" s="83"/>
       <c r="Y51" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z51" s="160">
+      <c r="Z51" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="159">
+      <c r="AA51" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB51" s="104"/>
-      <c r="AC51" s="103"/>
-      <c r="AD51" s="105"/>
-      <c r="AE51" s="122"/>
-      <c r="AF51" s="107"/>
-      <c r="AG51" s="123">
+      <c r="AB51" s="91"/>
+      <c r="AC51" s="90"/>
+      <c r="AD51" s="92"/>
+      <c r="AE51" s="150"/>
+      <c r="AF51" s="151"/>
+      <c r="AG51" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH51" s="124"/>
-      <c r="AI51" s="101"/>
-      <c r="AJ51" s="110"/>
-      <c r="AK51" s="111"/>
-      <c r="AL51" s="111"/>
-      <c r="AM51" s="121"/>
-      <c r="AN51" s="121"/>
-      <c r="AO51" s="121"/>
-      <c r="AP51" s="88"/>
-      <c r="AQ51" s="112"/>
-      <c r="AR51" s="113"/>
-      <c r="AS51" s="88"/>
-      <c r="AT51" s="88"/>
-      <c r="AU51" s="113"/>
-      <c r="AV51" s="112"/>
-      <c r="AW51" s="113"/>
-      <c r="AX51" s="102"/>
-      <c r="AY51" s="102"/>
-      <c r="AZ51" s="102"/>
-      <c r="BA51" s="114"/>
-      <c r="BB51" s="113"/>
-      <c r="BC51" s="102"/>
-      <c r="BD51" s="102"/>
-      <c r="BE51" s="113"/>
-      <c r="BF51" s="113"/>
+      <c r="AH51" s="102"/>
+      <c r="AI51" s="88"/>
+      <c r="AJ51" s="152"/>
+      <c r="AK51" s="93"/>
+      <c r="AL51" s="93"/>
+      <c r="AM51" s="100"/>
+      <c r="AN51" s="100"/>
+      <c r="AO51" s="100"/>
+      <c r="AP51" s="83"/>
+      <c r="AQ51" s="94"/>
+      <c r="AR51" s="95"/>
+      <c r="AS51" s="83"/>
+      <c r="AT51" s="83"/>
+      <c r="AU51" s="95"/>
+      <c r="AV51" s="94"/>
+      <c r="AW51" s="95"/>
+      <c r="AX51" s="89"/>
+      <c r="AY51" s="89"/>
+      <c r="AZ51" s="89"/>
+      <c r="BA51" s="96"/>
+      <c r="BB51" s="95"/>
+      <c r="BC51" s="89"/>
+      <c r="BD51" s="89"/>
+      <c r="BE51" s="95"/>
+      <c r="BF51" s="95"/>
     </row>
     <row r="52" spans="1:58" ht="30" customHeight="1">
-      <c r="A52" s="88"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="92"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="88"/>
-      <c r="H52" s="94"/>
-      <c r="I52" s="95">
+      <c r="A52" s="83"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="86"/>
+      <c r="E52" s="143"/>
+      <c r="F52" s="144"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="145"/>
+      <c r="I52" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J52" s="161">
+      <c r="J52" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K52" s="94"/>
-      <c r="L52" s="94"/>
-      <c r="M52" s="94"/>
-      <c r="N52" s="119"/>
-      <c r="O52" s="97"/>
-      <c r="P52" s="120"/>
-      <c r="Q52" s="121"/>
-      <c r="R52" s="100"/>
-      <c r="S52" s="101"/>
-      <c r="T52" s="102"/>
-      <c r="U52" s="121"/>
-      <c r="V52" s="121"/>
-      <c r="W52" s="120"/>
-      <c r="X52" s="88"/>
+      <c r="K52" s="145"/>
+      <c r="L52" s="145"/>
+      <c r="M52" s="145"/>
+      <c r="N52" s="148"/>
+      <c r="O52" s="88"/>
+      <c r="P52" s="99"/>
+      <c r="Q52" s="100"/>
+      <c r="R52" s="87"/>
+      <c r="S52" s="88"/>
+      <c r="T52" s="89"/>
+      <c r="U52" s="100"/>
+      <c r="V52" s="100"/>
+      <c r="W52" s="99"/>
+      <c r="X52" s="83"/>
       <c r="Y52" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z52" s="160">
+      <c r="Z52" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA52" s="159">
+      <c r="AA52" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB52" s="104"/>
-      <c r="AC52" s="103"/>
-      <c r="AD52" s="105"/>
-      <c r="AE52" s="122"/>
-      <c r="AF52" s="107"/>
-      <c r="AG52" s="123">
+      <c r="AB52" s="91"/>
+      <c r="AC52" s="90"/>
+      <c r="AD52" s="92"/>
+      <c r="AE52" s="150"/>
+      <c r="AF52" s="151"/>
+      <c r="AG52" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH52" s="124"/>
-      <c r="AI52" s="101"/>
-      <c r="AJ52" s="110"/>
-      <c r="AK52" s="111"/>
-      <c r="AL52" s="111"/>
-      <c r="AM52" s="121"/>
-      <c r="AN52" s="121"/>
-      <c r="AO52" s="121"/>
-      <c r="AP52" s="88"/>
-      <c r="AQ52" s="112"/>
-      <c r="AR52" s="113"/>
-      <c r="AS52" s="88"/>
-      <c r="AT52" s="88"/>
-      <c r="AU52" s="113"/>
-      <c r="AV52" s="112"/>
-      <c r="AW52" s="113"/>
-      <c r="AX52" s="102"/>
-      <c r="AY52" s="102"/>
-      <c r="AZ52" s="102"/>
-      <c r="BA52" s="114"/>
-      <c r="BB52" s="113"/>
-      <c r="BC52" s="102"/>
-      <c r="BD52" s="102"/>
-      <c r="BE52" s="113"/>
-      <c r="BF52" s="113"/>
+      <c r="AH52" s="102"/>
+      <c r="AI52" s="88"/>
+      <c r="AJ52" s="152"/>
+      <c r="AK52" s="93"/>
+      <c r="AL52" s="93"/>
+      <c r="AM52" s="100"/>
+      <c r="AN52" s="100"/>
+      <c r="AO52" s="100"/>
+      <c r="AP52" s="83"/>
+      <c r="AQ52" s="94"/>
+      <c r="AR52" s="95"/>
+      <c r="AS52" s="83"/>
+      <c r="AT52" s="83"/>
+      <c r="AU52" s="95"/>
+      <c r="AV52" s="94"/>
+      <c r="AW52" s="95"/>
+      <c r="AX52" s="89"/>
+      <c r="AY52" s="89"/>
+      <c r="AZ52" s="89"/>
+      <c r="BA52" s="96"/>
+      <c r="BB52" s="95"/>
+      <c r="BC52" s="89"/>
+      <c r="BD52" s="89"/>
+      <c r="BE52" s="95"/>
+      <c r="BF52" s="95"/>
     </row>
     <row r="53" spans="1:58" ht="30" customHeight="1">
-      <c r="A53" s="88"/>
-      <c r="B53" s="89"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="91"/>
-      <c r="E53" s="92"/>
-      <c r="F53" s="93"/>
-      <c r="G53" s="88"/>
-      <c r="H53" s="94"/>
-      <c r="I53" s="95">
+      <c r="A53" s="83"/>
+      <c r="B53" s="84"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="143"/>
+      <c r="F53" s="144"/>
+      <c r="G53" s="143"/>
+      <c r="H53" s="145"/>
+      <c r="I53" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J53" s="161">
+      <c r="J53" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K53" s="94"/>
-      <c r="L53" s="94"/>
-      <c r="M53" s="94"/>
-      <c r="N53" s="119"/>
-      <c r="O53" s="97"/>
-      <c r="P53" s="120"/>
-      <c r="Q53" s="121"/>
-      <c r="R53" s="100"/>
-      <c r="S53" s="101"/>
-      <c r="T53" s="102"/>
-      <c r="U53" s="121"/>
-      <c r="V53" s="121"/>
-      <c r="W53" s="120"/>
-      <c r="X53" s="88"/>
+      <c r="K53" s="145"/>
+      <c r="L53" s="145"/>
+      <c r="M53" s="145"/>
+      <c r="N53" s="148"/>
+      <c r="O53" s="88"/>
+      <c r="P53" s="99"/>
+      <c r="Q53" s="100"/>
+      <c r="R53" s="87"/>
+      <c r="S53" s="88"/>
+      <c r="T53" s="89"/>
+      <c r="U53" s="100"/>
+      <c r="V53" s="100"/>
+      <c r="W53" s="99"/>
+      <c r="X53" s="83"/>
       <c r="Y53" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z53" s="160">
+      <c r="Z53" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA53" s="159">
+      <c r="AA53" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB53" s="104"/>
-      <c r="AC53" s="103"/>
-      <c r="AD53" s="105"/>
-      <c r="AE53" s="122"/>
-      <c r="AF53" s="107"/>
-      <c r="AG53" s="123">
+      <c r="AB53" s="91"/>
+      <c r="AC53" s="90"/>
+      <c r="AD53" s="92"/>
+      <c r="AE53" s="150"/>
+      <c r="AF53" s="151"/>
+      <c r="AG53" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="124"/>
-      <c r="AI53" s="101"/>
-      <c r="AJ53" s="110"/>
-      <c r="AK53" s="111"/>
-      <c r="AL53" s="111"/>
-      <c r="AM53" s="121"/>
-      <c r="AN53" s="121"/>
-      <c r="AO53" s="121"/>
-      <c r="AP53" s="88"/>
-      <c r="AQ53" s="112"/>
-      <c r="AR53" s="113"/>
-      <c r="AS53" s="88"/>
-      <c r="AT53" s="88"/>
-      <c r="AU53" s="113"/>
-      <c r="AV53" s="112"/>
-      <c r="AW53" s="113"/>
-      <c r="AX53" s="102"/>
-      <c r="AY53" s="102"/>
-      <c r="AZ53" s="102"/>
-      <c r="BA53" s="114"/>
-      <c r="BB53" s="113"/>
-      <c r="BC53" s="102"/>
-      <c r="BD53" s="102"/>
-      <c r="BE53" s="113"/>
-      <c r="BF53" s="113"/>
+      <c r="AH53" s="102"/>
+      <c r="AI53" s="88"/>
+      <c r="AJ53" s="152"/>
+      <c r="AK53" s="93"/>
+      <c r="AL53" s="93"/>
+      <c r="AM53" s="100"/>
+      <c r="AN53" s="100"/>
+      <c r="AO53" s="100"/>
+      <c r="AP53" s="83"/>
+      <c r="AQ53" s="94"/>
+      <c r="AR53" s="95"/>
+      <c r="AS53" s="83"/>
+      <c r="AT53" s="83"/>
+      <c r="AU53" s="95"/>
+      <c r="AV53" s="94"/>
+      <c r="AW53" s="95"/>
+      <c r="AX53" s="89"/>
+      <c r="AY53" s="89"/>
+      <c r="AZ53" s="89"/>
+      <c r="BA53" s="96"/>
+      <c r="BB53" s="95"/>
+      <c r="BC53" s="89"/>
+      <c r="BD53" s="89"/>
+      <c r="BE53" s="95"/>
+      <c r="BF53" s="95"/>
     </row>
     <row r="54" spans="1:58" ht="30.75" customHeight="1">
-      <c r="A54" s="88"/>
-      <c r="B54" s="89"/>
-      <c r="C54" s="88"/>
-      <c r="D54" s="115"/>
-      <c r="E54" s="92"/>
-      <c r="F54" s="93"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="116"/>
-      <c r="I54" s="95">
+      <c r="A54" s="83"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="83"/>
+      <c r="D54" s="97"/>
+      <c r="E54" s="143"/>
+      <c r="F54" s="144"/>
+      <c r="G54" s="143"/>
+      <c r="H54" s="149"/>
+      <c r="I54" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J54" s="161">
+      <c r="J54" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K54" s="116"/>
-      <c r="L54" s="116"/>
-      <c r="M54" s="116"/>
-      <c r="N54" s="96"/>
-      <c r="O54" s="97"/>
-      <c r="P54" s="98"/>
-      <c r="Q54" s="99"/>
-      <c r="R54" s="100"/>
-      <c r="S54" s="101"/>
-      <c r="T54" s="102"/>
-      <c r="U54" s="99"/>
-      <c r="V54" s="99"/>
-      <c r="W54" s="98"/>
-      <c r="X54" s="88"/>
+      <c r="K54" s="149"/>
+      <c r="L54" s="149"/>
+      <c r="M54" s="149"/>
+      <c r="N54" s="148"/>
+      <c r="O54" s="88"/>
+      <c r="P54" s="99"/>
+      <c r="Q54" s="100"/>
+      <c r="R54" s="87"/>
+      <c r="S54" s="88"/>
+      <c r="T54" s="89"/>
+      <c r="U54" s="100"/>
+      <c r="V54" s="100"/>
+      <c r="W54" s="99"/>
+      <c r="X54" s="83"/>
       <c r="Y54" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z54" s="160">
+      <c r="Z54" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="159">
+      <c r="AA54" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB54" s="104"/>
-      <c r="AC54" s="103"/>
-      <c r="AD54" s="105"/>
-      <c r="AE54" s="125"/>
-      <c r="AF54" s="117"/>
-      <c r="AG54" s="123">
+      <c r="AB54" s="91"/>
+      <c r="AC54" s="90"/>
+      <c r="AD54" s="92"/>
+      <c r="AE54" s="153"/>
+      <c r="AF54" s="154"/>
+      <c r="AG54" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="126"/>
-      <c r="AI54" s="101"/>
-      <c r="AJ54" s="110"/>
-      <c r="AK54" s="111"/>
-      <c r="AL54" s="111"/>
-      <c r="AM54" s="99"/>
-      <c r="AN54" s="99"/>
-      <c r="AO54" s="99"/>
-      <c r="AP54" s="88"/>
-      <c r="AQ54" s="112"/>
-      <c r="AR54" s="113"/>
-      <c r="AS54" s="88"/>
-      <c r="AT54" s="88"/>
-      <c r="AU54" s="113"/>
-      <c r="AV54" s="112"/>
-      <c r="AW54" s="113"/>
-      <c r="AX54" s="102"/>
-      <c r="AY54" s="102"/>
-      <c r="AZ54" s="102"/>
-      <c r="BA54" s="114"/>
-      <c r="BB54" s="113"/>
-      <c r="BC54" s="102"/>
-      <c r="BD54" s="102"/>
-      <c r="BE54" s="113"/>
-      <c r="BF54" s="113"/>
+      <c r="AH54" s="103"/>
+      <c r="AI54" s="88"/>
+      <c r="AJ54" s="152"/>
+      <c r="AK54" s="93"/>
+      <c r="AL54" s="93"/>
+      <c r="AM54" s="100"/>
+      <c r="AN54" s="100"/>
+      <c r="AO54" s="100"/>
+      <c r="AP54" s="83"/>
+      <c r="AQ54" s="94"/>
+      <c r="AR54" s="95"/>
+      <c r="AS54" s="83"/>
+      <c r="AT54" s="83"/>
+      <c r="AU54" s="95"/>
+      <c r="AV54" s="94"/>
+      <c r="AW54" s="95"/>
+      <c r="AX54" s="89"/>
+      <c r="AY54" s="89"/>
+      <c r="AZ54" s="89"/>
+      <c r="BA54" s="96"/>
+      <c r="BB54" s="95"/>
+      <c r="BC54" s="89"/>
+      <c r="BD54" s="89"/>
+      <c r="BE54" s="95"/>
+      <c r="BF54" s="95"/>
     </row>
     <row r="55" spans="1:58" ht="30" customHeight="1">
-      <c r="A55" s="88"/>
-      <c r="B55" s="89"/>
-      <c r="C55" s="88"/>
-      <c r="D55" s="91"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="93"/>
-      <c r="G55" s="88"/>
-      <c r="H55" s="94"/>
-      <c r="I55" s="95">
+      <c r="A55" s="83"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="143"/>
+      <c r="F55" s="144"/>
+      <c r="G55" s="143"/>
+      <c r="H55" s="145"/>
+      <c r="I55" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J55" s="161">
+      <c r="J55" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K55" s="94"/>
-      <c r="L55" s="94"/>
-      <c r="M55" s="94"/>
-      <c r="N55" s="96"/>
-      <c r="O55" s="97"/>
-      <c r="P55" s="98"/>
-      <c r="Q55" s="99"/>
-      <c r="R55" s="100"/>
-      <c r="S55" s="101"/>
-      <c r="T55" s="102"/>
-      <c r="U55" s="99"/>
-      <c r="V55" s="99"/>
-      <c r="W55" s="98"/>
-      <c r="X55" s="88"/>
+      <c r="K55" s="145"/>
+      <c r="L55" s="145"/>
+      <c r="M55" s="145"/>
+      <c r="N55" s="148"/>
+      <c r="O55" s="88"/>
+      <c r="P55" s="99"/>
+      <c r="Q55" s="100"/>
+      <c r="R55" s="87"/>
+      <c r="S55" s="88"/>
+      <c r="T55" s="89"/>
+      <c r="U55" s="100"/>
+      <c r="V55" s="100"/>
+      <c r="W55" s="99"/>
+      <c r="X55" s="83"/>
       <c r="Y55" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z55" s="160">
+      <c r="Z55" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA55" s="159">
+      <c r="AA55" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB55" s="104"/>
-      <c r="AC55" s="103"/>
-      <c r="AD55" s="105"/>
-      <c r="AE55" s="125"/>
-      <c r="AF55" s="117"/>
-      <c r="AG55" s="123">
+      <c r="AB55" s="91"/>
+      <c r="AC55" s="90"/>
+      <c r="AD55" s="92"/>
+      <c r="AE55" s="153"/>
+      <c r="AF55" s="154"/>
+      <c r="AG55" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH55" s="126"/>
-      <c r="AI55" s="101"/>
-      <c r="AJ55" s="110"/>
-      <c r="AK55" s="111"/>
-      <c r="AL55" s="111"/>
-      <c r="AM55" s="99"/>
-      <c r="AN55" s="99"/>
-      <c r="AO55" s="99"/>
-      <c r="AP55" s="88"/>
-      <c r="AQ55" s="112"/>
-      <c r="AR55" s="113"/>
-      <c r="AS55" s="88"/>
-      <c r="AT55" s="88"/>
-      <c r="AU55" s="113"/>
-      <c r="AV55" s="112"/>
-      <c r="AW55" s="113"/>
-      <c r="AX55" s="102"/>
-      <c r="AY55" s="102"/>
-      <c r="AZ55" s="102"/>
-      <c r="BA55" s="114"/>
-      <c r="BB55" s="113"/>
-      <c r="BC55" s="102"/>
-      <c r="BD55" s="102"/>
-      <c r="BE55" s="113"/>
-      <c r="BF55" s="113"/>
+      <c r="AH55" s="103"/>
+      <c r="AI55" s="88"/>
+      <c r="AJ55" s="152"/>
+      <c r="AK55" s="93"/>
+      <c r="AL55" s="93"/>
+      <c r="AM55" s="100"/>
+      <c r="AN55" s="100"/>
+      <c r="AO55" s="100"/>
+      <c r="AP55" s="83"/>
+      <c r="AQ55" s="94"/>
+      <c r="AR55" s="95"/>
+      <c r="AS55" s="83"/>
+      <c r="AT55" s="83"/>
+      <c r="AU55" s="95"/>
+      <c r="AV55" s="94"/>
+      <c r="AW55" s="95"/>
+      <c r="AX55" s="89"/>
+      <c r="AY55" s="89"/>
+      <c r="AZ55" s="89"/>
+      <c r="BA55" s="96"/>
+      <c r="BB55" s="95"/>
+      <c r="BC55" s="89"/>
+      <c r="BD55" s="89"/>
+      <c r="BE55" s="95"/>
+      <c r="BF55" s="95"/>
     </row>
     <row r="56" spans="1:58" ht="30" customHeight="1">
-      <c r="A56" s="88"/>
-      <c r="B56" s="89"/>
-      <c r="C56" s="88"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="92"/>
-      <c r="F56" s="93"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="94"/>
-      <c r="I56" s="95">
+      <c r="A56" s="83"/>
+      <c r="B56" s="84"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="143"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="143"/>
+      <c r="H56" s="145"/>
+      <c r="I56" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J56" s="161">
+      <c r="J56" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K56" s="94"/>
-      <c r="L56" s="94"/>
-      <c r="M56" s="94"/>
-      <c r="N56" s="96"/>
-      <c r="O56" s="97"/>
-      <c r="P56" s="98"/>
-      <c r="Q56" s="99"/>
-      <c r="R56" s="100"/>
-      <c r="S56" s="101"/>
-      <c r="T56" s="102"/>
-      <c r="U56" s="99"/>
-      <c r="V56" s="99"/>
-      <c r="W56" s="98"/>
-      <c r="X56" s="88"/>
+      <c r="K56" s="145"/>
+      <c r="L56" s="145"/>
+      <c r="M56" s="145"/>
+      <c r="N56" s="148"/>
+      <c r="O56" s="88"/>
+      <c r="P56" s="99"/>
+      <c r="Q56" s="100"/>
+      <c r="R56" s="87"/>
+      <c r="S56" s="88"/>
+      <c r="T56" s="89"/>
+      <c r="U56" s="100"/>
+      <c r="V56" s="100"/>
+      <c r="W56" s="99"/>
+      <c r="X56" s="83"/>
       <c r="Y56" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z56" s="160">
+      <c r="Z56" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA56" s="159">
+      <c r="AA56" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB56" s="104"/>
-      <c r="AC56" s="103"/>
-      <c r="AD56" s="105"/>
-      <c r="AE56" s="125"/>
-      <c r="AF56" s="117"/>
-      <c r="AG56" s="123">
+      <c r="AB56" s="91"/>
+      <c r="AC56" s="90"/>
+      <c r="AD56" s="92"/>
+      <c r="AE56" s="153"/>
+      <c r="AF56" s="154"/>
+      <c r="AG56" s="101">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH56" s="126"/>
-      <c r="AI56" s="101"/>
-      <c r="AJ56" s="110"/>
-      <c r="AK56" s="111"/>
-      <c r="AL56" s="111"/>
-      <c r="AM56" s="99"/>
-      <c r="AN56" s="99"/>
-      <c r="AO56" s="99"/>
-      <c r="AP56" s="88"/>
-      <c r="AQ56" s="112"/>
-      <c r="AR56" s="113"/>
-      <c r="AS56" s="88"/>
-      <c r="AT56" s="88"/>
-      <c r="AU56" s="113"/>
-      <c r="AV56" s="112"/>
-      <c r="AW56" s="113"/>
-      <c r="AX56" s="102"/>
-      <c r="AY56" s="102"/>
-      <c r="AZ56" s="88"/>
-      <c r="BA56" s="114"/>
-      <c r="BB56" s="113"/>
-      <c r="BC56" s="102"/>
-      <c r="BD56" s="102"/>
-      <c r="BE56" s="113"/>
-      <c r="BF56" s="113"/>
+      <c r="AH56" s="103"/>
+      <c r="AI56" s="88"/>
+      <c r="AJ56" s="152"/>
+      <c r="AK56" s="93"/>
+      <c r="AL56" s="93"/>
+      <c r="AM56" s="100"/>
+      <c r="AN56" s="100"/>
+      <c r="AO56" s="100"/>
+      <c r="AP56" s="83"/>
+      <c r="AQ56" s="94"/>
+      <c r="AR56" s="95"/>
+      <c r="AS56" s="83"/>
+      <c r="AT56" s="83"/>
+      <c r="AU56" s="95"/>
+      <c r="AV56" s="94"/>
+      <c r="AW56" s="95"/>
+      <c r="AX56" s="89"/>
+      <c r="AY56" s="89"/>
+      <c r="AZ56" s="83"/>
+      <c r="BA56" s="96"/>
+      <c r="BB56" s="95"/>
+      <c r="BC56" s="89"/>
+      <c r="BD56" s="89"/>
+      <c r="BE56" s="95"/>
+      <c r="BF56" s="95"/>
     </row>
     <row r="57" spans="1:58" ht="30" customHeight="1">
-      <c r="A57" s="88"/>
-      <c r="B57" s="89"/>
-      <c r="C57" s="88"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="92"/>
-      <c r="F57" s="93"/>
-      <c r="G57" s="88"/>
-      <c r="H57" s="116"/>
-      <c r="I57" s="95">
+      <c r="A57" s="83"/>
+      <c r="B57" s="84"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="98"/>
+      <c r="E57" s="143"/>
+      <c r="F57" s="144"/>
+      <c r="G57" s="143"/>
+      <c r="H57" s="149"/>
+      <c r="I57" s="146">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J57" s="161">
+      <c r="J57" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K57" s="116"/>
-      <c r="L57" s="116"/>
-      <c r="M57" s="116"/>
-      <c r="N57" s="96"/>
-      <c r="O57" s="97"/>
-      <c r="P57" s="98"/>
-      <c r="Q57" s="99"/>
-      <c r="R57" s="100"/>
-      <c r="S57" s="101"/>
-      <c r="T57" s="102"/>
-      <c r="U57" s="99"/>
-      <c r="V57" s="99"/>
-      <c r="W57" s="98"/>
-      <c r="X57" s="88"/>
+      <c r="K57" s="149"/>
+      <c r="L57" s="149"/>
+      <c r="M57" s="149"/>
+      <c r="N57" s="148"/>
+      <c r="O57" s="88"/>
+      <c r="P57" s="99"/>
+      <c r="Q57" s="100"/>
+      <c r="R57" s="87"/>
+      <c r="S57" s="88"/>
+      <c r="T57" s="89"/>
+      <c r="U57" s="100"/>
+      <c r="V57" s="100"/>
+      <c r="W57" s="99"/>
+      <c r="X57" s="83"/>
       <c r="Y57" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z57" s="160">
+      <c r="Z57" s="110">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA57" s="159">
+      <c r="AA57" s="109">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB57" s="104"/>
-      <c r="AC57" s="103"/>
-      <c r="AD57" s="105"/>
-      <c r="AE57" s="125"/>
-      <c r="AF57" s="117"/>
-      <c r="AG57" s="123">
+      <c r="AB57" s="91"/>
+      <c r="AC57" s="90"/>
+      <c r="AD57" s="92"/>
+      <c r="AE57" s="153"/>
+      <c r="AF57" s="154"/>
+      <c r="AG57" s="99">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH57" s="126"/>
-      <c r="AI57" s="101"/>
-      <c r="AJ57" s="110"/>
-      <c r="AK57" s="111"/>
-      <c r="AL57" s="111"/>
-      <c r="AM57" s="99"/>
-      <c r="AN57" s="99"/>
-      <c r="AO57" s="99"/>
-      <c r="AP57" s="88"/>
-      <c r="AQ57" s="112"/>
-      <c r="AR57" s="113"/>
-      <c r="AS57" s="88"/>
-      <c r="AT57" s="88"/>
-      <c r="AU57" s="113"/>
-      <c r="AV57" s="112"/>
-      <c r="AW57" s="113"/>
-      <c r="AX57" s="102"/>
-      <c r="AY57" s="102"/>
-      <c r="AZ57" s="88"/>
-      <c r="BA57" s="114"/>
-      <c r="BB57" s="113"/>
-      <c r="BC57" s="102"/>
-      <c r="BD57" s="102"/>
-      <c r="BE57" s="113"/>
-      <c r="BF57" s="113"/>
+      <c r="AH57" s="103"/>
+      <c r="AI57" s="88"/>
+      <c r="AJ57" s="152"/>
+      <c r="AK57" s="93"/>
+      <c r="AL57" s="93"/>
+      <c r="AM57" s="100"/>
+      <c r="AN57" s="100"/>
+      <c r="AO57" s="100"/>
+      <c r="AP57" s="83"/>
+      <c r="AQ57" s="94"/>
+      <c r="AR57" s="95"/>
+      <c r="AS57" s="83"/>
+      <c r="AT57" s="83"/>
+      <c r="AU57" s="95"/>
+      <c r="AV57" s="94"/>
+      <c r="AW57" s="95"/>
+      <c r="AX57" s="89"/>
+      <c r="AY57" s="89"/>
+      <c r="AZ57" s="83"/>
+      <c r="BA57" s="96"/>
+      <c r="BB57" s="95"/>
+      <c r="BC57" s="89"/>
+      <c r="BD57" s="89"/>
+      <c r="BE57" s="95"/>
+      <c r="BF57" s="95"/>
     </row>
     <row r="58" spans="1:58" ht="24.9" customHeight="1">
-      <c r="A58" s="135"/>
-      <c r="B58" s="136"/>
-      <c r="C58" s="136"/>
-      <c r="D58" s="136"/>
-      <c r="E58" s="136"/>
-      <c r="F58" s="136"/>
-      <c r="G58" s="136"/>
-      <c r="H58" s="136"/>
-      <c r="I58" s="136"/>
-      <c r="J58" s="136"/>
-      <c r="K58" s="136"/>
-      <c r="L58" s="136"/>
-      <c r="M58" s="136"/>
-      <c r="N58" s="136"/>
-      <c r="O58" s="136"/>
-      <c r="P58" s="136"/>
-      <c r="Q58" s="136"/>
-      <c r="R58" s="136"/>
-      <c r="S58" s="136"/>
-      <c r="T58" s="136"/>
-      <c r="U58" s="136"/>
-      <c r="V58" s="136"/>
-      <c r="W58" s="136"/>
-      <c r="X58" s="136"/>
-      <c r="Y58" s="136"/>
-      <c r="Z58" s="136"/>
-      <c r="AA58" s="136"/>
-      <c r="AB58" s="136"/>
-      <c r="AC58" s="136"/>
-      <c r="AD58" s="136"/>
-      <c r="AE58" s="136"/>
-      <c r="AF58" s="136"/>
-      <c r="AG58" s="136"/>
-      <c r="AH58" s="136"/>
-      <c r="AI58" s="136"/>
-      <c r="AJ58" s="136"/>
-      <c r="AK58" s="136"/>
-      <c r="AL58" s="136"/>
-      <c r="AM58" s="136"/>
-      <c r="AN58" s="136"/>
-      <c r="AO58" s="136"/>
-      <c r="AP58" s="137"/>
-      <c r="AQ58" s="112"/>
-      <c r="AR58" s="113">
+      <c r="A58" s="125"/>
+      <c r="B58" s="126"/>
+      <c r="C58" s="126"/>
+      <c r="D58" s="126"/>
+      <c r="E58" s="126"/>
+      <c r="F58" s="126"/>
+      <c r="G58" s="126"/>
+      <c r="H58" s="126"/>
+      <c r="I58" s="126"/>
+      <c r="J58" s="126"/>
+      <c r="K58" s="126"/>
+      <c r="L58" s="126"/>
+      <c r="M58" s="126"/>
+      <c r="N58" s="126"/>
+      <c r="O58" s="126"/>
+      <c r="P58" s="126"/>
+      <c r="Q58" s="126"/>
+      <c r="R58" s="126"/>
+      <c r="S58" s="126"/>
+      <c r="T58" s="126"/>
+      <c r="U58" s="126"/>
+      <c r="V58" s="126"/>
+      <c r="W58" s="126"/>
+      <c r="X58" s="126"/>
+      <c r="Y58" s="126"/>
+      <c r="Z58" s="126"/>
+      <c r="AA58" s="126"/>
+      <c r="AB58" s="126"/>
+      <c r="AC58" s="126"/>
+      <c r="AD58" s="126"/>
+      <c r="AE58" s="126"/>
+      <c r="AF58" s="126"/>
+      <c r="AG58" s="126"/>
+      <c r="AH58" s="126"/>
+      <c r="AI58" s="126"/>
+      <c r="AJ58" s="126"/>
+      <c r="AK58" s="126"/>
+      <c r="AL58" s="126"/>
+      <c r="AM58" s="126"/>
+      <c r="AN58" s="126"/>
+      <c r="AO58" s="126"/>
+      <c r="AP58" s="127"/>
+      <c r="AQ58" s="94"/>
+      <c r="AR58" s="95">
         <v>2</v>
       </c>
-      <c r="AS58" s="88">
+      <c r="AS58" s="83">
         <v>25</v>
       </c>
-      <c r="AT58" s="88">
+      <c r="AT58" s="83">
         <f t="shared" ref="AT58" si="6">AR58*AS58</f>
         <v>50</v>
       </c>
-      <c r="AU58" s="113"/>
-      <c r="AV58" s="112"/>
-      <c r="AW58" s="113"/>
-      <c r="AX58" s="102"/>
-      <c r="AY58" s="102"/>
-      <c r="AZ58" s="102"/>
-      <c r="BA58" s="114"/>
-      <c r="BB58" s="113"/>
-      <c r="BC58" s="102"/>
-      <c r="BD58" s="102"/>
-      <c r="BE58" s="113"/>
-      <c r="BF58" s="113"/>
+      <c r="AU58" s="95"/>
+      <c r="AV58" s="94"/>
+      <c r="AW58" s="95"/>
+      <c r="AX58" s="89"/>
+      <c r="AY58" s="89"/>
+      <c r="AZ58" s="89"/>
+      <c r="BA58" s="96"/>
+      <c r="BB58" s="95"/>
+      <c r="BC58" s="89"/>
+      <c r="BD58" s="89"/>
+      <c r="BE58" s="95"/>
+      <c r="BF58" s="95"/>
     </row>
     <row r="59" spans="1:58" ht="17.100000000000001" customHeight="1"/>
     <row r="60" spans="1:58" ht="17.100000000000001" customHeight="1"/>
@@ -24284,11 +24257,6 @@
     <row r="149" ht="17.100000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="AQ7:AZ7"/>
     <mergeCell ref="BA7:BD7"/>
     <mergeCell ref="BE7:BF7"/>
@@ -24301,6 +24269,11 @@
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AA7:AD7"/>
     <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="X9 X50:X57">
@@ -24423,34 +24396,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="M2" s="157" t="s">
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="M2" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
       <c r="S2" s="22"/>
       <c r="T2" s="22"/>
-      <c r="V2" s="158" t="s">
+      <c r="V2" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="158"/>
-      <c r="X2" s="158"/>
-      <c r="Y2" s="158"/>
-      <c r="Z2" s="158"/>
+      <c r="W2" s="142"/>
+      <c r="X2" s="142"/>
+      <c r="Y2" s="142"/>
+      <c r="Z2" s="142"/>
     </row>
     <row r="3" spans="2:27" ht="48.6">
       <c r="B3" s="23" t="s">
@@ -25312,12 +25285,12 @@
       <c r="T17" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="V17" s="158" t="s">
+      <c r="V17" s="142" t="s">
         <v>82</v>
       </c>
-      <c r="W17" s="158"/>
-      <c r="X17" s="158"/>
-      <c r="Y17" s="158"/>
+      <c r="W17" s="142"/>
+      <c r="X17" s="142"/>
+      <c r="Y17" s="142"/>
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="26" t="s">

--- a/backend/product_database/選機表-.xlsx
+++ b/backend/product_database/選機表-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2792EBAD-A26E-4A1C-9D9F-234F7722D413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388C8031-65AF-4F0D-8946-01ECCC136215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B12BA144-AC3D-4CE9-9615-9201C80CE143}"/>
   </bookViews>
@@ -22,8 +22,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">選機!$A$8:$BF$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">選機!$A$1:$BF$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">選機!$A$8:$BG$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">選機!$A$1:$BG$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">選機!$1:$8</definedName>
     <definedName name="VRV能力">[1]不要刪!$B$2:$B$13</definedName>
     <definedName name="VRV機型" localSheetId="0">[2]不要刪!$A$2:$A$14</definedName>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="740">
   <si>
     <t>空調系統設計</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3288,11 +3288,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>人員密度
-(人/㎡)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>風量規劃基準
 (</t>
@@ -3436,6 +3431,26 @@
   <si>
     <t>每坪建議
 負荷值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>人員密度
+(㎡/人)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PM2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>濾網</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -4169,9 +4184,6 @@
     <xf numFmtId="189" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4220,26 +4232,41 @@
     <xf numFmtId="184" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="191" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4261,6 +4288,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4304,6 +4334,24 @@
     <xf numFmtId="178" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="186" fontId="21" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="21" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4316,41 +4364,8 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="191" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -19600,7 +19615,7 @@
   <sheetPr codeName="工作表5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BF149"/>
+  <dimension ref="A1:BG149"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -19637,27 +19652,27 @@
     <col min="37" max="37" width="19.44140625" style="14" customWidth="1"/>
     <col min="38" max="38" width="20.6640625" style="14" customWidth="1"/>
     <col min="39" max="40" width="10.6640625" style="14" customWidth="1"/>
-    <col min="41" max="41" width="15.6640625" style="14" customWidth="1"/>
-    <col min="42" max="42" width="14.6640625" style="17" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="10.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="6.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="10.44140625" style="14" hidden="1" customWidth="1"/>
-    <col min="46" max="46" width="10.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="13.88671875" style="14" hidden="1" customWidth="1"/>
-    <col min="48" max="48" width="16.109375" style="14" hidden="1" customWidth="1"/>
-    <col min="49" max="49" width="4.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="50" max="50" width="10.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="51" max="52" width="15.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="12.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="10.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="15.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="10.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="4.6640625" style="14" hidden="1" customWidth="1"/>
-    <col min="59" max="16384" width="9" style="1"/>
+    <col min="41" max="41" width="15.21875" style="14" customWidth="1"/>
+    <col min="42" max="42" width="14.6640625" style="17" customWidth="1"/>
+    <col min="43" max="43" width="10.6640625" style="14" customWidth="1"/>
+    <col min="44" max="44" width="6.6640625" style="14" customWidth="1"/>
+    <col min="45" max="45" width="10.44140625" style="14" customWidth="1"/>
+    <col min="46" max="46" width="10.6640625" style="14" customWidth="1"/>
+    <col min="47" max="47" width="13.88671875" style="14" customWidth="1"/>
+    <col min="48" max="48" width="16.109375" style="14" customWidth="1"/>
+    <col min="49" max="49" width="6.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.6640625" style="14" customWidth="1"/>
+    <col min="51" max="53" width="15.6640625" style="14" customWidth="1"/>
+    <col min="54" max="54" width="12.6640625" style="14" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="4.6640625" style="14" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="10.6640625" style="14" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="15.6640625" style="14" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="10.6640625" style="14" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="4.6640625" style="14" hidden="1" customWidth="1"/>
+    <col min="60" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="21" customHeight="1">
+    <row r="1" spans="1:59" ht="21" customHeight="1">
       <c r="F1" s="4"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -19710,8 +19725,9 @@
       <c r="BD1" s="7"/>
       <c r="BE1" s="7"/>
       <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
     </row>
-    <row r="2" spans="1:58" ht="21" customHeight="1">
+    <row r="2" spans="1:59" ht="21" customHeight="1">
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -19764,8 +19780,9 @@
       <c r="BD2" s="7"/>
       <c r="BE2" s="7"/>
       <c r="BF2" s="7"/>
+      <c r="BG2" s="7"/>
     </row>
-    <row r="3" spans="1:58" ht="21" customHeight="1">
+    <row r="3" spans="1:59" ht="21" customHeight="1">
       <c r="A3" s="54" t="s">
         <v>0</v>
       </c>
@@ -19826,8 +19843,9 @@
       <c r="BD3" s="54"/>
       <c r="BE3" s="54"/>
       <c r="BF3" s="54"/>
+      <c r="BG3" s="54"/>
     </row>
-    <row r="4" spans="1:58" ht="21" customHeight="1">
+    <row r="4" spans="1:59" ht="21" customHeight="1">
       <c r="A4" s="55" t="s">
         <v>1</v>
       </c>
@@ -19888,10 +19906,11 @@
       <c r="BD4" s="55"/>
       <c r="BE4" s="55"/>
       <c r="BF4" s="55"/>
+      <c r="BG4" s="55"/>
     </row>
-    <row r="5" spans="1:58" ht="21" customHeight="1">
+    <row r="5" spans="1:59" ht="21" customHeight="1">
       <c r="A5" s="56" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B5" s="57"/>
       <c r="C5" s="58"/>
@@ -19950,17 +19969,18 @@
       <c r="BD5" s="19"/>
       <c r="BE5" s="19"/>
       <c r="BF5" s="19"/>
+      <c r="BG5" s="19"/>
     </row>
-    <row r="6" spans="1:58" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="111" t="s">
-        <v>736</v>
-      </c>
-      <c r="B6" s="112"/>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="112"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
+    <row r="6" spans="1:59" s="2" customFormat="1" ht="21" customHeight="1">
+      <c r="A6" s="144" t="s">
+        <v>735</v>
+      </c>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
       <c r="H6" s="60"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -20012,121 +20032,123 @@
       <c r="BD6" s="10"/>
       <c r="BE6" s="10"/>
       <c r="BF6" s="10"/>
+      <c r="BG6" s="10"/>
     </row>
-    <row r="7" spans="1:58" ht="39.75" customHeight="1">
-      <c r="A7" s="113" t="s">
+    <row r="7" spans="1:59" ht="39.75" customHeight="1">
+      <c r="A7" s="146" t="s">
         <v>691</v>
       </c>
-      <c r="B7" s="115" t="s">
+      <c r="B7" s="147" t="s">
         <v>692</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="149" t="s">
         <v>693</v>
       </c>
-      <c r="D7" s="114" t="s">
+      <c r="D7" s="129" t="s">
         <v>694</v>
       </c>
-      <c r="E7" s="105" t="s">
+      <c r="E7" s="104" t="s">
         <v>695</v>
       </c>
-      <c r="F7" s="106" t="s">
+      <c r="F7" s="105" t="s">
         <v>696</v>
       </c>
-      <c r="G7" s="106" t="s">
+      <c r="G7" s="105" t="s">
         <v>697</v>
       </c>
-      <c r="H7" s="137" t="s">
-        <v>738</v>
-      </c>
-      <c r="I7" s="138"/>
-      <c r="J7" s="138"/>
-      <c r="K7" s="138"/>
-      <c r="L7" s="130" t="s">
+      <c r="H7" s="142" t="s">
+        <v>737</v>
+      </c>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="135" t="s">
         <v>698</v>
       </c>
-      <c r="M7" s="130"/>
-      <c r="N7" s="131" t="s">
+      <c r="M7" s="135"/>
+      <c r="N7" s="136" t="s">
         <v>699</v>
       </c>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="132"/>
-      <c r="S7" s="132"/>
-      <c r="T7" s="132"/>
-      <c r="U7" s="132"/>
-      <c r="V7" s="133"/>
-      <c r="W7" s="134" t="s">
+      <c r="O7" s="137"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="137"/>
+      <c r="U7" s="137"/>
+      <c r="V7" s="138"/>
+      <c r="W7" s="139" t="s">
         <v>700</v>
       </c>
-      <c r="X7" s="133"/>
-      <c r="Y7" s="135" t="s">
+      <c r="X7" s="138"/>
+      <c r="Y7" s="140" t="s">
         <v>701</v>
       </c>
-      <c r="Z7" s="108" t="s">
+      <c r="Z7" s="107" t="s">
         <v>702</v>
       </c>
-      <c r="AA7" s="134" t="s">
+      <c r="AA7" s="139" t="s">
         <v>703</v>
       </c>
-      <c r="AB7" s="132"/>
-      <c r="AC7" s="132"/>
-      <c r="AD7" s="133"/>
-      <c r="AE7" s="124" t="s">
+      <c r="AB7" s="137"/>
+      <c r="AC7" s="137"/>
+      <c r="AD7" s="138"/>
+      <c r="AE7" s="128" t="s">
         <v>704</v>
       </c>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="114"/>
-      <c r="AH7" s="114"/>
-      <c r="AI7" s="114"/>
-      <c r="AJ7" s="114"/>
-      <c r="AK7" s="114"/>
-      <c r="AL7" s="114"/>
-      <c r="AM7" s="114"/>
-      <c r="AN7" s="114"/>
-      <c r="AO7" s="114"/>
-      <c r="AP7" s="128" t="s">
+      <c r="AF7" s="128"/>
+      <c r="AG7" s="129"/>
+      <c r="AH7" s="129"/>
+      <c r="AI7" s="129"/>
+      <c r="AJ7" s="129"/>
+      <c r="AK7" s="129"/>
+      <c r="AL7" s="129"/>
+      <c r="AM7" s="129"/>
+      <c r="AN7" s="129"/>
+      <c r="AO7" s="129"/>
+      <c r="AP7" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="AQ7" s="118" t="s">
+      <c r="AQ7" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="AR7" s="119"/>
-      <c r="AS7" s="119"/>
-      <c r="AT7" s="119"/>
-      <c r="AU7" s="119"/>
-      <c r="AV7" s="119"/>
-      <c r="AW7" s="119"/>
-      <c r="AX7" s="119"/>
-      <c r="AY7" s="119"/>
-      <c r="AZ7" s="120"/>
-      <c r="BA7" s="121" t="s">
+      <c r="AR7" s="123"/>
+      <c r="AS7" s="123"/>
+      <c r="AT7" s="123"/>
+      <c r="AU7" s="123"/>
+      <c r="AV7" s="123"/>
+      <c r="AW7" s="123"/>
+      <c r="AX7" s="123"/>
+      <c r="AY7" s="123"/>
+      <c r="AZ7" s="123"/>
+      <c r="BA7" s="124"/>
+      <c r="BB7" s="125" t="s">
         <v>705</v>
       </c>
-      <c r="BB7" s="122"/>
-      <c r="BC7" s="122"/>
-      <c r="BD7" s="123"/>
-      <c r="BE7" s="121" t="s">
+      <c r="BC7" s="126"/>
+      <c r="BD7" s="126"/>
+      <c r="BE7" s="127"/>
+      <c r="BF7" s="125" t="s">
         <v>706</v>
       </c>
-      <c r="BF7" s="123"/>
+      <c r="BG7" s="127"/>
     </row>
-    <row r="8" spans="1:58" ht="51.75" customHeight="1">
-      <c r="A8" s="114"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="105" t="s">
+    <row r="8" spans="1:59" ht="51.75" customHeight="1">
+      <c r="A8" s="129"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="104" t="s">
         <v>707</v>
       </c>
-      <c r="F8" s="106" t="s">
+      <c r="F8" s="105" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="64" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="65" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I8" s="65" t="s">
         <v>719</v>
@@ -20164,7 +20186,7 @@
       <c r="T8" s="66" t="s">
         <v>716</v>
       </c>
-      <c r="U8" s="107" t="s">
+      <c r="U8" s="106" t="s">
         <v>717</v>
       </c>
       <c r="V8" s="68" t="s">
@@ -20176,7 +20198,7 @@
       <c r="X8" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="Y8" s="136"/>
+      <c r="Y8" s="141"/>
       <c r="Z8" s="69" t="s">
         <v>9</v>
       </c>
@@ -20186,10 +20208,10 @@
       <c r="AB8" s="70" t="s">
         <v>708</v>
       </c>
-      <c r="AC8" s="105" t="s">
+      <c r="AC8" s="104" t="s">
         <v>710</v>
       </c>
-      <c r="AD8" s="105" t="s">
+      <c r="AD8" s="104" t="s">
         <v>720</v>
       </c>
       <c r="AE8" s="71" t="s">
@@ -20198,54 +20220,54 @@
       <c r="AF8" s="71" t="s">
         <v>721</v>
       </c>
-      <c r="AG8" s="104" t="s">
+      <c r="AG8" s="103" t="s">
         <v>712</v>
       </c>
-      <c r="AH8" s="104" t="s">
+      <c r="AH8" s="103" t="s">
         <v>713</v>
       </c>
-      <c r="AI8" s="108" t="s">
+      <c r="AI8" s="107" t="s">
         <v>722</v>
       </c>
       <c r="AJ8" s="72" t="s">
         <v>723</v>
       </c>
-      <c r="AK8" s="104" t="s">
+      <c r="AK8" s="103" t="s">
         <v>724</v>
       </c>
       <c r="AL8" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="AM8" s="107" t="s">
+      <c r="AM8" s="106" t="s">
         <v>725</v>
       </c>
       <c r="AN8" s="68" t="s">
         <v>726</v>
       </c>
-      <c r="AO8" s="104" t="s">
+      <c r="AO8" s="103" t="s">
         <v>718</v>
       </c>
-      <c r="AP8" s="129"/>
+      <c r="AP8" s="134"/>
       <c r="AQ8" s="74" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="AR8" s="74" t="s">
         <v>10</v>
       </c>
       <c r="AS8" s="74" t="s">
+        <v>727</v>
+      </c>
+      <c r="AT8" s="75" t="s">
         <v>728</v>
       </c>
-      <c r="AT8" s="75" t="s">
+      <c r="AU8" s="75" t="s">
         <v>729</v>
-      </c>
-      <c r="AU8" s="75" t="s">
-        <v>730</v>
       </c>
       <c r="AV8" s="76" t="s">
         <v>11</v>
       </c>
       <c r="AW8" s="77" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AX8" s="75" t="s">
         <v>716</v>
@@ -20256,3920 +20278,3966 @@
       <c r="AZ8" s="79" t="s">
         <v>718</v>
       </c>
-      <c r="BA8" s="80" t="s">
+      <c r="BA8" s="79" t="s">
+        <v>739</v>
+      </c>
+      <c r="BB8" s="80" t="s">
+        <v>731</v>
+      </c>
+      <c r="BC8" s="81" t="s">
         <v>732</v>
       </c>
-      <c r="BB8" s="81" t="s">
+      <c r="BD8" s="82" t="s">
+        <v>716</v>
+      </c>
+      <c r="BE8" s="80" t="s">
+        <v>715</v>
+      </c>
+      <c r="BF8" s="80" t="s">
+        <v>731</v>
+      </c>
+      <c r="BG8" s="81" t="s">
         <v>733</v>
       </c>
-      <c r="BC8" s="82" t="s">
-        <v>716</v>
-      </c>
-      <c r="BD8" s="80" t="s">
-        <v>715</v>
-      </c>
-      <c r="BE8" s="80" t="s">
-        <v>732</v>
-      </c>
-      <c r="BF8" s="81" t="s">
-        <v>734</v>
-      </c>
     </row>
-    <row r="9" spans="1:58" ht="30" customHeight="1">
+    <row r="9" spans="1:59" ht="30" customHeight="1">
       <c r="A9" s="83"/>
       <c r="B9" s="84"/>
       <c r="C9" s="85"/>
       <c r="D9" s="86"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="143"/>
-      <c r="H9" s="145"/>
-      <c r="I9" s="146">
+      <c r="E9" s="110"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="113">
         <f>H9*0.3025</f>
         <v>0</v>
       </c>
-      <c r="J9" s="147">
+      <c r="J9" s="114">
         <f>H9/0.86*0.3025</f>
         <v>0</v>
       </c>
-      <c r="K9" s="145"/>
-      <c r="L9" s="145"/>
-      <c r="M9" s="145"/>
-      <c r="N9" s="148"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="115"/>
       <c r="O9" s="88"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="100"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="99"/>
       <c r="R9" s="87"/>
       <c r="S9" s="88"/>
       <c r="T9" s="89"/>
-      <c r="U9" s="100"/>
-      <c r="V9" s="100"/>
-      <c r="W9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="98"/>
       <c r="X9" s="83"/>
       <c r="Y9" s="53">
         <f>R9*O9</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="110">
+      <c r="Z9" s="109">
         <f>O9*T9</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="109">
+      <c r="AA9" s="108">
         <f>AB9*0.3025</f>
         <v>0</v>
       </c>
       <c r="AB9" s="91"/>
       <c r="AC9" s="90"/>
       <c r="AD9" s="92"/>
-      <c r="AE9" s="150"/>
-      <c r="AF9" s="151"/>
-      <c r="AG9" s="101">
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="118"/>
+      <c r="AG9" s="100">
         <f>AH9*860</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="102"/>
+      <c r="AH9" s="101"/>
       <c r="AI9" s="88"/>
-      <c r="AJ9" s="152"/>
+      <c r="AJ9" s="119"/>
       <c r="AK9" s="93"/>
       <c r="AL9" s="93"/>
-      <c r="AM9" s="100"/>
-      <c r="AN9" s="100"/>
-      <c r="AO9" s="100"/>
+      <c r="AM9" s="99"/>
+      <c r="AN9" s="99"/>
+      <c r="AO9" s="99"/>
       <c r="AP9" s="83"/>
-      <c r="AQ9" s="94"/>
-      <c r="AR9" s="95"/>
-      <c r="AS9" s="83"/>
-      <c r="AT9" s="83"/>
-      <c r="AU9" s="95"/>
-      <c r="AV9" s="94"/>
-      <c r="AW9" s="95"/>
+      <c r="AQ9" s="154"/>
+      <c r="AR9" s="110"/>
+      <c r="AS9" s="110"/>
+      <c r="AT9" s="110"/>
+      <c r="AU9" s="110"/>
+      <c r="AV9" s="154"/>
+      <c r="AW9" s="110"/>
       <c r="AX9" s="89"/>
       <c r="AY9" s="89"/>
       <c r="AZ9" s="89"/>
-      <c r="BA9" s="96"/>
+      <c r="BA9" s="89"/>
       <c r="BB9" s="95"/>
-      <c r="BC9" s="89"/>
+      <c r="BC9" s="94"/>
       <c r="BD9" s="89"/>
-      <c r="BE9" s="95"/>
-      <c r="BF9" s="95"/>
+      <c r="BE9" s="89"/>
+      <c r="BF9" s="94"/>
+      <c r="BG9" s="94"/>
     </row>
-    <row r="10" spans="1:58" ht="30" customHeight="1">
+    <row r="10" spans="1:59" ht="30" customHeight="1">
       <c r="A10" s="83"/>
       <c r="B10" s="84"/>
       <c r="C10" s="85"/>
       <c r="D10" s="86"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="146">
+      <c r="E10" s="110"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="113">
         <f t="shared" ref="I10:I57" si="0">H10*0.3025</f>
         <v>0</v>
       </c>
-      <c r="J10" s="147">
+      <c r="J10" s="114">
         <f t="shared" ref="J10:J57" si="1">H10/0.86*0.3025</f>
         <v>0</v>
       </c>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="145"/>
-      <c r="N10" s="148"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="115"/>
       <c r="O10" s="88"/>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="100"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="99"/>
       <c r="R10" s="87"/>
       <c r="S10" s="88"/>
       <c r="T10" s="89"/>
-      <c r="U10" s="100"/>
-      <c r="V10" s="100"/>
-      <c r="W10" s="99"/>
+      <c r="U10" s="99"/>
+      <c r="V10" s="99"/>
+      <c r="W10" s="98"/>
       <c r="X10" s="83"/>
       <c r="Y10" s="53">
         <f t="shared" ref="Y10:Y57" si="2">R10*O10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="110">
+      <c r="Z10" s="109">
         <f t="shared" ref="Z10:Z57" si="3">O10*T10</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="109">
+      <c r="AA10" s="108">
         <f t="shared" ref="AA10:AA57" si="4">AB10*0.3025</f>
         <v>0</v>
       </c>
       <c r="AB10" s="91"/>
       <c r="AC10" s="90"/>
       <c r="AD10" s="92"/>
-      <c r="AE10" s="150"/>
-      <c r="AF10" s="151"/>
-      <c r="AG10" s="101">
+      <c r="AE10" s="117"/>
+      <c r="AF10" s="118"/>
+      <c r="AG10" s="100">
         <f t="shared" ref="AG10:AG57" si="5">AH10*860</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="102"/>
+      <c r="AH10" s="101"/>
       <c r="AI10" s="88"/>
-      <c r="AJ10" s="152"/>
+      <c r="AJ10" s="119"/>
       <c r="AK10" s="93"/>
       <c r="AL10" s="93"/>
-      <c r="AM10" s="100"/>
-      <c r="AN10" s="100"/>
-      <c r="AO10" s="100"/>
+      <c r="AM10" s="99"/>
+      <c r="AN10" s="99"/>
+      <c r="AO10" s="99"/>
       <c r="AP10" s="83"/>
-      <c r="AQ10" s="94"/>
-      <c r="AR10" s="95"/>
-      <c r="AS10" s="83"/>
-      <c r="AT10" s="83"/>
-      <c r="AU10" s="95"/>
-      <c r="AV10" s="94"/>
-      <c r="AW10" s="95"/>
+      <c r="AQ10" s="154"/>
+      <c r="AR10" s="110"/>
+      <c r="AS10" s="110"/>
+      <c r="AT10" s="110"/>
+      <c r="AU10" s="110"/>
+      <c r="AV10" s="154"/>
+      <c r="AW10" s="110"/>
       <c r="AX10" s="89"/>
       <c r="AY10" s="89"/>
       <c r="AZ10" s="89"/>
-      <c r="BA10" s="96"/>
+      <c r="BA10" s="89"/>
       <c r="BB10" s="95"/>
-      <c r="BC10" s="89"/>
+      <c r="BC10" s="94"/>
       <c r="BD10" s="89"/>
-      <c r="BE10" s="95"/>
-      <c r="BF10" s="95"/>
+      <c r="BE10" s="89"/>
+      <c r="BF10" s="94"/>
+      <c r="BG10" s="94"/>
     </row>
-    <row r="11" spans="1:58" ht="30" customHeight="1">
+    <row r="11" spans="1:59" ht="30" customHeight="1">
       <c r="A11" s="83"/>
       <c r="B11" s="84"/>
       <c r="C11" s="85"/>
       <c r="D11" s="86"/>
-      <c r="E11" s="143"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="146">
+      <c r="E11" s="110"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="147">
+      <c r="J11" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145"/>
-      <c r="M11" s="145"/>
-      <c r="N11" s="148"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="115"/>
       <c r="O11" s="88"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="100"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="99"/>
       <c r="R11" s="87"/>
       <c r="S11" s="88"/>
       <c r="T11" s="89"/>
-      <c r="U11" s="100"/>
-      <c r="V11" s="100"/>
-      <c r="W11" s="99"/>
+      <c r="U11" s="99"/>
+      <c r="V11" s="99"/>
+      <c r="W11" s="98"/>
       <c r="X11" s="83"/>
       <c r="Y11" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="110">
+      <c r="Z11" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="109">
+      <c r="AA11" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB11" s="91"/>
       <c r="AC11" s="90"/>
       <c r="AD11" s="92"/>
-      <c r="AE11" s="150"/>
-      <c r="AF11" s="151"/>
-      <c r="AG11" s="101">
+      <c r="AE11" s="117"/>
+      <c r="AF11" s="118"/>
+      <c r="AG11" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="102"/>
+      <c r="AH11" s="101"/>
       <c r="AI11" s="88"/>
-      <c r="AJ11" s="152"/>
+      <c r="AJ11" s="119"/>
       <c r="AK11" s="93"/>
       <c r="AL11" s="93"/>
-      <c r="AM11" s="100"/>
-      <c r="AN11" s="100"/>
-      <c r="AO11" s="100"/>
+      <c r="AM11" s="99"/>
+      <c r="AN11" s="99"/>
+      <c r="AO11" s="99"/>
       <c r="AP11" s="83"/>
-      <c r="AQ11" s="94"/>
-      <c r="AR11" s="95"/>
-      <c r="AS11" s="83"/>
-      <c r="AT11" s="83"/>
-      <c r="AU11" s="95"/>
-      <c r="AV11" s="94"/>
-      <c r="AW11" s="95"/>
+      <c r="AQ11" s="154"/>
+      <c r="AR11" s="110"/>
+      <c r="AS11" s="110"/>
+      <c r="AT11" s="110"/>
+      <c r="AU11" s="110"/>
+      <c r="AV11" s="154"/>
+      <c r="AW11" s="110"/>
       <c r="AX11" s="89"/>
       <c r="AY11" s="89"/>
       <c r="AZ11" s="89"/>
-      <c r="BA11" s="96"/>
+      <c r="BA11" s="89"/>
       <c r="BB11" s="95"/>
-      <c r="BC11" s="89"/>
+      <c r="BC11" s="94"/>
       <c r="BD11" s="89"/>
-      <c r="BE11" s="95"/>
-      <c r="BF11" s="95"/>
+      <c r="BE11" s="89"/>
+      <c r="BF11" s="94"/>
+      <c r="BG11" s="94"/>
     </row>
-    <row r="12" spans="1:58" ht="30" customHeight="1">
+    <row r="12" spans="1:59" ht="30" customHeight="1">
       <c r="A12" s="83"/>
       <c r="B12" s="84"/>
       <c r="C12" s="85"/>
       <c r="D12" s="86"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="145"/>
-      <c r="I12" s="146">
+      <c r="E12" s="110"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="147">
+      <c r="J12" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="145"/>
-      <c r="L12" s="145"/>
-      <c r="M12" s="145"/>
-      <c r="N12" s="148"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="115"/>
       <c r="O12" s="88"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="100"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="99"/>
       <c r="R12" s="87"/>
       <c r="S12" s="88"/>
       <c r="T12" s="89"/>
-      <c r="U12" s="100"/>
-      <c r="V12" s="100"/>
-      <c r="W12" s="99"/>
+      <c r="U12" s="99"/>
+      <c r="V12" s="99"/>
+      <c r="W12" s="98"/>
       <c r="X12" s="83"/>
       <c r="Y12" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="110">
+      <c r="Z12" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="109">
+      <c r="AA12" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB12" s="91"/>
       <c r="AC12" s="90"/>
       <c r="AD12" s="92"/>
-      <c r="AE12" s="150"/>
-      <c r="AF12" s="151"/>
-      <c r="AG12" s="101">
+      <c r="AE12" s="117"/>
+      <c r="AF12" s="118"/>
+      <c r="AG12" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="102"/>
+      <c r="AH12" s="101"/>
       <c r="AI12" s="88"/>
-      <c r="AJ12" s="152"/>
+      <c r="AJ12" s="119"/>
       <c r="AK12" s="93"/>
       <c r="AL12" s="93"/>
-      <c r="AM12" s="100"/>
-      <c r="AN12" s="100"/>
-      <c r="AO12" s="100"/>
+      <c r="AM12" s="99"/>
+      <c r="AN12" s="99"/>
+      <c r="AO12" s="99"/>
       <c r="AP12" s="83"/>
-      <c r="AQ12" s="94"/>
-      <c r="AR12" s="95"/>
-      <c r="AS12" s="83"/>
-      <c r="AT12" s="83"/>
-      <c r="AU12" s="95"/>
-      <c r="AV12" s="94"/>
-      <c r="AW12" s="95"/>
+      <c r="AQ12" s="154"/>
+      <c r="AR12" s="110"/>
+      <c r="AS12" s="110"/>
+      <c r="AT12" s="110"/>
+      <c r="AU12" s="110"/>
+      <c r="AV12" s="154"/>
+      <c r="AW12" s="110"/>
       <c r="AX12" s="89"/>
       <c r="AY12" s="89"/>
       <c r="AZ12" s="89"/>
-      <c r="BA12" s="96"/>
+      <c r="BA12" s="89"/>
       <c r="BB12" s="95"/>
-      <c r="BC12" s="89"/>
+      <c r="BC12" s="94"/>
       <c r="BD12" s="89"/>
-      <c r="BE12" s="95"/>
-      <c r="BF12" s="95"/>
+      <c r="BE12" s="89"/>
+      <c r="BF12" s="94"/>
+      <c r="BG12" s="94"/>
     </row>
-    <row r="13" spans="1:58" ht="30" customHeight="1">
+    <row r="13" spans="1:59" ht="30" customHeight="1">
       <c r="A13" s="83"/>
       <c r="B13" s="84"/>
       <c r="C13" s="85"/>
       <c r="D13" s="86"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="145"/>
-      <c r="I13" s="146">
+      <c r="E13" s="110"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="145"/>
-      <c r="L13" s="145"/>
-      <c r="M13" s="145"/>
-      <c r="N13" s="148"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="115"/>
       <c r="O13" s="88"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="100"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="99"/>
       <c r="R13" s="87"/>
       <c r="S13" s="88"/>
       <c r="T13" s="89"/>
-      <c r="U13" s="100"/>
-      <c r="V13" s="100"/>
-      <c r="W13" s="99"/>
+      <c r="U13" s="99"/>
+      <c r="V13" s="99"/>
+      <c r="W13" s="98"/>
       <c r="X13" s="83"/>
       <c r="Y13" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="110">
+      <c r="Z13" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="109">
+      <c r="AA13" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB13" s="91"/>
       <c r="AC13" s="90"/>
       <c r="AD13" s="92"/>
-      <c r="AE13" s="150"/>
-      <c r="AF13" s="151"/>
-      <c r="AG13" s="101">
+      <c r="AE13" s="117"/>
+      <c r="AF13" s="118"/>
+      <c r="AG13" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH13" s="102"/>
+      <c r="AH13" s="101"/>
       <c r="AI13" s="88"/>
-      <c r="AJ13" s="152"/>
+      <c r="AJ13" s="119"/>
       <c r="AK13" s="93"/>
       <c r="AL13" s="93"/>
-      <c r="AM13" s="100"/>
-      <c r="AN13" s="100"/>
-      <c r="AO13" s="100"/>
+      <c r="AM13" s="99"/>
+      <c r="AN13" s="99"/>
+      <c r="AO13" s="99"/>
       <c r="AP13" s="83"/>
-      <c r="AQ13" s="94"/>
-      <c r="AR13" s="95"/>
-      <c r="AS13" s="83"/>
-      <c r="AT13" s="83"/>
-      <c r="AU13" s="95"/>
-      <c r="AV13" s="94"/>
-      <c r="AW13" s="95"/>
+      <c r="AQ13" s="154"/>
+      <c r="AR13" s="110"/>
+      <c r="AS13" s="110"/>
+      <c r="AT13" s="110"/>
+      <c r="AU13" s="110"/>
+      <c r="AV13" s="154"/>
+      <c r="AW13" s="110"/>
       <c r="AX13" s="89"/>
       <c r="AY13" s="89"/>
       <c r="AZ13" s="89"/>
-      <c r="BA13" s="96"/>
+      <c r="BA13" s="89"/>
       <c r="BB13" s="95"/>
-      <c r="BC13" s="89"/>
+      <c r="BC13" s="94"/>
       <c r="BD13" s="89"/>
-      <c r="BE13" s="95"/>
-      <c r="BF13" s="95"/>
+      <c r="BE13" s="89"/>
+      <c r="BF13" s="94"/>
+      <c r="BG13" s="94"/>
     </row>
-    <row r="14" spans="1:58" ht="30" customHeight="1">
+    <row r="14" spans="1:59" ht="30" customHeight="1">
       <c r="A14" s="83"/>
       <c r="B14" s="84"/>
       <c r="C14" s="85"/>
       <c r="D14" s="86"/>
-      <c r="E14" s="143"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="145"/>
-      <c r="I14" s="146">
+      <c r="E14" s="110"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="147">
+      <c r="J14" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="145"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="145"/>
-      <c r="N14" s="148"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="115"/>
       <c r="O14" s="88"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="100"/>
+      <c r="P14" s="98"/>
+      <c r="Q14" s="99"/>
       <c r="R14" s="87"/>
       <c r="S14" s="88"/>
       <c r="T14" s="89"/>
-      <c r="U14" s="100"/>
-      <c r="V14" s="100"/>
-      <c r="W14" s="99"/>
+      <c r="U14" s="99"/>
+      <c r="V14" s="99"/>
+      <c r="W14" s="98"/>
       <c r="X14" s="83"/>
       <c r="Y14" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="110">
+      <c r="Z14" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="109">
+      <c r="AA14" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB14" s="91"/>
       <c r="AC14" s="90"/>
       <c r="AD14" s="92"/>
-      <c r="AE14" s="150"/>
-      <c r="AF14" s="151"/>
-      <c r="AG14" s="101">
+      <c r="AE14" s="117"/>
+      <c r="AF14" s="118"/>
+      <c r="AG14" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="102"/>
+      <c r="AH14" s="101"/>
       <c r="AI14" s="88"/>
-      <c r="AJ14" s="152"/>
+      <c r="AJ14" s="119"/>
       <c r="AK14" s="93"/>
       <c r="AL14" s="93"/>
-      <c r="AM14" s="100"/>
-      <c r="AN14" s="100"/>
-      <c r="AO14" s="100"/>
+      <c r="AM14" s="99"/>
+      <c r="AN14" s="99"/>
+      <c r="AO14" s="99"/>
       <c r="AP14" s="83"/>
-      <c r="AQ14" s="94"/>
-      <c r="AR14" s="95"/>
-      <c r="AS14" s="83"/>
-      <c r="AT14" s="83"/>
-      <c r="AU14" s="95"/>
-      <c r="AV14" s="94"/>
-      <c r="AW14" s="95"/>
+      <c r="AQ14" s="154"/>
+      <c r="AR14" s="110"/>
+      <c r="AS14" s="110"/>
+      <c r="AT14" s="110"/>
+      <c r="AU14" s="110"/>
+      <c r="AV14" s="154"/>
+      <c r="AW14" s="110"/>
       <c r="AX14" s="89"/>
       <c r="AY14" s="89"/>
       <c r="AZ14" s="89"/>
-      <c r="BA14" s="96"/>
+      <c r="BA14" s="89"/>
       <c r="BB14" s="95"/>
-      <c r="BC14" s="89"/>
+      <c r="BC14" s="94"/>
       <c r="BD14" s="89"/>
-      <c r="BE14" s="95"/>
-      <c r="BF14" s="95"/>
+      <c r="BE14" s="89"/>
+      <c r="BF14" s="94"/>
+      <c r="BG14" s="94"/>
     </row>
-    <row r="15" spans="1:58" ht="30" customHeight="1">
+    <row r="15" spans="1:59" ht="30" customHeight="1">
       <c r="A15" s="83"/>
       <c r="B15" s="84"/>
       <c r="C15" s="85"/>
       <c r="D15" s="86"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="145"/>
-      <c r="I15" s="146">
+      <c r="E15" s="110"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="147">
+      <c r="J15" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="145"/>
-      <c r="L15" s="145"/>
-      <c r="M15" s="145"/>
-      <c r="N15" s="148"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="115"/>
       <c r="O15" s="88"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="100"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="99"/>
       <c r="R15" s="87"/>
       <c r="S15" s="88"/>
       <c r="T15" s="89"/>
-      <c r="U15" s="100"/>
-      <c r="V15" s="100"/>
-      <c r="W15" s="99"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="98"/>
       <c r="X15" s="83"/>
       <c r="Y15" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="110">
+      <c r="Z15" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="109">
+      <c r="AA15" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB15" s="91"/>
       <c r="AC15" s="90"/>
       <c r="AD15" s="92"/>
-      <c r="AE15" s="150"/>
-      <c r="AF15" s="151"/>
-      <c r="AG15" s="101">
+      <c r="AE15" s="117"/>
+      <c r="AF15" s="118"/>
+      <c r="AG15" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="102"/>
+      <c r="AH15" s="101"/>
       <c r="AI15" s="88"/>
-      <c r="AJ15" s="152"/>
+      <c r="AJ15" s="119"/>
       <c r="AK15" s="93"/>
       <c r="AL15" s="93"/>
-      <c r="AM15" s="100"/>
-      <c r="AN15" s="100"/>
-      <c r="AO15" s="100"/>
+      <c r="AM15" s="99"/>
+      <c r="AN15" s="99"/>
+      <c r="AO15" s="99"/>
       <c r="AP15" s="83"/>
-      <c r="AQ15" s="94"/>
-      <c r="AR15" s="95"/>
-      <c r="AS15" s="83"/>
-      <c r="AT15" s="83"/>
-      <c r="AU15" s="95"/>
-      <c r="AV15" s="94"/>
-      <c r="AW15" s="95"/>
+      <c r="AQ15" s="154"/>
+      <c r="AR15" s="110"/>
+      <c r="AS15" s="110"/>
+      <c r="AT15" s="110"/>
+      <c r="AU15" s="110"/>
+      <c r="AV15" s="154"/>
+      <c r="AW15" s="110"/>
       <c r="AX15" s="89"/>
       <c r="AY15" s="89"/>
       <c r="AZ15" s="89"/>
-      <c r="BA15" s="96"/>
+      <c r="BA15" s="89"/>
       <c r="BB15" s="95"/>
-      <c r="BC15" s="89"/>
+      <c r="BC15" s="94"/>
       <c r="BD15" s="89"/>
-      <c r="BE15" s="95"/>
-      <c r="BF15" s="95"/>
+      <c r="BE15" s="89"/>
+      <c r="BF15" s="94"/>
+      <c r="BG15" s="94"/>
     </row>
-    <row r="16" spans="1:58" ht="30" customHeight="1">
+    <row r="16" spans="1:59" ht="30" customHeight="1">
       <c r="A16" s="83"/>
       <c r="B16" s="84"/>
       <c r="C16" s="85"/>
       <c r="D16" s="86"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="145"/>
-      <c r="I16" s="146">
+      <c r="E16" s="110"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="147">
+      <c r="J16" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="145"/>
-      <c r="L16" s="145"/>
-      <c r="M16" s="145"/>
-      <c r="N16" s="148"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="115"/>
       <c r="O16" s="88"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="100"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="99"/>
       <c r="R16" s="87"/>
       <c r="S16" s="88"/>
       <c r="T16" s="89"/>
-      <c r="U16" s="100"/>
-      <c r="V16" s="100"/>
-      <c r="W16" s="99"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="99"/>
+      <c r="W16" s="98"/>
       <c r="X16" s="83"/>
       <c r="Y16" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="110">
+      <c r="Z16" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="109">
+      <c r="AA16" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB16" s="91"/>
       <c r="AC16" s="90"/>
       <c r="AD16" s="92"/>
-      <c r="AE16" s="150"/>
-      <c r="AF16" s="151"/>
-      <c r="AG16" s="101">
+      <c r="AE16" s="117"/>
+      <c r="AF16" s="118"/>
+      <c r="AG16" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="102"/>
+      <c r="AH16" s="101"/>
       <c r="AI16" s="88"/>
-      <c r="AJ16" s="152"/>
+      <c r="AJ16" s="119"/>
       <c r="AK16" s="93"/>
       <c r="AL16" s="93"/>
-      <c r="AM16" s="100"/>
-      <c r="AN16" s="100"/>
-      <c r="AO16" s="100"/>
+      <c r="AM16" s="99"/>
+      <c r="AN16" s="99"/>
+      <c r="AO16" s="99"/>
       <c r="AP16" s="83"/>
-      <c r="AQ16" s="94"/>
-      <c r="AR16" s="95"/>
-      <c r="AS16" s="83"/>
-      <c r="AT16" s="83"/>
-      <c r="AU16" s="95"/>
-      <c r="AV16" s="94"/>
-      <c r="AW16" s="95"/>
+      <c r="AQ16" s="154"/>
+      <c r="AR16" s="110"/>
+      <c r="AS16" s="110"/>
+      <c r="AT16" s="110"/>
+      <c r="AU16" s="110"/>
+      <c r="AV16" s="154"/>
+      <c r="AW16" s="110"/>
       <c r="AX16" s="89"/>
       <c r="AY16" s="89"/>
       <c r="AZ16" s="89"/>
-      <c r="BA16" s="96"/>
+      <c r="BA16" s="89"/>
       <c r="BB16" s="95"/>
-      <c r="BC16" s="89"/>
+      <c r="BC16" s="94"/>
       <c r="BD16" s="89"/>
-      <c r="BE16" s="95"/>
-      <c r="BF16" s="95"/>
+      <c r="BE16" s="89"/>
+      <c r="BF16" s="94"/>
+      <c r="BG16" s="94"/>
     </row>
-    <row r="17" spans="1:58" ht="30" customHeight="1">
+    <row r="17" spans="1:59" ht="30" customHeight="1">
       <c r="A17" s="83"/>
       <c r="B17" s="84"/>
       <c r="C17" s="85"/>
       <c r="D17" s="86"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="145"/>
-      <c r="I17" s="146">
+      <c r="E17" s="110"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="147">
+      <c r="J17" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="145"/>
-      <c r="L17" s="145"/>
-      <c r="M17" s="145"/>
-      <c r="N17" s="148"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="115"/>
       <c r="O17" s="88"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="100"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="99"/>
       <c r="R17" s="87"/>
       <c r="S17" s="88"/>
       <c r="T17" s="89"/>
-      <c r="U17" s="100"/>
-      <c r="V17" s="100"/>
-      <c r="W17" s="99"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="98"/>
       <c r="X17" s="83"/>
       <c r="Y17" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="110">
+      <c r="Z17" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="109">
+      <c r="AA17" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB17" s="91"/>
       <c r="AC17" s="90"/>
       <c r="AD17" s="92"/>
-      <c r="AE17" s="150"/>
-      <c r="AF17" s="151"/>
-      <c r="AG17" s="101">
+      <c r="AE17" s="117"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="102"/>
+      <c r="AH17" s="101"/>
       <c r="AI17" s="88"/>
-      <c r="AJ17" s="152"/>
+      <c r="AJ17" s="119"/>
       <c r="AK17" s="93"/>
       <c r="AL17" s="93"/>
-      <c r="AM17" s="100"/>
-      <c r="AN17" s="100"/>
-      <c r="AO17" s="100"/>
+      <c r="AM17" s="99"/>
+      <c r="AN17" s="99"/>
+      <c r="AO17" s="99"/>
       <c r="AP17" s="83"/>
-      <c r="AQ17" s="94"/>
-      <c r="AR17" s="95"/>
-      <c r="AS17" s="83"/>
-      <c r="AT17" s="83"/>
-      <c r="AU17" s="95"/>
-      <c r="AV17" s="94"/>
-      <c r="AW17" s="95"/>
+      <c r="AQ17" s="154"/>
+      <c r="AR17" s="110"/>
+      <c r="AS17" s="110"/>
+      <c r="AT17" s="110"/>
+      <c r="AU17" s="110"/>
+      <c r="AV17" s="154"/>
+      <c r="AW17" s="110"/>
       <c r="AX17" s="89"/>
       <c r="AY17" s="89"/>
       <c r="AZ17" s="89"/>
-      <c r="BA17" s="96"/>
+      <c r="BA17" s="89"/>
       <c r="BB17" s="95"/>
-      <c r="BC17" s="89"/>
+      <c r="BC17" s="94"/>
       <c r="BD17" s="89"/>
-      <c r="BE17" s="95"/>
-      <c r="BF17" s="95"/>
+      <c r="BE17" s="89"/>
+      <c r="BF17" s="94"/>
+      <c r="BG17" s="94"/>
     </row>
-    <row r="18" spans="1:58" ht="30.75" customHeight="1">
+    <row r="18" spans="1:59" ht="30.75" customHeight="1">
       <c r="A18" s="83"/>
       <c r="B18" s="84"/>
       <c r="C18" s="83"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="146">
+      <c r="D18" s="96"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="147">
+      <c r="J18" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="149"/>
-      <c r="L18" s="149"/>
-      <c r="M18" s="149"/>
-      <c r="N18" s="148"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="116"/>
+      <c r="N18" s="115"/>
       <c r="O18" s="88"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="100"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="99"/>
       <c r="R18" s="87"/>
       <c r="S18" s="88"/>
       <c r="T18" s="89"/>
-      <c r="U18" s="100"/>
-      <c r="V18" s="100"/>
-      <c r="W18" s="99"/>
+      <c r="U18" s="99"/>
+      <c r="V18" s="99"/>
+      <c r="W18" s="98"/>
       <c r="X18" s="83"/>
       <c r="Y18" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="110">
+      <c r="Z18" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="109">
+      <c r="AA18" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB18" s="91"/>
       <c r="AC18" s="90"/>
       <c r="AD18" s="92"/>
-      <c r="AE18" s="153"/>
-      <c r="AF18" s="154"/>
-      <c r="AG18" s="101">
+      <c r="AE18" s="120"/>
+      <c r="AF18" s="121"/>
+      <c r="AG18" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="103"/>
+      <c r="AH18" s="102"/>
       <c r="AI18" s="88"/>
-      <c r="AJ18" s="152"/>
+      <c r="AJ18" s="119"/>
       <c r="AK18" s="93"/>
       <c r="AL18" s="93"/>
-      <c r="AM18" s="100"/>
-      <c r="AN18" s="100"/>
-      <c r="AO18" s="100"/>
+      <c r="AM18" s="99"/>
+      <c r="AN18" s="99"/>
+      <c r="AO18" s="99"/>
       <c r="AP18" s="83"/>
-      <c r="AQ18" s="94"/>
-      <c r="AR18" s="95"/>
-      <c r="AS18" s="83"/>
-      <c r="AT18" s="83"/>
-      <c r="AU18" s="95"/>
-      <c r="AV18" s="94"/>
-      <c r="AW18" s="95"/>
+      <c r="AQ18" s="154"/>
+      <c r="AR18" s="110"/>
+      <c r="AS18" s="110"/>
+      <c r="AT18" s="110"/>
+      <c r="AU18" s="110"/>
+      <c r="AV18" s="154"/>
+      <c r="AW18" s="110"/>
       <c r="AX18" s="89"/>
       <c r="AY18" s="89"/>
       <c r="AZ18" s="89"/>
-      <c r="BA18" s="96"/>
+      <c r="BA18" s="89"/>
       <c r="BB18" s="95"/>
-      <c r="BC18" s="89"/>
+      <c r="BC18" s="94"/>
       <c r="BD18" s="89"/>
-      <c r="BE18" s="95"/>
-      <c r="BF18" s="95"/>
+      <c r="BE18" s="89"/>
+      <c r="BF18" s="94"/>
+      <c r="BG18" s="94"/>
     </row>
-    <row r="19" spans="1:58" ht="30" customHeight="1">
+    <row r="19" spans="1:59" ht="30" customHeight="1">
       <c r="A19" s="83"/>
       <c r="B19" s="84"/>
       <c r="C19" s="83"/>
       <c r="D19" s="86"/>
-      <c r="E19" s="143"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="146">
+      <c r="E19" s="110"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="147">
+      <c r="J19" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="148"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="115"/>
       <c r="O19" s="88"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="100"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="99"/>
       <c r="R19" s="87"/>
       <c r="S19" s="88"/>
       <c r="T19" s="89"/>
-      <c r="U19" s="100"/>
-      <c r="V19" s="100"/>
-      <c r="W19" s="99"/>
+      <c r="U19" s="99"/>
+      <c r="V19" s="99"/>
+      <c r="W19" s="98"/>
       <c r="X19" s="83"/>
       <c r="Y19" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z19" s="110">
+      <c r="Z19" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="109">
+      <c r="AA19" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB19" s="91"/>
       <c r="AC19" s="90"/>
       <c r="AD19" s="92"/>
-      <c r="AE19" s="153"/>
-      <c r="AF19" s="154"/>
-      <c r="AG19" s="101">
+      <c r="AE19" s="120"/>
+      <c r="AF19" s="121"/>
+      <c r="AG19" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="103"/>
+      <c r="AH19" s="102"/>
       <c r="AI19" s="88"/>
-      <c r="AJ19" s="152"/>
+      <c r="AJ19" s="119"/>
       <c r="AK19" s="93"/>
       <c r="AL19" s="93"/>
-      <c r="AM19" s="100"/>
-      <c r="AN19" s="100"/>
-      <c r="AO19" s="100"/>
+      <c r="AM19" s="99"/>
+      <c r="AN19" s="99"/>
+      <c r="AO19" s="99"/>
       <c r="AP19" s="83"/>
-      <c r="AQ19" s="94"/>
-      <c r="AR19" s="95"/>
-      <c r="AS19" s="83"/>
-      <c r="AT19" s="83"/>
-      <c r="AU19" s="95"/>
-      <c r="AV19" s="94"/>
-      <c r="AW19" s="95"/>
+      <c r="AQ19" s="154"/>
+      <c r="AR19" s="110"/>
+      <c r="AS19" s="110"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="154"/>
+      <c r="AW19" s="110"/>
       <c r="AX19" s="89"/>
       <c r="AY19" s="89"/>
       <c r="AZ19" s="89"/>
-      <c r="BA19" s="96"/>
+      <c r="BA19" s="89"/>
       <c r="BB19" s="95"/>
-      <c r="BC19" s="89"/>
+      <c r="BC19" s="94"/>
       <c r="BD19" s="89"/>
-      <c r="BE19" s="95"/>
-      <c r="BF19" s="95"/>
+      <c r="BE19" s="89"/>
+      <c r="BF19" s="94"/>
+      <c r="BG19" s="94"/>
     </row>
-    <row r="20" spans="1:58" ht="30" customHeight="1">
+    <row r="20" spans="1:59" ht="30" customHeight="1">
       <c r="A20" s="83"/>
       <c r="B20" s="84"/>
       <c r="C20" s="83"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="143"/>
-      <c r="F20" s="144"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="146">
+      <c r="D20" s="97"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="147">
+      <c r="J20" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="148"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="115"/>
       <c r="O20" s="88"/>
-      <c r="P20" s="99"/>
-      <c r="Q20" s="100"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="99"/>
       <c r="R20" s="87"/>
       <c r="S20" s="88"/>
       <c r="T20" s="89"/>
-      <c r="U20" s="100"/>
-      <c r="V20" s="100"/>
-      <c r="W20" s="99"/>
+      <c r="U20" s="99"/>
+      <c r="V20" s="99"/>
+      <c r="W20" s="98"/>
       <c r="X20" s="83"/>
       <c r="Y20" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="110">
+      <c r="Z20" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="109">
+      <c r="AA20" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB20" s="91"/>
       <c r="AC20" s="90"/>
       <c r="AD20" s="92"/>
-      <c r="AE20" s="153"/>
-      <c r="AF20" s="154"/>
-      <c r="AG20" s="101">
+      <c r="AE20" s="120"/>
+      <c r="AF20" s="121"/>
+      <c r="AG20" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="103"/>
+      <c r="AH20" s="102"/>
       <c r="AI20" s="88"/>
-      <c r="AJ20" s="152"/>
+      <c r="AJ20" s="119"/>
       <c r="AK20" s="93"/>
       <c r="AL20" s="93"/>
-      <c r="AM20" s="100"/>
-      <c r="AN20" s="100"/>
-      <c r="AO20" s="100"/>
+      <c r="AM20" s="99"/>
+      <c r="AN20" s="99"/>
+      <c r="AO20" s="99"/>
       <c r="AP20" s="83"/>
-      <c r="AQ20" s="94"/>
-      <c r="AR20" s="95"/>
-      <c r="AS20" s="83"/>
-      <c r="AT20" s="83"/>
-      <c r="AU20" s="95"/>
-      <c r="AV20" s="94"/>
-      <c r="AW20" s="95"/>
+      <c r="AQ20" s="154"/>
+      <c r="AR20" s="110"/>
+      <c r="AS20" s="110"/>
+      <c r="AT20" s="110"/>
+      <c r="AU20" s="110"/>
+      <c r="AV20" s="154"/>
+      <c r="AW20" s="110"/>
       <c r="AX20" s="89"/>
       <c r="AY20" s="89"/>
-      <c r="AZ20" s="83"/>
-      <c r="BA20" s="96"/>
+      <c r="AZ20" s="89"/>
+      <c r="BA20" s="83"/>
       <c r="BB20" s="95"/>
-      <c r="BC20" s="89"/>
+      <c r="BC20" s="94"/>
       <c r="BD20" s="89"/>
-      <c r="BE20" s="95"/>
-      <c r="BF20" s="95"/>
+      <c r="BE20" s="89"/>
+      <c r="BF20" s="94"/>
+      <c r="BG20" s="94"/>
     </row>
-    <row r="21" spans="1:58" ht="30" customHeight="1">
+    <row r="21" spans="1:59" ht="30" customHeight="1">
       <c r="A21" s="83"/>
       <c r="B21" s="84"/>
       <c r="C21" s="83"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="149"/>
-      <c r="I21" s="146">
+      <c r="D21" s="97"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="147">
+      <c r="J21" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="149"/>
-      <c r="L21" s="149"/>
-      <c r="M21" s="149"/>
-      <c r="N21" s="148"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="116"/>
+      <c r="N21" s="115"/>
       <c r="O21" s="88"/>
-      <c r="P21" s="99"/>
-      <c r="Q21" s="100"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="99"/>
       <c r="R21" s="87"/>
       <c r="S21" s="88"/>
       <c r="T21" s="89"/>
-      <c r="U21" s="100"/>
-      <c r="V21" s="100"/>
-      <c r="W21" s="99"/>
+      <c r="U21" s="99"/>
+      <c r="V21" s="99"/>
+      <c r="W21" s="98"/>
       <c r="X21" s="83"/>
       <c r="Y21" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="110">
+      <c r="Z21" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="109">
+      <c r="AA21" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB21" s="91"/>
       <c r="AC21" s="90"/>
       <c r="AD21" s="92"/>
-      <c r="AE21" s="153"/>
-      <c r="AF21" s="154"/>
-      <c r="AG21" s="101">
+      <c r="AE21" s="120"/>
+      <c r="AF21" s="121"/>
+      <c r="AG21" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="103"/>
+      <c r="AH21" s="102"/>
       <c r="AI21" s="88"/>
-      <c r="AJ21" s="152"/>
+      <c r="AJ21" s="119"/>
       <c r="AK21" s="93"/>
       <c r="AL21" s="93"/>
-      <c r="AM21" s="100"/>
-      <c r="AN21" s="100"/>
-      <c r="AO21" s="100"/>
+      <c r="AM21" s="99"/>
+      <c r="AN21" s="99"/>
+      <c r="AO21" s="99"/>
       <c r="AP21" s="83"/>
-      <c r="AQ21" s="94"/>
-      <c r="AR21" s="95"/>
-      <c r="AS21" s="83"/>
-      <c r="AT21" s="83"/>
-      <c r="AU21" s="95"/>
-      <c r="AV21" s="94"/>
-      <c r="AW21" s="95"/>
+      <c r="AQ21" s="154"/>
+      <c r="AR21" s="110"/>
+      <c r="AS21" s="110"/>
+      <c r="AT21" s="110"/>
+      <c r="AU21" s="110"/>
+      <c r="AV21" s="154"/>
+      <c r="AW21" s="110"/>
       <c r="AX21" s="89"/>
       <c r="AY21" s="89"/>
-      <c r="AZ21" s="83"/>
-      <c r="BA21" s="96"/>
+      <c r="AZ21" s="89"/>
+      <c r="BA21" s="83"/>
       <c r="BB21" s="95"/>
-      <c r="BC21" s="89"/>
+      <c r="BC21" s="94"/>
       <c r="BD21" s="89"/>
-      <c r="BE21" s="95"/>
-      <c r="BF21" s="95"/>
+      <c r="BE21" s="89"/>
+      <c r="BF21" s="94"/>
+      <c r="BG21" s="94"/>
     </row>
-    <row r="22" spans="1:58" ht="30" customHeight="1">
+    <row r="22" spans="1:59" ht="30" customHeight="1">
       <c r="A22" s="83"/>
       <c r="B22" s="84"/>
       <c r="C22" s="85"/>
       <c r="D22" s="86"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="145"/>
-      <c r="I22" s="146">
+      <c r="E22" s="110"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="147">
+      <c r="J22" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="145"/>
-      <c r="L22" s="145"/>
-      <c r="M22" s="145"/>
-      <c r="N22" s="148"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="115"/>
       <c r="O22" s="88"/>
-      <c r="P22" s="99"/>
-      <c r="Q22" s="100"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="99"/>
       <c r="R22" s="87"/>
       <c r="S22" s="88"/>
       <c r="T22" s="89"/>
-      <c r="U22" s="100"/>
-      <c r="V22" s="100"/>
-      <c r="W22" s="99"/>
+      <c r="U22" s="99"/>
+      <c r="V22" s="99"/>
+      <c r="W22" s="98"/>
       <c r="X22" s="83"/>
       <c r="Y22" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z22" s="110">
+      <c r="Z22" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA22" s="109">
+      <c r="AA22" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB22" s="91"/>
       <c r="AC22" s="90"/>
       <c r="AD22" s="92"/>
-      <c r="AE22" s="150"/>
-      <c r="AF22" s="151"/>
-      <c r="AG22" s="101">
+      <c r="AE22" s="117"/>
+      <c r="AF22" s="118"/>
+      <c r="AG22" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="102"/>
+      <c r="AH22" s="101"/>
       <c r="AI22" s="88"/>
-      <c r="AJ22" s="152"/>
+      <c r="AJ22" s="119"/>
       <c r="AK22" s="93"/>
       <c r="AL22" s="93"/>
-      <c r="AM22" s="100"/>
-      <c r="AN22" s="100"/>
-      <c r="AO22" s="100"/>
+      <c r="AM22" s="99"/>
+      <c r="AN22" s="99"/>
+      <c r="AO22" s="99"/>
       <c r="AP22" s="83"/>
-      <c r="AQ22" s="94"/>
-      <c r="AR22" s="95"/>
-      <c r="AS22" s="83"/>
-      <c r="AT22" s="83"/>
-      <c r="AU22" s="95"/>
-      <c r="AV22" s="94"/>
-      <c r="AW22" s="95"/>
+      <c r="AQ22" s="154"/>
+      <c r="AR22" s="110"/>
+      <c r="AS22" s="110"/>
+      <c r="AT22" s="110"/>
+      <c r="AU22" s="110"/>
+      <c r="AV22" s="154"/>
+      <c r="AW22" s="110"/>
       <c r="AX22" s="89"/>
       <c r="AY22" s="89"/>
       <c r="AZ22" s="89"/>
-      <c r="BA22" s="96"/>
+      <c r="BA22" s="89"/>
       <c r="BB22" s="95"/>
-      <c r="BC22" s="89"/>
+      <c r="BC22" s="94"/>
       <c r="BD22" s="89"/>
-      <c r="BE22" s="95"/>
-      <c r="BF22" s="95"/>
+      <c r="BE22" s="89"/>
+      <c r="BF22" s="94"/>
+      <c r="BG22" s="94"/>
     </row>
-    <row r="23" spans="1:58" ht="30" customHeight="1">
+    <row r="23" spans="1:59" ht="30" customHeight="1">
       <c r="A23" s="83"/>
       <c r="B23" s="84"/>
       <c r="C23" s="85"/>
       <c r="D23" s="86"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="146">
+      <c r="E23" s="110"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="147">
+      <c r="J23" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="145"/>
-      <c r="L23" s="145"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="148"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="115"/>
       <c r="O23" s="88"/>
-      <c r="P23" s="99"/>
-      <c r="Q23" s="100"/>
+      <c r="P23" s="98"/>
+      <c r="Q23" s="99"/>
       <c r="R23" s="87"/>
       <c r="S23" s="88"/>
       <c r="T23" s="89"/>
-      <c r="U23" s="100"/>
-      <c r="V23" s="100"/>
-      <c r="W23" s="99"/>
+      <c r="U23" s="99"/>
+      <c r="V23" s="99"/>
+      <c r="W23" s="98"/>
       <c r="X23" s="83"/>
       <c r="Y23" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="110">
+      <c r="Z23" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="109">
+      <c r="AA23" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB23" s="91"/>
       <c r="AC23" s="90"/>
       <c r="AD23" s="92"/>
-      <c r="AE23" s="150"/>
-      <c r="AF23" s="151"/>
-      <c r="AG23" s="101">
+      <c r="AE23" s="117"/>
+      <c r="AF23" s="118"/>
+      <c r="AG23" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="102"/>
+      <c r="AH23" s="101"/>
       <c r="AI23" s="88"/>
-      <c r="AJ23" s="152"/>
+      <c r="AJ23" s="119"/>
       <c r="AK23" s="93"/>
       <c r="AL23" s="93"/>
-      <c r="AM23" s="100"/>
-      <c r="AN23" s="100"/>
-      <c r="AO23" s="100"/>
+      <c r="AM23" s="99"/>
+      <c r="AN23" s="99"/>
+      <c r="AO23" s="99"/>
       <c r="AP23" s="83"/>
-      <c r="AQ23" s="94"/>
-      <c r="AR23" s="95"/>
-      <c r="AS23" s="83"/>
-      <c r="AT23" s="83"/>
-      <c r="AU23" s="95"/>
-      <c r="AV23" s="94"/>
-      <c r="AW23" s="95"/>
+      <c r="AQ23" s="154"/>
+      <c r="AR23" s="110"/>
+      <c r="AS23" s="110"/>
+      <c r="AT23" s="110"/>
+      <c r="AU23" s="110"/>
+      <c r="AV23" s="154"/>
+      <c r="AW23" s="110"/>
       <c r="AX23" s="89"/>
       <c r="AY23" s="89"/>
       <c r="AZ23" s="89"/>
-      <c r="BA23" s="96"/>
+      <c r="BA23" s="89"/>
       <c r="BB23" s="95"/>
-      <c r="BC23" s="89"/>
+      <c r="BC23" s="94"/>
       <c r="BD23" s="89"/>
-      <c r="BE23" s="95"/>
-      <c r="BF23" s="95"/>
+      <c r="BE23" s="89"/>
+      <c r="BF23" s="94"/>
+      <c r="BG23" s="94"/>
     </row>
-    <row r="24" spans="1:58" ht="30" customHeight="1">
+    <row r="24" spans="1:59" ht="30" customHeight="1">
       <c r="A24" s="83"/>
       <c r="B24" s="84"/>
       <c r="C24" s="85"/>
       <c r="D24" s="86"/>
-      <c r="E24" s="143"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="145"/>
-      <c r="I24" s="146">
+      <c r="E24" s="110"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="147">
+      <c r="J24" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="145"/>
-      <c r="L24" s="145"/>
-      <c r="M24" s="145"/>
-      <c r="N24" s="148"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="115"/>
       <c r="O24" s="88"/>
-      <c r="P24" s="99"/>
-      <c r="Q24" s="100"/>
+      <c r="P24" s="98"/>
+      <c r="Q24" s="99"/>
       <c r="R24" s="87"/>
       <c r="S24" s="88"/>
       <c r="T24" s="89"/>
-      <c r="U24" s="100"/>
-      <c r="V24" s="100"/>
-      <c r="W24" s="99"/>
+      <c r="U24" s="99"/>
+      <c r="V24" s="99"/>
+      <c r="W24" s="98"/>
       <c r="X24" s="83"/>
       <c r="Y24" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z24" s="110">
+      <c r="Z24" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA24" s="109">
+      <c r="AA24" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB24" s="91"/>
       <c r="AC24" s="90"/>
       <c r="AD24" s="92"/>
-      <c r="AE24" s="150"/>
-      <c r="AF24" s="151"/>
-      <c r="AG24" s="101">
+      <c r="AE24" s="117"/>
+      <c r="AF24" s="118"/>
+      <c r="AG24" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="102"/>
+      <c r="AH24" s="101"/>
       <c r="AI24" s="88"/>
-      <c r="AJ24" s="152"/>
+      <c r="AJ24" s="119"/>
       <c r="AK24" s="93"/>
       <c r="AL24" s="93"/>
-      <c r="AM24" s="100"/>
-      <c r="AN24" s="100"/>
-      <c r="AO24" s="100"/>
+      <c r="AM24" s="99"/>
+      <c r="AN24" s="99"/>
+      <c r="AO24" s="99"/>
       <c r="AP24" s="83"/>
-      <c r="AQ24" s="94"/>
-      <c r="AR24" s="95"/>
-      <c r="AS24" s="83"/>
-      <c r="AT24" s="83"/>
-      <c r="AU24" s="95"/>
-      <c r="AV24" s="94"/>
-      <c r="AW24" s="95"/>
+      <c r="AQ24" s="154"/>
+      <c r="AR24" s="110"/>
+      <c r="AS24" s="110"/>
+      <c r="AT24" s="110"/>
+      <c r="AU24" s="110"/>
+      <c r="AV24" s="154"/>
+      <c r="AW24" s="110"/>
       <c r="AX24" s="89"/>
       <c r="AY24" s="89"/>
       <c r="AZ24" s="89"/>
-      <c r="BA24" s="96"/>
+      <c r="BA24" s="89"/>
       <c r="BB24" s="95"/>
-      <c r="BC24" s="89"/>
+      <c r="BC24" s="94"/>
       <c r="BD24" s="89"/>
-      <c r="BE24" s="95"/>
-      <c r="BF24" s="95"/>
+      <c r="BE24" s="89"/>
+      <c r="BF24" s="94"/>
+      <c r="BG24" s="94"/>
     </row>
-    <row r="25" spans="1:58" ht="30" customHeight="1">
+    <row r="25" spans="1:59" ht="30" customHeight="1">
       <c r="A25" s="83"/>
       <c r="B25" s="84"/>
       <c r="C25" s="85"/>
       <c r="D25" s="86"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="145"/>
-      <c r="I25" s="146">
+      <c r="E25" s="110"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="147">
+      <c r="J25" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="145"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="145"/>
-      <c r="N25" s="148"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="115"/>
       <c r="O25" s="88"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="100"/>
+      <c r="P25" s="98"/>
+      <c r="Q25" s="99"/>
       <c r="R25" s="87"/>
       <c r="S25" s="88"/>
       <c r="T25" s="89"/>
-      <c r="U25" s="100"/>
-      <c r="V25" s="100"/>
-      <c r="W25" s="99"/>
+      <c r="U25" s="99"/>
+      <c r="V25" s="99"/>
+      <c r="W25" s="98"/>
       <c r="X25" s="83"/>
       <c r="Y25" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z25" s="110">
+      <c r="Z25" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA25" s="109">
+      <c r="AA25" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB25" s="91"/>
       <c r="AC25" s="90"/>
       <c r="AD25" s="92"/>
-      <c r="AE25" s="150"/>
-      <c r="AF25" s="151"/>
-      <c r="AG25" s="101">
+      <c r="AE25" s="117"/>
+      <c r="AF25" s="118"/>
+      <c r="AG25" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="102"/>
+      <c r="AH25" s="101"/>
       <c r="AI25" s="88"/>
-      <c r="AJ25" s="152"/>
+      <c r="AJ25" s="119"/>
       <c r="AK25" s="93"/>
       <c r="AL25" s="93"/>
-      <c r="AM25" s="100"/>
-      <c r="AN25" s="100"/>
-      <c r="AO25" s="100"/>
+      <c r="AM25" s="99"/>
+      <c r="AN25" s="99"/>
+      <c r="AO25" s="99"/>
       <c r="AP25" s="83"/>
-      <c r="AQ25" s="94"/>
-      <c r="AR25" s="95"/>
-      <c r="AS25" s="83"/>
-      <c r="AT25" s="83"/>
-      <c r="AU25" s="95"/>
-      <c r="AV25" s="94"/>
-      <c r="AW25" s="95"/>
+      <c r="AQ25" s="154"/>
+      <c r="AR25" s="110"/>
+      <c r="AS25" s="110"/>
+      <c r="AT25" s="110"/>
+      <c r="AU25" s="110"/>
+      <c r="AV25" s="154"/>
+      <c r="AW25" s="110"/>
       <c r="AX25" s="89"/>
       <c r="AY25" s="89"/>
       <c r="AZ25" s="89"/>
-      <c r="BA25" s="96"/>
+      <c r="BA25" s="89"/>
       <c r="BB25" s="95"/>
-      <c r="BC25" s="89"/>
+      <c r="BC25" s="94"/>
       <c r="BD25" s="89"/>
-      <c r="BE25" s="95"/>
-      <c r="BF25" s="95"/>
+      <c r="BE25" s="89"/>
+      <c r="BF25" s="94"/>
+      <c r="BG25" s="94"/>
     </row>
-    <row r="26" spans="1:58" ht="30" customHeight="1">
+    <row r="26" spans="1:59" ht="30" customHeight="1">
       <c r="A26" s="83"/>
       <c r="B26" s="84"/>
       <c r="C26" s="85"/>
       <c r="D26" s="86"/>
-      <c r="E26" s="143"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="145"/>
-      <c r="I26" s="146">
+      <c r="E26" s="110"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="147">
+      <c r="J26" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="145"/>
-      <c r="L26" s="145"/>
-      <c r="M26" s="145"/>
-      <c r="N26" s="148"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="115"/>
       <c r="O26" s="88"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="100"/>
+      <c r="P26" s="98"/>
+      <c r="Q26" s="99"/>
       <c r="R26" s="87"/>
       <c r="S26" s="88"/>
       <c r="T26" s="89"/>
-      <c r="U26" s="100"/>
-      <c r="V26" s="100"/>
-      <c r="W26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="98"/>
       <c r="X26" s="83"/>
       <c r="Y26" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z26" s="110">
+      <c r="Z26" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="109">
+      <c r="AA26" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB26" s="91"/>
       <c r="AC26" s="90"/>
       <c r="AD26" s="92"/>
-      <c r="AE26" s="150"/>
-      <c r="AF26" s="151"/>
-      <c r="AG26" s="101">
+      <c r="AE26" s="117"/>
+      <c r="AF26" s="118"/>
+      <c r="AG26" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="102"/>
+      <c r="AH26" s="101"/>
       <c r="AI26" s="88"/>
-      <c r="AJ26" s="152"/>
+      <c r="AJ26" s="119"/>
       <c r="AK26" s="93"/>
       <c r="AL26" s="93"/>
-      <c r="AM26" s="100"/>
-      <c r="AN26" s="100"/>
-      <c r="AO26" s="100"/>
+      <c r="AM26" s="99"/>
+      <c r="AN26" s="99"/>
+      <c r="AO26" s="99"/>
       <c r="AP26" s="83"/>
-      <c r="AQ26" s="94"/>
-      <c r="AR26" s="95"/>
-      <c r="AS26" s="83"/>
-      <c r="AT26" s="83"/>
-      <c r="AU26" s="95"/>
-      <c r="AV26" s="94"/>
-      <c r="AW26" s="95"/>
+      <c r="AQ26" s="154"/>
+      <c r="AR26" s="110"/>
+      <c r="AS26" s="110"/>
+      <c r="AT26" s="110"/>
+      <c r="AU26" s="110"/>
+      <c r="AV26" s="154"/>
+      <c r="AW26" s="110"/>
       <c r="AX26" s="89"/>
       <c r="AY26" s="89"/>
       <c r="AZ26" s="89"/>
-      <c r="BA26" s="96"/>
+      <c r="BA26" s="89"/>
       <c r="BB26" s="95"/>
-      <c r="BC26" s="89"/>
+      <c r="BC26" s="94"/>
       <c r="BD26" s="89"/>
-      <c r="BE26" s="95"/>
-      <c r="BF26" s="95"/>
+      <c r="BE26" s="89"/>
+      <c r="BF26" s="94"/>
+      <c r="BG26" s="94"/>
     </row>
-    <row r="27" spans="1:58" ht="30" customHeight="1">
+    <row r="27" spans="1:59" ht="30" customHeight="1">
       <c r="A27" s="83"/>
       <c r="B27" s="84"/>
       <c r="C27" s="85"/>
       <c r="D27" s="86"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="145"/>
-      <c r="I27" s="146">
+      <c r="E27" s="110"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="147">
+      <c r="J27" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="145"/>
-      <c r="L27" s="145"/>
-      <c r="M27" s="145"/>
-      <c r="N27" s="148"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="115"/>
       <c r="O27" s="88"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="100"/>
+      <c r="P27" s="98"/>
+      <c r="Q27" s="99"/>
       <c r="R27" s="87"/>
       <c r="S27" s="88"/>
       <c r="T27" s="89"/>
-      <c r="U27" s="100"/>
-      <c r="V27" s="100"/>
-      <c r="W27" s="99"/>
+      <c r="U27" s="99"/>
+      <c r="V27" s="99"/>
+      <c r="W27" s="98"/>
       <c r="X27" s="83"/>
       <c r="Y27" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="110">
+      <c r="Z27" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="109">
+      <c r="AA27" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB27" s="91"/>
       <c r="AC27" s="90"/>
       <c r="AD27" s="92"/>
-      <c r="AE27" s="150"/>
-      <c r="AF27" s="151"/>
-      <c r="AG27" s="101">
+      <c r="AE27" s="117"/>
+      <c r="AF27" s="118"/>
+      <c r="AG27" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="102"/>
+      <c r="AH27" s="101"/>
       <c r="AI27" s="88"/>
-      <c r="AJ27" s="152"/>
+      <c r="AJ27" s="119"/>
       <c r="AK27" s="93"/>
       <c r="AL27" s="93"/>
-      <c r="AM27" s="100"/>
-      <c r="AN27" s="100"/>
-      <c r="AO27" s="100"/>
+      <c r="AM27" s="99"/>
+      <c r="AN27" s="99"/>
+      <c r="AO27" s="99"/>
       <c r="AP27" s="83"/>
-      <c r="AQ27" s="94"/>
-      <c r="AR27" s="95"/>
-      <c r="AS27" s="83"/>
-      <c r="AT27" s="83"/>
-      <c r="AU27" s="95"/>
-      <c r="AV27" s="94"/>
-      <c r="AW27" s="95"/>
+      <c r="AQ27" s="154"/>
+      <c r="AR27" s="110"/>
+      <c r="AS27" s="110"/>
+      <c r="AT27" s="110"/>
+      <c r="AU27" s="110"/>
+      <c r="AV27" s="154"/>
+      <c r="AW27" s="110"/>
       <c r="AX27" s="89"/>
       <c r="AY27" s="89"/>
       <c r="AZ27" s="89"/>
-      <c r="BA27" s="96"/>
+      <c r="BA27" s="89"/>
       <c r="BB27" s="95"/>
-      <c r="BC27" s="89"/>
+      <c r="BC27" s="94"/>
       <c r="BD27" s="89"/>
-      <c r="BE27" s="95"/>
-      <c r="BF27" s="95"/>
+      <c r="BE27" s="89"/>
+      <c r="BF27" s="94"/>
+      <c r="BG27" s="94"/>
     </row>
-    <row r="28" spans="1:58" ht="30" customHeight="1">
+    <row r="28" spans="1:59" ht="30" customHeight="1">
       <c r="A28" s="83"/>
       <c r="B28" s="84"/>
       <c r="C28" s="85"/>
       <c r="D28" s="86"/>
-      <c r="E28" s="143"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="146">
+      <c r="E28" s="110"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="147">
+      <c r="J28" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="145"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="145"/>
-      <c r="N28" s="148"/>
+      <c r="K28" s="112"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="115"/>
       <c r="O28" s="88"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="100"/>
+      <c r="P28" s="98"/>
+      <c r="Q28" s="99"/>
       <c r="R28" s="87"/>
       <c r="S28" s="88"/>
       <c r="T28" s="89"/>
-      <c r="U28" s="100"/>
-      <c r="V28" s="100"/>
-      <c r="W28" s="99"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="99"/>
+      <c r="W28" s="98"/>
       <c r="X28" s="83"/>
       <c r="Y28" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="110">
+      <c r="Z28" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="109">
+      <c r="AA28" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB28" s="91"/>
       <c r="AC28" s="90"/>
       <c r="AD28" s="92"/>
-      <c r="AE28" s="150"/>
-      <c r="AF28" s="151"/>
-      <c r="AG28" s="101">
+      <c r="AE28" s="117"/>
+      <c r="AF28" s="118"/>
+      <c r="AG28" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="102"/>
+      <c r="AH28" s="101"/>
       <c r="AI28" s="88"/>
-      <c r="AJ28" s="152"/>
+      <c r="AJ28" s="119"/>
       <c r="AK28" s="93"/>
       <c r="AL28" s="93"/>
-      <c r="AM28" s="100"/>
-      <c r="AN28" s="100"/>
-      <c r="AO28" s="100"/>
+      <c r="AM28" s="99"/>
+      <c r="AN28" s="99"/>
+      <c r="AO28" s="99"/>
       <c r="AP28" s="83"/>
-      <c r="AQ28" s="94"/>
-      <c r="AR28" s="95"/>
-      <c r="AS28" s="83"/>
-      <c r="AT28" s="83"/>
-      <c r="AU28" s="95"/>
-      <c r="AV28" s="94"/>
-      <c r="AW28" s="95"/>
+      <c r="AQ28" s="154"/>
+      <c r="AR28" s="110"/>
+      <c r="AS28" s="110"/>
+      <c r="AT28" s="110"/>
+      <c r="AU28" s="110"/>
+      <c r="AV28" s="154"/>
+      <c r="AW28" s="110"/>
       <c r="AX28" s="89"/>
       <c r="AY28" s="89"/>
       <c r="AZ28" s="89"/>
-      <c r="BA28" s="96"/>
+      <c r="BA28" s="89"/>
       <c r="BB28" s="95"/>
-      <c r="BC28" s="89"/>
+      <c r="BC28" s="94"/>
       <c r="BD28" s="89"/>
-      <c r="BE28" s="95"/>
-      <c r="BF28" s="95"/>
+      <c r="BE28" s="89"/>
+      <c r="BF28" s="94"/>
+      <c r="BG28" s="94"/>
     </row>
-    <row r="29" spans="1:58" ht="30" customHeight="1">
+    <row r="29" spans="1:59" ht="30" customHeight="1">
       <c r="A29" s="83"/>
       <c r="B29" s="84"/>
       <c r="C29" s="85"/>
       <c r="D29" s="86"/>
-      <c r="E29" s="143"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="146">
+      <c r="E29" s="110"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="147">
+      <c r="J29" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="145"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="145"/>
-      <c r="N29" s="148"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="115"/>
       <c r="O29" s="88"/>
-      <c r="P29" s="99"/>
-      <c r="Q29" s="100"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="99"/>
       <c r="R29" s="87"/>
       <c r="S29" s="88"/>
       <c r="T29" s="89"/>
-      <c r="U29" s="100"/>
-      <c r="V29" s="100"/>
-      <c r="W29" s="99"/>
+      <c r="U29" s="99"/>
+      <c r="V29" s="99"/>
+      <c r="W29" s="98"/>
       <c r="X29" s="83"/>
       <c r="Y29" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="110">
+      <c r="Z29" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="109">
+      <c r="AA29" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB29" s="91"/>
       <c r="AC29" s="90"/>
       <c r="AD29" s="92"/>
-      <c r="AE29" s="150"/>
-      <c r="AF29" s="151"/>
-      <c r="AG29" s="101">
+      <c r="AE29" s="117"/>
+      <c r="AF29" s="118"/>
+      <c r="AG29" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="102"/>
+      <c r="AH29" s="101"/>
       <c r="AI29" s="88"/>
-      <c r="AJ29" s="152"/>
+      <c r="AJ29" s="119"/>
       <c r="AK29" s="93"/>
       <c r="AL29" s="93"/>
-      <c r="AM29" s="100"/>
-      <c r="AN29" s="100"/>
-      <c r="AO29" s="100"/>
+      <c r="AM29" s="99"/>
+      <c r="AN29" s="99"/>
+      <c r="AO29" s="99"/>
       <c r="AP29" s="83"/>
-      <c r="AQ29" s="94"/>
-      <c r="AR29" s="95"/>
-      <c r="AS29" s="83"/>
-      <c r="AT29" s="83"/>
-      <c r="AU29" s="95"/>
-      <c r="AV29" s="94"/>
-      <c r="AW29" s="95"/>
+      <c r="AQ29" s="154"/>
+      <c r="AR29" s="110"/>
+      <c r="AS29" s="110"/>
+      <c r="AT29" s="110"/>
+      <c r="AU29" s="110"/>
+      <c r="AV29" s="154"/>
+      <c r="AW29" s="110"/>
       <c r="AX29" s="89"/>
       <c r="AY29" s="89"/>
       <c r="AZ29" s="89"/>
-      <c r="BA29" s="96"/>
+      <c r="BA29" s="89"/>
       <c r="BB29" s="95"/>
-      <c r="BC29" s="89"/>
+      <c r="BC29" s="94"/>
       <c r="BD29" s="89"/>
-      <c r="BE29" s="95"/>
-      <c r="BF29" s="95"/>
+      <c r="BE29" s="89"/>
+      <c r="BF29" s="94"/>
+      <c r="BG29" s="94"/>
     </row>
-    <row r="30" spans="1:58" ht="30.75" customHeight="1">
+    <row r="30" spans="1:59" ht="30.75" customHeight="1">
       <c r="A30" s="83"/>
       <c r="B30" s="84"/>
       <c r="C30" s="83"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="143"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="149"/>
-      <c r="I30" s="146">
+      <c r="D30" s="96"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="116"/>
+      <c r="I30" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="147">
+      <c r="J30" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="149"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="149"/>
-      <c r="N30" s="148"/>
+      <c r="K30" s="116"/>
+      <c r="L30" s="116"/>
+      <c r="M30" s="116"/>
+      <c r="N30" s="115"/>
       <c r="O30" s="88"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="100"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="99"/>
       <c r="R30" s="87"/>
       <c r="S30" s="88"/>
       <c r="T30" s="89"/>
-      <c r="U30" s="100"/>
-      <c r="V30" s="100"/>
-      <c r="W30" s="99"/>
+      <c r="U30" s="99"/>
+      <c r="V30" s="99"/>
+      <c r="W30" s="98"/>
       <c r="X30" s="83"/>
       <c r="Y30" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="110">
+      <c r="Z30" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="109">
+      <c r="AA30" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB30" s="91"/>
       <c r="AC30" s="90"/>
       <c r="AD30" s="92"/>
-      <c r="AE30" s="153"/>
-      <c r="AF30" s="154"/>
-      <c r="AG30" s="101">
+      <c r="AE30" s="120"/>
+      <c r="AF30" s="121"/>
+      <c r="AG30" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="103"/>
+      <c r="AH30" s="102"/>
       <c r="AI30" s="88"/>
-      <c r="AJ30" s="152"/>
+      <c r="AJ30" s="119"/>
       <c r="AK30" s="93"/>
       <c r="AL30" s="93"/>
-      <c r="AM30" s="100"/>
-      <c r="AN30" s="100"/>
-      <c r="AO30" s="100"/>
+      <c r="AM30" s="99"/>
+      <c r="AN30" s="99"/>
+      <c r="AO30" s="99"/>
       <c r="AP30" s="83"/>
-      <c r="AQ30" s="94"/>
-      <c r="AR30" s="95"/>
-      <c r="AS30" s="83"/>
-      <c r="AT30" s="83"/>
-      <c r="AU30" s="95"/>
-      <c r="AV30" s="94"/>
-      <c r="AW30" s="95"/>
+      <c r="AQ30" s="154"/>
+      <c r="AR30" s="110"/>
+      <c r="AS30" s="110"/>
+      <c r="AT30" s="110"/>
+      <c r="AU30" s="110"/>
+      <c r="AV30" s="154"/>
+      <c r="AW30" s="110"/>
       <c r="AX30" s="89"/>
       <c r="AY30" s="89"/>
       <c r="AZ30" s="89"/>
-      <c r="BA30" s="96"/>
+      <c r="BA30" s="89"/>
       <c r="BB30" s="95"/>
-      <c r="BC30" s="89"/>
+      <c r="BC30" s="94"/>
       <c r="BD30" s="89"/>
-      <c r="BE30" s="95"/>
-      <c r="BF30" s="95"/>
+      <c r="BE30" s="89"/>
+      <c r="BF30" s="94"/>
+      <c r="BG30" s="94"/>
     </row>
-    <row r="31" spans="1:58" ht="30" customHeight="1">
+    <row r="31" spans="1:59" ht="30" customHeight="1">
       <c r="A31" s="83"/>
       <c r="B31" s="84"/>
       <c r="C31" s="83"/>
       <c r="D31" s="86"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="146">
+      <c r="E31" s="110"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J31" s="147">
+      <c r="J31" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K31" s="145"/>
-      <c r="L31" s="145"/>
-      <c r="M31" s="145"/>
-      <c r="N31" s="148"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="115"/>
       <c r="O31" s="88"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="100"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="99"/>
       <c r="R31" s="87"/>
       <c r="S31" s="88"/>
       <c r="T31" s="89"/>
-      <c r="U31" s="100"/>
-      <c r="V31" s="100"/>
-      <c r="W31" s="99"/>
+      <c r="U31" s="99"/>
+      <c r="V31" s="99"/>
+      <c r="W31" s="98"/>
       <c r="X31" s="83"/>
       <c r="Y31" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z31" s="110">
+      <c r="Z31" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="109">
+      <c r="AA31" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB31" s="91"/>
       <c r="AC31" s="90"/>
       <c r="AD31" s="92"/>
-      <c r="AE31" s="153"/>
-      <c r="AF31" s="154"/>
-      <c r="AG31" s="101">
+      <c r="AE31" s="120"/>
+      <c r="AF31" s="121"/>
+      <c r="AG31" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="103"/>
+      <c r="AH31" s="102"/>
       <c r="AI31" s="88"/>
-      <c r="AJ31" s="152"/>
+      <c r="AJ31" s="119"/>
       <c r="AK31" s="93"/>
       <c r="AL31" s="93"/>
-      <c r="AM31" s="100"/>
-      <c r="AN31" s="100"/>
-      <c r="AO31" s="100"/>
+      <c r="AM31" s="99"/>
+      <c r="AN31" s="99"/>
+      <c r="AO31" s="99"/>
       <c r="AP31" s="83"/>
-      <c r="AQ31" s="94"/>
-      <c r="AR31" s="95"/>
-      <c r="AS31" s="83"/>
-      <c r="AT31" s="83"/>
-      <c r="AU31" s="95"/>
-      <c r="AV31" s="94"/>
-      <c r="AW31" s="95"/>
+      <c r="AQ31" s="154"/>
+      <c r="AR31" s="110"/>
+      <c r="AS31" s="110"/>
+      <c r="AT31" s="110"/>
+      <c r="AU31" s="110"/>
+      <c r="AV31" s="154"/>
+      <c r="AW31" s="110"/>
       <c r="AX31" s="89"/>
       <c r="AY31" s="89"/>
       <c r="AZ31" s="89"/>
-      <c r="BA31" s="96"/>
+      <c r="BA31" s="89"/>
       <c r="BB31" s="95"/>
-      <c r="BC31" s="89"/>
+      <c r="BC31" s="94"/>
       <c r="BD31" s="89"/>
-      <c r="BE31" s="95"/>
-      <c r="BF31" s="95"/>
+      <c r="BE31" s="89"/>
+      <c r="BF31" s="94"/>
+      <c r="BG31" s="94"/>
     </row>
-    <row r="32" spans="1:58" ht="30" customHeight="1">
+    <row r="32" spans="1:59" ht="30" customHeight="1">
       <c r="A32" s="83"/>
       <c r="B32" s="84"/>
       <c r="C32" s="83"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="143"/>
-      <c r="F32" s="144"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="146">
+      <c r="D32" s="97"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="112"/>
+      <c r="I32" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="147">
+      <c r="J32" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K32" s="145"/>
-      <c r="L32" s="145"/>
-      <c r="M32" s="145"/>
-      <c r="N32" s="148"/>
+      <c r="K32" s="112"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="115"/>
       <c r="O32" s="88"/>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="100"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="99"/>
       <c r="R32" s="87"/>
       <c r="S32" s="88"/>
       <c r="T32" s="89"/>
-      <c r="U32" s="100"/>
-      <c r="V32" s="100"/>
-      <c r="W32" s="99"/>
+      <c r="U32" s="99"/>
+      <c r="V32" s="99"/>
+      <c r="W32" s="98"/>
       <c r="X32" s="83"/>
       <c r="Y32" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="110">
+      <c r="Z32" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="109">
+      <c r="AA32" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB32" s="91"/>
       <c r="AC32" s="90"/>
       <c r="AD32" s="92"/>
-      <c r="AE32" s="153"/>
-      <c r="AF32" s="154"/>
-      <c r="AG32" s="101">
+      <c r="AE32" s="120"/>
+      <c r="AF32" s="121"/>
+      <c r="AG32" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="103"/>
+      <c r="AH32" s="102"/>
       <c r="AI32" s="88"/>
-      <c r="AJ32" s="152"/>
+      <c r="AJ32" s="119"/>
       <c r="AK32" s="93"/>
       <c r="AL32" s="93"/>
-      <c r="AM32" s="100"/>
-      <c r="AN32" s="100"/>
-      <c r="AO32" s="100"/>
+      <c r="AM32" s="99"/>
+      <c r="AN32" s="99"/>
+      <c r="AO32" s="99"/>
       <c r="AP32" s="83"/>
-      <c r="AQ32" s="94"/>
-      <c r="AR32" s="95"/>
-      <c r="AS32" s="83"/>
-      <c r="AT32" s="83"/>
-      <c r="AU32" s="95"/>
-      <c r="AV32" s="94"/>
-      <c r="AW32" s="95"/>
+      <c r="AQ32" s="154"/>
+      <c r="AR32" s="110"/>
+      <c r="AS32" s="110"/>
+      <c r="AT32" s="110"/>
+      <c r="AU32" s="110"/>
+      <c r="AV32" s="154"/>
+      <c r="AW32" s="110"/>
       <c r="AX32" s="89"/>
       <c r="AY32" s="89"/>
-      <c r="AZ32" s="83"/>
-      <c r="BA32" s="96"/>
+      <c r="AZ32" s="89"/>
+      <c r="BA32" s="83"/>
       <c r="BB32" s="95"/>
-      <c r="BC32" s="89"/>
+      <c r="BC32" s="94"/>
       <c r="BD32" s="89"/>
-      <c r="BE32" s="95"/>
-      <c r="BF32" s="95"/>
+      <c r="BE32" s="89"/>
+      <c r="BF32" s="94"/>
+      <c r="BG32" s="94"/>
     </row>
-    <row r="33" spans="1:58" ht="30" customHeight="1">
+    <row r="33" spans="1:59" ht="30" customHeight="1">
       <c r="A33" s="83"/>
       <c r="B33" s="84"/>
       <c r="C33" s="83"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="143"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="149"/>
-      <c r="I33" s="146">
+      <c r="D33" s="97"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="116"/>
+      <c r="I33" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="147">
+      <c r="J33" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K33" s="149"/>
-      <c r="L33" s="149"/>
-      <c r="M33" s="149"/>
-      <c r="N33" s="148"/>
+      <c r="K33" s="116"/>
+      <c r="L33" s="116"/>
+      <c r="M33" s="116"/>
+      <c r="N33" s="115"/>
       <c r="O33" s="88"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="100"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="99"/>
       <c r="R33" s="87"/>
       <c r="S33" s="88"/>
       <c r="T33" s="89"/>
-      <c r="U33" s="100"/>
-      <c r="V33" s="100"/>
-      <c r="W33" s="99"/>
+      <c r="U33" s="99"/>
+      <c r="V33" s="99"/>
+      <c r="W33" s="98"/>
       <c r="X33" s="83"/>
       <c r="Y33" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="110">
+      <c r="Z33" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="109">
+      <c r="AA33" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB33" s="91"/>
       <c r="AC33" s="90"/>
       <c r="AD33" s="92"/>
-      <c r="AE33" s="153"/>
-      <c r="AF33" s="154"/>
-      <c r="AG33" s="101">
+      <c r="AE33" s="120"/>
+      <c r="AF33" s="121"/>
+      <c r="AG33" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="103"/>
+      <c r="AH33" s="102"/>
       <c r="AI33" s="88"/>
-      <c r="AJ33" s="152"/>
+      <c r="AJ33" s="119"/>
       <c r="AK33" s="93"/>
       <c r="AL33" s="93"/>
-      <c r="AM33" s="100"/>
-      <c r="AN33" s="100"/>
-      <c r="AO33" s="100"/>
+      <c r="AM33" s="99"/>
+      <c r="AN33" s="99"/>
+      <c r="AO33" s="99"/>
       <c r="AP33" s="83"/>
-      <c r="AQ33" s="94"/>
-      <c r="AR33" s="95"/>
-      <c r="AS33" s="83"/>
-      <c r="AT33" s="83"/>
-      <c r="AU33" s="95"/>
-      <c r="AV33" s="94"/>
-      <c r="AW33" s="95"/>
+      <c r="AQ33" s="154"/>
+      <c r="AR33" s="110"/>
+      <c r="AS33" s="110"/>
+      <c r="AT33" s="110"/>
+      <c r="AU33" s="110"/>
+      <c r="AV33" s="154"/>
+      <c r="AW33" s="110"/>
       <c r="AX33" s="89"/>
       <c r="AY33" s="89"/>
-      <c r="AZ33" s="83"/>
-      <c r="BA33" s="96"/>
+      <c r="AZ33" s="89"/>
+      <c r="BA33" s="83"/>
       <c r="BB33" s="95"/>
-      <c r="BC33" s="89"/>
+      <c r="BC33" s="94"/>
       <c r="BD33" s="89"/>
-      <c r="BE33" s="95"/>
-      <c r="BF33" s="95"/>
+      <c r="BE33" s="89"/>
+      <c r="BF33" s="94"/>
+      <c r="BG33" s="94"/>
     </row>
-    <row r="34" spans="1:58" ht="30" customHeight="1">
+    <row r="34" spans="1:59" ht="30" customHeight="1">
       <c r="A34" s="83"/>
       <c r="B34" s="84"/>
       <c r="C34" s="85"/>
       <c r="D34" s="86"/>
-      <c r="E34" s="143"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="143"/>
-      <c r="H34" s="145"/>
-      <c r="I34" s="146">
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="112"/>
+      <c r="I34" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J34" s="147">
+      <c r="J34" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K34" s="145"/>
-      <c r="L34" s="145"/>
-      <c r="M34" s="145"/>
-      <c r="N34" s="148"/>
+      <c r="K34" s="112"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="115"/>
       <c r="O34" s="88"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="100"/>
+      <c r="P34" s="98"/>
+      <c r="Q34" s="99"/>
       <c r="R34" s="87"/>
       <c r="S34" s="88"/>
       <c r="T34" s="89"/>
-      <c r="U34" s="100"/>
-      <c r="V34" s="100"/>
-      <c r="W34" s="99"/>
+      <c r="U34" s="99"/>
+      <c r="V34" s="99"/>
+      <c r="W34" s="98"/>
       <c r="X34" s="83"/>
       <c r="Y34" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z34" s="110">
+      <c r="Z34" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="109">
+      <c r="AA34" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB34" s="91"/>
       <c r="AC34" s="90"/>
       <c r="AD34" s="92"/>
-      <c r="AE34" s="150"/>
-      <c r="AF34" s="151"/>
-      <c r="AG34" s="101">
+      <c r="AE34" s="117"/>
+      <c r="AF34" s="118"/>
+      <c r="AG34" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="102"/>
+      <c r="AH34" s="101"/>
       <c r="AI34" s="88"/>
-      <c r="AJ34" s="152"/>
+      <c r="AJ34" s="119"/>
       <c r="AK34" s="93"/>
       <c r="AL34" s="93"/>
-      <c r="AM34" s="100"/>
-      <c r="AN34" s="100"/>
-      <c r="AO34" s="100"/>
+      <c r="AM34" s="99"/>
+      <c r="AN34" s="99"/>
+      <c r="AO34" s="99"/>
       <c r="AP34" s="83"/>
-      <c r="AQ34" s="94"/>
-      <c r="AR34" s="95"/>
-      <c r="AS34" s="83"/>
-      <c r="AT34" s="83"/>
-      <c r="AU34" s="95"/>
-      <c r="AV34" s="94"/>
-      <c r="AW34" s="95"/>
+      <c r="AQ34" s="154"/>
+      <c r="AR34" s="110"/>
+      <c r="AS34" s="110"/>
+      <c r="AT34" s="110"/>
+      <c r="AU34" s="110"/>
+      <c r="AV34" s="154"/>
+      <c r="AW34" s="110"/>
       <c r="AX34" s="89"/>
       <c r="AY34" s="89"/>
       <c r="AZ34" s="89"/>
-      <c r="BA34" s="96"/>
+      <c r="BA34" s="89"/>
       <c r="BB34" s="95"/>
-      <c r="BC34" s="89"/>
+      <c r="BC34" s="94"/>
       <c r="BD34" s="89"/>
-      <c r="BE34" s="95"/>
-      <c r="BF34" s="95"/>
+      <c r="BE34" s="89"/>
+      <c r="BF34" s="94"/>
+      <c r="BG34" s="94"/>
     </row>
-    <row r="35" spans="1:58" ht="30" customHeight="1">
+    <row r="35" spans="1:59" ht="30" customHeight="1">
       <c r="A35" s="83"/>
       <c r="B35" s="84"/>
       <c r="C35" s="85"/>
       <c r="D35" s="86"/>
-      <c r="E35" s="143"/>
-      <c r="F35" s="144"/>
-      <c r="G35" s="143"/>
-      <c r="H35" s="145"/>
-      <c r="I35" s="146">
+      <c r="E35" s="110"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="112"/>
+      <c r="I35" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="147">
+      <c r="J35" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K35" s="145"/>
-      <c r="L35" s="145"/>
-      <c r="M35" s="145"/>
-      <c r="N35" s="148"/>
+      <c r="K35" s="112"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="115"/>
       <c r="O35" s="88"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="100"/>
+      <c r="P35" s="98"/>
+      <c r="Q35" s="99"/>
       <c r="R35" s="87"/>
       <c r="S35" s="88"/>
       <c r="T35" s="89"/>
-      <c r="U35" s="100"/>
-      <c r="V35" s="100"/>
-      <c r="W35" s="99"/>
+      <c r="U35" s="99"/>
+      <c r="V35" s="99"/>
+      <c r="W35" s="98"/>
       <c r="X35" s="83"/>
       <c r="Y35" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="110">
+      <c r="Z35" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA35" s="109">
+      <c r="AA35" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB35" s="91"/>
       <c r="AC35" s="90"/>
       <c r="AD35" s="92"/>
-      <c r="AE35" s="150"/>
-      <c r="AF35" s="151"/>
-      <c r="AG35" s="101">
+      <c r="AE35" s="117"/>
+      <c r="AF35" s="118"/>
+      <c r="AG35" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="102"/>
+      <c r="AH35" s="101"/>
       <c r="AI35" s="88"/>
-      <c r="AJ35" s="152"/>
+      <c r="AJ35" s="119"/>
       <c r="AK35" s="93"/>
       <c r="AL35" s="93"/>
-      <c r="AM35" s="100"/>
-      <c r="AN35" s="100"/>
-      <c r="AO35" s="100"/>
+      <c r="AM35" s="99"/>
+      <c r="AN35" s="99"/>
+      <c r="AO35" s="99"/>
       <c r="AP35" s="83"/>
-      <c r="AQ35" s="94"/>
-      <c r="AR35" s="95"/>
-      <c r="AS35" s="83"/>
-      <c r="AT35" s="83"/>
-      <c r="AU35" s="95"/>
-      <c r="AV35" s="94"/>
-      <c r="AW35" s="95"/>
+      <c r="AQ35" s="154"/>
+      <c r="AR35" s="110"/>
+      <c r="AS35" s="110"/>
+      <c r="AT35" s="110"/>
+      <c r="AU35" s="110"/>
+      <c r="AV35" s="154"/>
+      <c r="AW35" s="110"/>
       <c r="AX35" s="89"/>
       <c r="AY35" s="89"/>
       <c r="AZ35" s="89"/>
-      <c r="BA35" s="96"/>
+      <c r="BA35" s="89"/>
       <c r="BB35" s="95"/>
-      <c r="BC35" s="89"/>
+      <c r="BC35" s="94"/>
       <c r="BD35" s="89"/>
-      <c r="BE35" s="95"/>
-      <c r="BF35" s="95"/>
+      <c r="BE35" s="89"/>
+      <c r="BF35" s="94"/>
+      <c r="BG35" s="94"/>
     </row>
-    <row r="36" spans="1:58" ht="30" customHeight="1">
+    <row r="36" spans="1:59" ht="30" customHeight="1">
       <c r="A36" s="83"/>
       <c r="B36" s="84"/>
       <c r="C36" s="85"/>
       <c r="D36" s="86"/>
-      <c r="E36" s="143"/>
-      <c r="F36" s="144"/>
-      <c r="G36" s="143"/>
-      <c r="H36" s="145"/>
-      <c r="I36" s="146">
+      <c r="E36" s="110"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="110"/>
+      <c r="H36" s="112"/>
+      <c r="I36" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="147">
+      <c r="J36" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="145"/>
-      <c r="N36" s="148"/>
+      <c r="K36" s="112"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="115"/>
       <c r="O36" s="88"/>
-      <c r="P36" s="99"/>
-      <c r="Q36" s="100"/>
+      <c r="P36" s="98"/>
+      <c r="Q36" s="99"/>
       <c r="R36" s="87"/>
       <c r="S36" s="88"/>
       <c r="T36" s="89"/>
-      <c r="U36" s="100"/>
-      <c r="V36" s="100"/>
-      <c r="W36" s="99"/>
+      <c r="U36" s="99"/>
+      <c r="V36" s="99"/>
+      <c r="W36" s="98"/>
       <c r="X36" s="83"/>
       <c r="Y36" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="110">
+      <c r="Z36" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="109">
+      <c r="AA36" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB36" s="91"/>
       <c r="AC36" s="90"/>
       <c r="AD36" s="92"/>
-      <c r="AE36" s="150"/>
-      <c r="AF36" s="151"/>
-      <c r="AG36" s="101">
+      <c r="AE36" s="117"/>
+      <c r="AF36" s="118"/>
+      <c r="AG36" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="102"/>
+      <c r="AH36" s="101"/>
       <c r="AI36" s="88"/>
-      <c r="AJ36" s="152"/>
+      <c r="AJ36" s="119"/>
       <c r="AK36" s="93"/>
       <c r="AL36" s="93"/>
-      <c r="AM36" s="100"/>
-      <c r="AN36" s="100"/>
-      <c r="AO36" s="100"/>
+      <c r="AM36" s="99"/>
+      <c r="AN36" s="99"/>
+      <c r="AO36" s="99"/>
       <c r="AP36" s="83"/>
-      <c r="AQ36" s="94"/>
-      <c r="AR36" s="95"/>
-      <c r="AS36" s="83"/>
-      <c r="AT36" s="83"/>
-      <c r="AU36" s="95"/>
-      <c r="AV36" s="94"/>
-      <c r="AW36" s="95"/>
+      <c r="AQ36" s="154"/>
+      <c r="AR36" s="110"/>
+      <c r="AS36" s="110"/>
+      <c r="AT36" s="110"/>
+      <c r="AU36" s="110"/>
+      <c r="AV36" s="154"/>
+      <c r="AW36" s="110"/>
       <c r="AX36" s="89"/>
       <c r="AY36" s="89"/>
       <c r="AZ36" s="89"/>
-      <c r="BA36" s="96"/>
+      <c r="BA36" s="89"/>
       <c r="BB36" s="95"/>
-      <c r="BC36" s="89"/>
+      <c r="BC36" s="94"/>
       <c r="BD36" s="89"/>
-      <c r="BE36" s="95"/>
-      <c r="BF36" s="95"/>
+      <c r="BE36" s="89"/>
+      <c r="BF36" s="94"/>
+      <c r="BG36" s="94"/>
     </row>
-    <row r="37" spans="1:58" ht="30" customHeight="1">
+    <row r="37" spans="1:59" ht="30" customHeight="1">
       <c r="A37" s="83"/>
       <c r="B37" s="84"/>
       <c r="C37" s="85"/>
       <c r="D37" s="86"/>
-      <c r="E37" s="143"/>
-      <c r="F37" s="144"/>
-      <c r="G37" s="143"/>
-      <c r="H37" s="145"/>
-      <c r="I37" s="146">
+      <c r="E37" s="110"/>
+      <c r="F37" s="111"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="112"/>
+      <c r="I37" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J37" s="147">
+      <c r="J37" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K37" s="145"/>
-      <c r="L37" s="145"/>
-      <c r="M37" s="145"/>
-      <c r="N37" s="148"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="115"/>
       <c r="O37" s="88"/>
-      <c r="P37" s="99"/>
-      <c r="Q37" s="100"/>
+      <c r="P37" s="98"/>
+      <c r="Q37" s="99"/>
       <c r="R37" s="87"/>
       <c r="S37" s="88"/>
       <c r="T37" s="89"/>
-      <c r="U37" s="100"/>
-      <c r="V37" s="100"/>
-      <c r="W37" s="99"/>
+      <c r="U37" s="99"/>
+      <c r="V37" s="99"/>
+      <c r="W37" s="98"/>
       <c r="X37" s="83"/>
       <c r="Y37" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="110">
+      <c r="Z37" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="109">
+      <c r="AA37" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB37" s="91"/>
       <c r="AC37" s="90"/>
       <c r="AD37" s="92"/>
-      <c r="AE37" s="150"/>
-      <c r="AF37" s="151"/>
-      <c r="AG37" s="101">
+      <c r="AE37" s="117"/>
+      <c r="AF37" s="118"/>
+      <c r="AG37" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="102"/>
+      <c r="AH37" s="101"/>
       <c r="AI37" s="88"/>
-      <c r="AJ37" s="152"/>
+      <c r="AJ37" s="119"/>
       <c r="AK37" s="93"/>
       <c r="AL37" s="93"/>
-      <c r="AM37" s="100"/>
-      <c r="AN37" s="100"/>
-      <c r="AO37" s="100"/>
+      <c r="AM37" s="99"/>
+      <c r="AN37" s="99"/>
+      <c r="AO37" s="99"/>
       <c r="AP37" s="83"/>
-      <c r="AQ37" s="94"/>
-      <c r="AR37" s="95"/>
-      <c r="AS37" s="83"/>
-      <c r="AT37" s="83"/>
-      <c r="AU37" s="95"/>
-      <c r="AV37" s="94"/>
-      <c r="AW37" s="95"/>
+      <c r="AQ37" s="154"/>
+      <c r="AR37" s="110"/>
+      <c r="AS37" s="110"/>
+      <c r="AT37" s="110"/>
+      <c r="AU37" s="110"/>
+      <c r="AV37" s="154"/>
+      <c r="AW37" s="110"/>
       <c r="AX37" s="89"/>
       <c r="AY37" s="89"/>
       <c r="AZ37" s="89"/>
-      <c r="BA37" s="96"/>
+      <c r="BA37" s="89"/>
       <c r="BB37" s="95"/>
-      <c r="BC37" s="89"/>
+      <c r="BC37" s="94"/>
       <c r="BD37" s="89"/>
-      <c r="BE37" s="95"/>
-      <c r="BF37" s="95"/>
+      <c r="BE37" s="89"/>
+      <c r="BF37" s="94"/>
+      <c r="BG37" s="94"/>
     </row>
-    <row r="38" spans="1:58" ht="30" customHeight="1">
+    <row r="38" spans="1:59" ht="30" customHeight="1">
       <c r="A38" s="83"/>
       <c r="B38" s="84"/>
       <c r="C38" s="85"/>
       <c r="D38" s="86"/>
-      <c r="E38" s="143"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="143"/>
-      <c r="H38" s="145"/>
-      <c r="I38" s="146">
+      <c r="E38" s="110"/>
+      <c r="F38" s="111"/>
+      <c r="G38" s="110"/>
+      <c r="H38" s="112"/>
+      <c r="I38" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J38" s="147">
+      <c r="J38" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K38" s="145"/>
-      <c r="L38" s="145"/>
-      <c r="M38" s="145"/>
-      <c r="N38" s="148"/>
+      <c r="K38" s="112"/>
+      <c r="L38" s="112"/>
+      <c r="M38" s="112"/>
+      <c r="N38" s="115"/>
       <c r="O38" s="88"/>
-      <c r="P38" s="99"/>
-      <c r="Q38" s="100"/>
+      <c r="P38" s="98"/>
+      <c r="Q38" s="99"/>
       <c r="R38" s="87"/>
       <c r="S38" s="88"/>
       <c r="T38" s="89"/>
-      <c r="U38" s="100"/>
-      <c r="V38" s="100"/>
-      <c r="W38" s="99"/>
+      <c r="U38" s="99"/>
+      <c r="V38" s="99"/>
+      <c r="W38" s="98"/>
       <c r="X38" s="83"/>
       <c r="Y38" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z38" s="110">
+      <c r="Z38" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA38" s="109">
+      <c r="AA38" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB38" s="91"/>
       <c r="AC38" s="90"/>
       <c r="AD38" s="92"/>
-      <c r="AE38" s="150"/>
-      <c r="AF38" s="151"/>
-      <c r="AG38" s="101">
+      <c r="AE38" s="117"/>
+      <c r="AF38" s="118"/>
+      <c r="AG38" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="102"/>
+      <c r="AH38" s="101"/>
       <c r="AI38" s="88"/>
-      <c r="AJ38" s="152"/>
+      <c r="AJ38" s="119"/>
       <c r="AK38" s="93"/>
       <c r="AL38" s="93"/>
-      <c r="AM38" s="100"/>
-      <c r="AN38" s="100"/>
-      <c r="AO38" s="100"/>
+      <c r="AM38" s="99"/>
+      <c r="AN38" s="99"/>
+      <c r="AO38" s="99"/>
       <c r="AP38" s="83"/>
-      <c r="AQ38" s="94"/>
-      <c r="AR38" s="95"/>
-      <c r="AS38" s="83"/>
-      <c r="AT38" s="83"/>
-      <c r="AU38" s="95"/>
-      <c r="AV38" s="94"/>
-      <c r="AW38" s="95"/>
+      <c r="AQ38" s="154"/>
+      <c r="AR38" s="110"/>
+      <c r="AS38" s="110"/>
+      <c r="AT38" s="110"/>
+      <c r="AU38" s="110"/>
+      <c r="AV38" s="154"/>
+      <c r="AW38" s="110"/>
       <c r="AX38" s="89"/>
       <c r="AY38" s="89"/>
       <c r="AZ38" s="89"/>
-      <c r="BA38" s="96"/>
+      <c r="BA38" s="89"/>
       <c r="BB38" s="95"/>
-      <c r="BC38" s="89"/>
+      <c r="BC38" s="94"/>
       <c r="BD38" s="89"/>
-      <c r="BE38" s="95"/>
-      <c r="BF38" s="95"/>
+      <c r="BE38" s="89"/>
+      <c r="BF38" s="94"/>
+      <c r="BG38" s="94"/>
     </row>
-    <row r="39" spans="1:58" ht="30" customHeight="1">
+    <row r="39" spans="1:59" ht="30" customHeight="1">
       <c r="A39" s="83"/>
       <c r="B39" s="84"/>
       <c r="C39" s="85"/>
       <c r="D39" s="86"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="145"/>
-      <c r="I39" s="146">
+      <c r="E39" s="110"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="112"/>
+      <c r="I39" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J39" s="147">
+      <c r="J39" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K39" s="145"/>
-      <c r="L39" s="145"/>
-      <c r="M39" s="145"/>
-      <c r="N39" s="148"/>
+      <c r="K39" s="112"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="115"/>
       <c r="O39" s="88"/>
-      <c r="P39" s="99"/>
-      <c r="Q39" s="100"/>
+      <c r="P39" s="98"/>
+      <c r="Q39" s="99"/>
       <c r="R39" s="87"/>
       <c r="S39" s="88"/>
       <c r="T39" s="89"/>
-      <c r="U39" s="100"/>
-      <c r="V39" s="100"/>
-      <c r="W39" s="99"/>
+      <c r="U39" s="99"/>
+      <c r="V39" s="99"/>
+      <c r="W39" s="98"/>
       <c r="X39" s="83"/>
       <c r="Y39" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z39" s="110">
+      <c r="Z39" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA39" s="109">
+      <c r="AA39" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB39" s="91"/>
       <c r="AC39" s="90"/>
       <c r="AD39" s="92"/>
-      <c r="AE39" s="150"/>
-      <c r="AF39" s="151"/>
-      <c r="AG39" s="101">
+      <c r="AE39" s="117"/>
+      <c r="AF39" s="118"/>
+      <c r="AG39" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="102"/>
+      <c r="AH39" s="101"/>
       <c r="AI39" s="88"/>
-      <c r="AJ39" s="152"/>
+      <c r="AJ39" s="119"/>
       <c r="AK39" s="93"/>
       <c r="AL39" s="93"/>
-      <c r="AM39" s="100"/>
-      <c r="AN39" s="100"/>
-      <c r="AO39" s="100"/>
+      <c r="AM39" s="99"/>
+      <c r="AN39" s="99"/>
+      <c r="AO39" s="99"/>
       <c r="AP39" s="83"/>
-      <c r="AQ39" s="94"/>
-      <c r="AR39" s="95"/>
-      <c r="AS39" s="83"/>
-      <c r="AT39" s="83"/>
-      <c r="AU39" s="95"/>
-      <c r="AV39" s="94"/>
-      <c r="AW39" s="95"/>
+      <c r="AQ39" s="154"/>
+      <c r="AR39" s="110"/>
+      <c r="AS39" s="110"/>
+      <c r="AT39" s="110"/>
+      <c r="AU39" s="110"/>
+      <c r="AV39" s="154"/>
+      <c r="AW39" s="110"/>
       <c r="AX39" s="89"/>
       <c r="AY39" s="89"/>
       <c r="AZ39" s="89"/>
-      <c r="BA39" s="96"/>
+      <c r="BA39" s="89"/>
       <c r="BB39" s="95"/>
-      <c r="BC39" s="89"/>
+      <c r="BC39" s="94"/>
       <c r="BD39" s="89"/>
-      <c r="BE39" s="95"/>
-      <c r="BF39" s="95"/>
+      <c r="BE39" s="89"/>
+      <c r="BF39" s="94"/>
+      <c r="BG39" s="94"/>
     </row>
-    <row r="40" spans="1:58" ht="30" customHeight="1">
+    <row r="40" spans="1:59" ht="30" customHeight="1">
       <c r="A40" s="83"/>
       <c r="B40" s="84"/>
       <c r="C40" s="85"/>
       <c r="D40" s="86"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="144"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="145"/>
-      <c r="I40" s="146">
+      <c r="E40" s="110"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="112"/>
+      <c r="I40" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J40" s="147">
+      <c r="J40" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K40" s="145"/>
-      <c r="L40" s="145"/>
-      <c r="M40" s="145"/>
-      <c r="N40" s="148"/>
+      <c r="K40" s="112"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="115"/>
       <c r="O40" s="88"/>
-      <c r="P40" s="99"/>
-      <c r="Q40" s="100"/>
+      <c r="P40" s="98"/>
+      <c r="Q40" s="99"/>
       <c r="R40" s="87"/>
       <c r="S40" s="88"/>
       <c r="T40" s="89"/>
-      <c r="U40" s="100"/>
-      <c r="V40" s="100"/>
-      <c r="W40" s="99"/>
+      <c r="U40" s="99"/>
+      <c r="V40" s="99"/>
+      <c r="W40" s="98"/>
       <c r="X40" s="83"/>
       <c r="Y40" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z40" s="110">
+      <c r="Z40" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA40" s="109">
+      <c r="AA40" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB40" s="91"/>
       <c r="AC40" s="90"/>
       <c r="AD40" s="92"/>
-      <c r="AE40" s="150"/>
-      <c r="AF40" s="151"/>
-      <c r="AG40" s="101">
+      <c r="AE40" s="117"/>
+      <c r="AF40" s="118"/>
+      <c r="AG40" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="102"/>
+      <c r="AH40" s="101"/>
       <c r="AI40" s="88"/>
-      <c r="AJ40" s="152"/>
+      <c r="AJ40" s="119"/>
       <c r="AK40" s="93"/>
       <c r="AL40" s="93"/>
-      <c r="AM40" s="100"/>
-      <c r="AN40" s="100"/>
-      <c r="AO40" s="100"/>
+      <c r="AM40" s="99"/>
+      <c r="AN40" s="99"/>
+      <c r="AO40" s="99"/>
       <c r="AP40" s="83"/>
-      <c r="AQ40" s="94"/>
-      <c r="AR40" s="95"/>
-      <c r="AS40" s="83"/>
-      <c r="AT40" s="83"/>
-      <c r="AU40" s="95"/>
-      <c r="AV40" s="94"/>
-      <c r="AW40" s="95"/>
+      <c r="AQ40" s="154"/>
+      <c r="AR40" s="110"/>
+      <c r="AS40" s="110"/>
+      <c r="AT40" s="110"/>
+      <c r="AU40" s="110"/>
+      <c r="AV40" s="154"/>
+      <c r="AW40" s="110"/>
       <c r="AX40" s="89"/>
       <c r="AY40" s="89"/>
       <c r="AZ40" s="89"/>
-      <c r="BA40" s="96"/>
+      <c r="BA40" s="89"/>
       <c r="BB40" s="95"/>
-      <c r="BC40" s="89"/>
+      <c r="BC40" s="94"/>
       <c r="BD40" s="89"/>
-      <c r="BE40" s="95"/>
-      <c r="BF40" s="95"/>
+      <c r="BE40" s="89"/>
+      <c r="BF40" s="94"/>
+      <c r="BG40" s="94"/>
     </row>
-    <row r="41" spans="1:58" ht="30" customHeight="1">
+    <row r="41" spans="1:59" ht="30" customHeight="1">
       <c r="A41" s="83"/>
       <c r="B41" s="84"/>
       <c r="C41" s="85"/>
       <c r="D41" s="86"/>
-      <c r="E41" s="143"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="143"/>
-      <c r="H41" s="145"/>
-      <c r="I41" s="146">
+      <c r="E41" s="110"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="110"/>
+      <c r="H41" s="112"/>
+      <c r="I41" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J41" s="147">
+      <c r="J41" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K41" s="145"/>
-      <c r="L41" s="145"/>
-      <c r="M41" s="145"/>
-      <c r="N41" s="148"/>
+      <c r="K41" s="112"/>
+      <c r="L41" s="112"/>
+      <c r="M41" s="112"/>
+      <c r="N41" s="115"/>
       <c r="O41" s="88"/>
-      <c r="P41" s="99"/>
-      <c r="Q41" s="100"/>
+      <c r="P41" s="98"/>
+      <c r="Q41" s="99"/>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="89"/>
-      <c r="U41" s="100"/>
-      <c r="V41" s="100"/>
-      <c r="W41" s="99"/>
+      <c r="U41" s="99"/>
+      <c r="V41" s="99"/>
+      <c r="W41" s="98"/>
       <c r="X41" s="83"/>
       <c r="Y41" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z41" s="110">
+      <c r="Z41" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA41" s="109">
+      <c r="AA41" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB41" s="91"/>
       <c r="AC41" s="90"/>
       <c r="AD41" s="92"/>
-      <c r="AE41" s="150"/>
-      <c r="AF41" s="151"/>
-      <c r="AG41" s="101">
+      <c r="AE41" s="117"/>
+      <c r="AF41" s="118"/>
+      <c r="AG41" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="102"/>
+      <c r="AH41" s="101"/>
       <c r="AI41" s="88"/>
-      <c r="AJ41" s="152"/>
+      <c r="AJ41" s="119"/>
       <c r="AK41" s="93"/>
       <c r="AL41" s="93"/>
-      <c r="AM41" s="100"/>
-      <c r="AN41" s="100"/>
-      <c r="AO41" s="100"/>
+      <c r="AM41" s="99"/>
+      <c r="AN41" s="99"/>
+      <c r="AO41" s="99"/>
       <c r="AP41" s="83"/>
-      <c r="AQ41" s="94"/>
-      <c r="AR41" s="95"/>
-      <c r="AS41" s="83"/>
-      <c r="AT41" s="83"/>
-      <c r="AU41" s="95"/>
-      <c r="AV41" s="94"/>
-      <c r="AW41" s="95"/>
+      <c r="AQ41" s="154"/>
+      <c r="AR41" s="110"/>
+      <c r="AS41" s="110"/>
+      <c r="AT41" s="110"/>
+      <c r="AU41" s="110"/>
+      <c r="AV41" s="154"/>
+      <c r="AW41" s="110"/>
       <c r="AX41" s="89"/>
       <c r="AY41" s="89"/>
       <c r="AZ41" s="89"/>
-      <c r="BA41" s="96"/>
+      <c r="BA41" s="89"/>
       <c r="BB41" s="95"/>
-      <c r="BC41" s="89"/>
+      <c r="BC41" s="94"/>
       <c r="BD41" s="89"/>
-      <c r="BE41" s="95"/>
-      <c r="BF41" s="95"/>
+      <c r="BE41" s="89"/>
+      <c r="BF41" s="94"/>
+      <c r="BG41" s="94"/>
     </row>
-    <row r="42" spans="1:58" ht="30.75" customHeight="1">
+    <row r="42" spans="1:59" ht="30.75" customHeight="1">
       <c r="A42" s="83"/>
       <c r="B42" s="84"/>
       <c r="C42" s="83"/>
-      <c r="D42" s="97"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="144"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="146">
+      <c r="D42" s="96"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="110"/>
+      <c r="H42" s="116"/>
+      <c r="I42" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J42" s="147">
+      <c r="J42" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K42" s="149"/>
-      <c r="L42" s="149"/>
-      <c r="M42" s="149"/>
-      <c r="N42" s="148"/>
+      <c r="K42" s="116"/>
+      <c r="L42" s="116"/>
+      <c r="M42" s="116"/>
+      <c r="N42" s="115"/>
       <c r="O42" s="88"/>
-      <c r="P42" s="99"/>
-      <c r="Q42" s="100"/>
+      <c r="P42" s="98"/>
+      <c r="Q42" s="99"/>
       <c r="R42" s="87"/>
       <c r="S42" s="88"/>
       <c r="T42" s="89"/>
-      <c r="U42" s="100"/>
-      <c r="V42" s="100"/>
-      <c r="W42" s="99"/>
+      <c r="U42" s="99"/>
+      <c r="V42" s="99"/>
+      <c r="W42" s="98"/>
       <c r="X42" s="83"/>
       <c r="Y42" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z42" s="110">
+      <c r="Z42" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="109">
+      <c r="AA42" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB42" s="91"/>
       <c r="AC42" s="90"/>
       <c r="AD42" s="92"/>
-      <c r="AE42" s="153"/>
-      <c r="AF42" s="154"/>
-      <c r="AG42" s="101">
+      <c r="AE42" s="120"/>
+      <c r="AF42" s="121"/>
+      <c r="AG42" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH42" s="103"/>
+      <c r="AH42" s="102"/>
       <c r="AI42" s="88"/>
-      <c r="AJ42" s="152"/>
+      <c r="AJ42" s="119"/>
       <c r="AK42" s="93"/>
       <c r="AL42" s="93"/>
-      <c r="AM42" s="100"/>
-      <c r="AN42" s="100"/>
-      <c r="AO42" s="100"/>
+      <c r="AM42" s="99"/>
+      <c r="AN42" s="99"/>
+      <c r="AO42" s="99"/>
       <c r="AP42" s="83"/>
-      <c r="AQ42" s="94"/>
-      <c r="AR42" s="95"/>
-      <c r="AS42" s="83"/>
-      <c r="AT42" s="83"/>
-      <c r="AU42" s="95"/>
-      <c r="AV42" s="94"/>
-      <c r="AW42" s="95"/>
+      <c r="AQ42" s="154"/>
+      <c r="AR42" s="110"/>
+      <c r="AS42" s="110"/>
+      <c r="AT42" s="110"/>
+      <c r="AU42" s="110"/>
+      <c r="AV42" s="154"/>
+      <c r="AW42" s="110"/>
       <c r="AX42" s="89"/>
       <c r="AY42" s="89"/>
       <c r="AZ42" s="89"/>
-      <c r="BA42" s="96"/>
+      <c r="BA42" s="89"/>
       <c r="BB42" s="95"/>
-      <c r="BC42" s="89"/>
+      <c r="BC42" s="94"/>
       <c r="BD42" s="89"/>
-      <c r="BE42" s="95"/>
-      <c r="BF42" s="95"/>
+      <c r="BE42" s="89"/>
+      <c r="BF42" s="94"/>
+      <c r="BG42" s="94"/>
     </row>
-    <row r="43" spans="1:58" ht="30" customHeight="1">
+    <row r="43" spans="1:59" ht="30" customHeight="1">
       <c r="A43" s="83"/>
       <c r="B43" s="84"/>
       <c r="C43" s="83"/>
       <c r="D43" s="86"/>
-      <c r="E43" s="143"/>
-      <c r="F43" s="144"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="145"/>
-      <c r="I43" s="146">
+      <c r="E43" s="110"/>
+      <c r="F43" s="111"/>
+      <c r="G43" s="110"/>
+      <c r="H43" s="112"/>
+      <c r="I43" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J43" s="147">
+      <c r="J43" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K43" s="145"/>
-      <c r="L43" s="145"/>
-      <c r="M43" s="145"/>
-      <c r="N43" s="148"/>
+      <c r="K43" s="112"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="115"/>
       <c r="O43" s="88"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="100"/>
+      <c r="P43" s="98"/>
+      <c r="Q43" s="99"/>
       <c r="R43" s="87"/>
       <c r="S43" s="88"/>
       <c r="T43" s="89"/>
-      <c r="U43" s="100"/>
-      <c r="V43" s="100"/>
-      <c r="W43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="98"/>
       <c r="X43" s="83"/>
       <c r="Y43" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z43" s="110">
+      <c r="Z43" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA43" s="109">
+      <c r="AA43" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB43" s="91"/>
       <c r="AC43" s="90"/>
       <c r="AD43" s="92"/>
-      <c r="AE43" s="153"/>
-      <c r="AF43" s="154"/>
-      <c r="AG43" s="101">
+      <c r="AE43" s="120"/>
+      <c r="AF43" s="121"/>
+      <c r="AG43" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="103"/>
+      <c r="AH43" s="102"/>
       <c r="AI43" s="88"/>
-      <c r="AJ43" s="152"/>
+      <c r="AJ43" s="119"/>
       <c r="AK43" s="93"/>
       <c r="AL43" s="93"/>
-      <c r="AM43" s="100"/>
-      <c r="AN43" s="100"/>
-      <c r="AO43" s="100"/>
+      <c r="AM43" s="99"/>
+      <c r="AN43" s="99"/>
+      <c r="AO43" s="99"/>
       <c r="AP43" s="83"/>
-      <c r="AQ43" s="94"/>
-      <c r="AR43" s="95"/>
-      <c r="AS43" s="83"/>
-      <c r="AT43" s="83"/>
-      <c r="AU43" s="95"/>
-      <c r="AV43" s="94"/>
-      <c r="AW43" s="95"/>
+      <c r="AQ43" s="154"/>
+      <c r="AR43" s="110"/>
+      <c r="AS43" s="110"/>
+      <c r="AT43" s="110"/>
+      <c r="AU43" s="110"/>
+      <c r="AV43" s="154"/>
+      <c r="AW43" s="110"/>
       <c r="AX43" s="89"/>
       <c r="AY43" s="89"/>
       <c r="AZ43" s="89"/>
-      <c r="BA43" s="96"/>
+      <c r="BA43" s="89"/>
       <c r="BB43" s="95"/>
-      <c r="BC43" s="89"/>
+      <c r="BC43" s="94"/>
       <c r="BD43" s="89"/>
-      <c r="BE43" s="95"/>
-      <c r="BF43" s="95"/>
+      <c r="BE43" s="89"/>
+      <c r="BF43" s="94"/>
+      <c r="BG43" s="94"/>
     </row>
-    <row r="44" spans="1:58" ht="30" customHeight="1">
+    <row r="44" spans="1:59" ht="30" customHeight="1">
       <c r="A44" s="83"/>
       <c r="B44" s="84"/>
       <c r="C44" s="83"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="143"/>
-      <c r="F44" s="144"/>
-      <c r="G44" s="143"/>
-      <c r="H44" s="145"/>
-      <c r="I44" s="146">
+      <c r="D44" s="97"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="110"/>
+      <c r="H44" s="112"/>
+      <c r="I44" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J44" s="147">
+      <c r="J44" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K44" s="145"/>
-      <c r="L44" s="145"/>
-      <c r="M44" s="145"/>
-      <c r="N44" s="148"/>
+      <c r="K44" s="112"/>
+      <c r="L44" s="112"/>
+      <c r="M44" s="112"/>
+      <c r="N44" s="115"/>
       <c r="O44" s="88"/>
-      <c r="P44" s="99"/>
-      <c r="Q44" s="100"/>
+      <c r="P44" s="98"/>
+      <c r="Q44" s="99"/>
       <c r="R44" s="87"/>
       <c r="S44" s="88"/>
       <c r="T44" s="89"/>
-      <c r="U44" s="100"/>
-      <c r="V44" s="100"/>
-      <c r="W44" s="99"/>
+      <c r="U44" s="99"/>
+      <c r="V44" s="99"/>
+      <c r="W44" s="98"/>
       <c r="X44" s="83"/>
       <c r="Y44" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z44" s="110">
+      <c r="Z44" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA44" s="109">
+      <c r="AA44" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB44" s="91"/>
       <c r="AC44" s="90"/>
       <c r="AD44" s="92"/>
-      <c r="AE44" s="153"/>
-      <c r="AF44" s="154"/>
-      <c r="AG44" s="101">
+      <c r="AE44" s="120"/>
+      <c r="AF44" s="121"/>
+      <c r="AG44" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH44" s="103"/>
+      <c r="AH44" s="102"/>
       <c r="AI44" s="88"/>
-      <c r="AJ44" s="152"/>
+      <c r="AJ44" s="119"/>
       <c r="AK44" s="93"/>
       <c r="AL44" s="93"/>
-      <c r="AM44" s="100"/>
-      <c r="AN44" s="100"/>
-      <c r="AO44" s="100"/>
+      <c r="AM44" s="99"/>
+      <c r="AN44" s="99"/>
+      <c r="AO44" s="99"/>
       <c r="AP44" s="83"/>
-      <c r="AQ44" s="94"/>
-      <c r="AR44" s="95"/>
-      <c r="AS44" s="83"/>
-      <c r="AT44" s="83"/>
-      <c r="AU44" s="95"/>
-      <c r="AV44" s="94"/>
-      <c r="AW44" s="95"/>
+      <c r="AQ44" s="154"/>
+      <c r="AR44" s="110"/>
+      <c r="AS44" s="110"/>
+      <c r="AT44" s="110"/>
+      <c r="AU44" s="110"/>
+      <c r="AV44" s="154"/>
+      <c r="AW44" s="110"/>
       <c r="AX44" s="89"/>
       <c r="AY44" s="89"/>
-      <c r="AZ44" s="83"/>
-      <c r="BA44" s="96"/>
+      <c r="AZ44" s="89"/>
+      <c r="BA44" s="83"/>
       <c r="BB44" s="95"/>
-      <c r="BC44" s="89"/>
+      <c r="BC44" s="94"/>
       <c r="BD44" s="89"/>
-      <c r="BE44" s="95"/>
-      <c r="BF44" s="95"/>
+      <c r="BE44" s="89"/>
+      <c r="BF44" s="94"/>
+      <c r="BG44" s="94"/>
     </row>
-    <row r="45" spans="1:58" ht="30" customHeight="1">
+    <row r="45" spans="1:59" ht="30" customHeight="1">
       <c r="A45" s="83"/>
       <c r="B45" s="84"/>
       <c r="C45" s="83"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="143"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="143"/>
-      <c r="H45" s="149"/>
-      <c r="I45" s="146">
+      <c r="D45" s="97"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="111"/>
+      <c r="G45" s="110"/>
+      <c r="H45" s="116"/>
+      <c r="I45" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J45" s="147">
+      <c r="J45" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K45" s="149"/>
-      <c r="L45" s="149"/>
-      <c r="M45" s="149"/>
-      <c r="N45" s="148"/>
+      <c r="K45" s="116"/>
+      <c r="L45" s="116"/>
+      <c r="M45" s="116"/>
+      <c r="N45" s="115"/>
       <c r="O45" s="88"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="100"/>
+      <c r="P45" s="98"/>
+      <c r="Q45" s="99"/>
       <c r="R45" s="87"/>
       <c r="S45" s="88"/>
       <c r="T45" s="89"/>
-      <c r="U45" s="100"/>
-      <c r="V45" s="100"/>
-      <c r="W45" s="99"/>
+      <c r="U45" s="99"/>
+      <c r="V45" s="99"/>
+      <c r="W45" s="98"/>
       <c r="X45" s="83"/>
       <c r="Y45" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z45" s="110">
+      <c r="Z45" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA45" s="109">
+      <c r="AA45" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB45" s="91"/>
       <c r="AC45" s="90"/>
       <c r="AD45" s="92"/>
-      <c r="AE45" s="153"/>
-      <c r="AF45" s="154"/>
-      <c r="AG45" s="101">
+      <c r="AE45" s="120"/>
+      <c r="AF45" s="121"/>
+      <c r="AG45" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="103"/>
+      <c r="AH45" s="102"/>
       <c r="AI45" s="88"/>
-      <c r="AJ45" s="152"/>
+      <c r="AJ45" s="119"/>
       <c r="AK45" s="93"/>
       <c r="AL45" s="93"/>
-      <c r="AM45" s="100"/>
-      <c r="AN45" s="100"/>
-      <c r="AO45" s="100"/>
+      <c r="AM45" s="99"/>
+      <c r="AN45" s="99"/>
+      <c r="AO45" s="99"/>
       <c r="AP45" s="83"/>
-      <c r="AQ45" s="94"/>
-      <c r="AR45" s="95"/>
-      <c r="AS45" s="83"/>
-      <c r="AT45" s="83"/>
-      <c r="AU45" s="95"/>
-      <c r="AV45" s="94"/>
-      <c r="AW45" s="95"/>
+      <c r="AQ45" s="154"/>
+      <c r="AR45" s="110"/>
+      <c r="AS45" s="110"/>
+      <c r="AT45" s="110"/>
+      <c r="AU45" s="110"/>
+      <c r="AV45" s="154"/>
+      <c r="AW45" s="110"/>
       <c r="AX45" s="89"/>
       <c r="AY45" s="89"/>
-      <c r="AZ45" s="83"/>
-      <c r="BA45" s="96"/>
+      <c r="AZ45" s="89"/>
+      <c r="BA45" s="83"/>
       <c r="BB45" s="95"/>
-      <c r="BC45" s="89"/>
+      <c r="BC45" s="94"/>
       <c r="BD45" s="89"/>
-      <c r="BE45" s="95"/>
-      <c r="BF45" s="95"/>
+      <c r="BE45" s="89"/>
+      <c r="BF45" s="94"/>
+      <c r="BG45" s="94"/>
     </row>
-    <row r="46" spans="1:58" ht="30" customHeight="1">
+    <row r="46" spans="1:59" ht="30" customHeight="1">
       <c r="A46" s="83"/>
       <c r="B46" s="84"/>
       <c r="C46" s="85"/>
       <c r="D46" s="86"/>
-      <c r="E46" s="143"/>
-      <c r="F46" s="144"/>
-      <c r="G46" s="143"/>
-      <c r="H46" s="145"/>
-      <c r="I46" s="146">
+      <c r="E46" s="110"/>
+      <c r="F46" s="111"/>
+      <c r="G46" s="110"/>
+      <c r="H46" s="112"/>
+      <c r="I46" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J46" s="147">
+      <c r="J46" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K46" s="145"/>
-      <c r="L46" s="145"/>
-      <c r="M46" s="145"/>
-      <c r="N46" s="148"/>
+      <c r="K46" s="112"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="115"/>
       <c r="O46" s="88"/>
-      <c r="P46" s="99"/>
-      <c r="Q46" s="100"/>
+      <c r="P46" s="98"/>
+      <c r="Q46" s="99"/>
       <c r="R46" s="87"/>
       <c r="S46" s="88"/>
       <c r="T46" s="89"/>
-      <c r="U46" s="100"/>
-      <c r="V46" s="100"/>
-      <c r="W46" s="99"/>
+      <c r="U46" s="99"/>
+      <c r="V46" s="99"/>
+      <c r="W46" s="98"/>
       <c r="X46" s="83"/>
       <c r="Y46" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z46" s="110">
+      <c r="Z46" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="109">
+      <c r="AA46" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB46" s="91"/>
       <c r="AC46" s="90"/>
       <c r="AD46" s="92"/>
-      <c r="AE46" s="150"/>
-      <c r="AF46" s="151"/>
-      <c r="AG46" s="101">
+      <c r="AE46" s="117"/>
+      <c r="AF46" s="118"/>
+      <c r="AG46" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH46" s="102"/>
+      <c r="AH46" s="101"/>
       <c r="AI46" s="88"/>
-      <c r="AJ46" s="152"/>
+      <c r="AJ46" s="119"/>
       <c r="AK46" s="93"/>
       <c r="AL46" s="93"/>
-      <c r="AM46" s="100"/>
-      <c r="AN46" s="100"/>
-      <c r="AO46" s="100"/>
+      <c r="AM46" s="99"/>
+      <c r="AN46" s="99"/>
+      <c r="AO46" s="99"/>
       <c r="AP46" s="83"/>
-      <c r="AQ46" s="94"/>
-      <c r="AR46" s="95"/>
-      <c r="AS46" s="83"/>
-      <c r="AT46" s="83"/>
-      <c r="AU46" s="95"/>
-      <c r="AV46" s="94"/>
-      <c r="AW46" s="95"/>
+      <c r="AQ46" s="154"/>
+      <c r="AR46" s="110"/>
+      <c r="AS46" s="110"/>
+      <c r="AT46" s="110"/>
+      <c r="AU46" s="110"/>
+      <c r="AV46" s="154"/>
+      <c r="AW46" s="110"/>
       <c r="AX46" s="89"/>
       <c r="AY46" s="89"/>
       <c r="AZ46" s="89"/>
-      <c r="BA46" s="96"/>
+      <c r="BA46" s="89"/>
       <c r="BB46" s="95"/>
-      <c r="BC46" s="89"/>
+      <c r="BC46" s="94"/>
       <c r="BD46" s="89"/>
-      <c r="BE46" s="95"/>
-      <c r="BF46" s="95"/>
+      <c r="BE46" s="89"/>
+      <c r="BF46" s="94"/>
+      <c r="BG46" s="94"/>
     </row>
-    <row r="47" spans="1:58" ht="30" customHeight="1">
+    <row r="47" spans="1:59" ht="30" customHeight="1">
       <c r="A47" s="83"/>
       <c r="B47" s="84"/>
       <c r="C47" s="85"/>
       <c r="D47" s="86"/>
-      <c r="E47" s="143"/>
-      <c r="F47" s="144"/>
-      <c r="G47" s="143"/>
-      <c r="H47" s="145"/>
-      <c r="I47" s="146">
+      <c r="E47" s="110"/>
+      <c r="F47" s="111"/>
+      <c r="G47" s="110"/>
+      <c r="H47" s="112"/>
+      <c r="I47" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J47" s="147">
+      <c r="J47" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K47" s="145"/>
-      <c r="L47" s="145"/>
-      <c r="M47" s="145"/>
-      <c r="N47" s="148"/>
+      <c r="K47" s="112"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="115"/>
       <c r="O47" s="88"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="100"/>
+      <c r="P47" s="98"/>
+      <c r="Q47" s="99"/>
       <c r="R47" s="87"/>
       <c r="S47" s="88"/>
       <c r="T47" s="89"/>
-      <c r="U47" s="100"/>
-      <c r="V47" s="100"/>
-      <c r="W47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="99"/>
+      <c r="W47" s="98"/>
       <c r="X47" s="83"/>
       <c r="Y47" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z47" s="110">
+      <c r="Z47" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="109">
+      <c r="AA47" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB47" s="91"/>
       <c r="AC47" s="90"/>
       <c r="AD47" s="92"/>
-      <c r="AE47" s="150"/>
-      <c r="AF47" s="151"/>
-      <c r="AG47" s="101">
+      <c r="AE47" s="117"/>
+      <c r="AF47" s="118"/>
+      <c r="AG47" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH47" s="102"/>
+      <c r="AH47" s="101"/>
       <c r="AI47" s="88"/>
-      <c r="AJ47" s="152"/>
+      <c r="AJ47" s="119"/>
       <c r="AK47" s="93"/>
       <c r="AL47" s="93"/>
-      <c r="AM47" s="100"/>
-      <c r="AN47" s="100"/>
-      <c r="AO47" s="100"/>
+      <c r="AM47" s="99"/>
+      <c r="AN47" s="99"/>
+      <c r="AO47" s="99"/>
       <c r="AP47" s="83"/>
-      <c r="AQ47" s="94"/>
-      <c r="AR47" s="95"/>
-      <c r="AS47" s="83"/>
-      <c r="AT47" s="83"/>
-      <c r="AU47" s="95"/>
-      <c r="AV47" s="94"/>
-      <c r="AW47" s="95"/>
+      <c r="AQ47" s="154"/>
+      <c r="AR47" s="110"/>
+      <c r="AS47" s="110"/>
+      <c r="AT47" s="110"/>
+      <c r="AU47" s="110"/>
+      <c r="AV47" s="154"/>
+      <c r="AW47" s="110"/>
       <c r="AX47" s="89"/>
       <c r="AY47" s="89"/>
       <c r="AZ47" s="89"/>
-      <c r="BA47" s="96"/>
+      <c r="BA47" s="89"/>
       <c r="BB47" s="95"/>
-      <c r="BC47" s="89"/>
+      <c r="BC47" s="94"/>
       <c r="BD47" s="89"/>
-      <c r="BE47" s="95"/>
-      <c r="BF47" s="95"/>
+      <c r="BE47" s="89"/>
+      <c r="BF47" s="94"/>
+      <c r="BG47" s="94"/>
     </row>
-    <row r="48" spans="1:58" ht="30" customHeight="1">
+    <row r="48" spans="1:59" ht="30" customHeight="1">
       <c r="A48" s="83"/>
       <c r="B48" s="84"/>
       <c r="C48" s="85"/>
       <c r="D48" s="86"/>
-      <c r="E48" s="143"/>
-      <c r="F48" s="144"/>
-      <c r="G48" s="143"/>
-      <c r="H48" s="145"/>
-      <c r="I48" s="146">
+      <c r="E48" s="110"/>
+      <c r="F48" s="111"/>
+      <c r="G48" s="110"/>
+      <c r="H48" s="112"/>
+      <c r="I48" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="147">
+      <c r="J48" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K48" s="145"/>
-      <c r="L48" s="145"/>
-      <c r="M48" s="145"/>
-      <c r="N48" s="148"/>
+      <c r="K48" s="112"/>
+      <c r="L48" s="112"/>
+      <c r="M48" s="112"/>
+      <c r="N48" s="115"/>
       <c r="O48" s="88"/>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="100"/>
+      <c r="P48" s="98"/>
+      <c r="Q48" s="99"/>
       <c r="R48" s="87"/>
       <c r="S48" s="88"/>
       <c r="T48" s="89"/>
-      <c r="U48" s="100"/>
-      <c r="V48" s="100"/>
-      <c r="W48" s="99"/>
+      <c r="U48" s="99"/>
+      <c r="V48" s="99"/>
+      <c r="W48" s="98"/>
       <c r="X48" s="83"/>
       <c r="Y48" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z48" s="110">
+      <c r="Z48" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA48" s="109">
+      <c r="AA48" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB48" s="91"/>
       <c r="AC48" s="90"/>
       <c r="AD48" s="92"/>
-      <c r="AE48" s="150"/>
-      <c r="AF48" s="151"/>
-      <c r="AG48" s="101">
+      <c r="AE48" s="117"/>
+      <c r="AF48" s="118"/>
+      <c r="AG48" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH48" s="102"/>
+      <c r="AH48" s="101"/>
       <c r="AI48" s="88"/>
-      <c r="AJ48" s="152"/>
+      <c r="AJ48" s="119"/>
       <c r="AK48" s="93"/>
       <c r="AL48" s="93"/>
-      <c r="AM48" s="100"/>
-      <c r="AN48" s="100"/>
-      <c r="AO48" s="100"/>
+      <c r="AM48" s="99"/>
+      <c r="AN48" s="99"/>
+      <c r="AO48" s="99"/>
       <c r="AP48" s="83"/>
-      <c r="AQ48" s="94"/>
-      <c r="AR48" s="95"/>
-      <c r="AS48" s="83"/>
-      <c r="AT48" s="83"/>
-      <c r="AU48" s="95"/>
-      <c r="AV48" s="94"/>
-      <c r="AW48" s="95"/>
+      <c r="AQ48" s="154"/>
+      <c r="AR48" s="110"/>
+      <c r="AS48" s="110"/>
+      <c r="AT48" s="110"/>
+      <c r="AU48" s="110"/>
+      <c r="AV48" s="154"/>
+      <c r="AW48" s="110"/>
       <c r="AX48" s="89"/>
       <c r="AY48" s="89"/>
       <c r="AZ48" s="89"/>
-      <c r="BA48" s="96"/>
+      <c r="BA48" s="89"/>
       <c r="BB48" s="95"/>
-      <c r="BC48" s="89"/>
+      <c r="BC48" s="94"/>
       <c r="BD48" s="89"/>
-      <c r="BE48" s="95"/>
-      <c r="BF48" s="95"/>
+      <c r="BE48" s="89"/>
+      <c r="BF48" s="94"/>
+      <c r="BG48" s="94"/>
     </row>
-    <row r="49" spans="1:58" ht="30" customHeight="1">
+    <row r="49" spans="1:59" ht="30" customHeight="1">
       <c r="A49" s="83"/>
       <c r="B49" s="84"/>
       <c r="C49" s="85"/>
       <c r="D49" s="86"/>
-      <c r="E49" s="143"/>
-      <c r="F49" s="144"/>
-      <c r="G49" s="143"/>
-      <c r="H49" s="145"/>
-      <c r="I49" s="146">
+      <c r="E49" s="110"/>
+      <c r="F49" s="111"/>
+      <c r="G49" s="110"/>
+      <c r="H49" s="112"/>
+      <c r="I49" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J49" s="147">
+      <c r="J49" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K49" s="145"/>
-      <c r="L49" s="145"/>
-      <c r="M49" s="145"/>
-      <c r="N49" s="148"/>
+      <c r="K49" s="112"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="115"/>
       <c r="O49" s="88"/>
-      <c r="P49" s="99"/>
-      <c r="Q49" s="100"/>
+      <c r="P49" s="98"/>
+      <c r="Q49" s="99"/>
       <c r="R49" s="87"/>
       <c r="S49" s="88"/>
       <c r="T49" s="89"/>
-      <c r="U49" s="100"/>
-      <c r="V49" s="100"/>
-      <c r="W49" s="99"/>
+      <c r="U49" s="99"/>
+      <c r="V49" s="99"/>
+      <c r="W49" s="98"/>
       <c r="X49" s="83"/>
       <c r="Y49" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z49" s="110">
+      <c r="Z49" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="109">
+      <c r="AA49" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB49" s="91"/>
       <c r="AC49" s="90"/>
       <c r="AD49" s="92"/>
-      <c r="AE49" s="150"/>
-      <c r="AF49" s="151"/>
-      <c r="AG49" s="101">
+      <c r="AE49" s="117"/>
+      <c r="AF49" s="118"/>
+      <c r="AG49" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="102"/>
+      <c r="AH49" s="101"/>
       <c r="AI49" s="88"/>
-      <c r="AJ49" s="152"/>
+      <c r="AJ49" s="119"/>
       <c r="AK49" s="93"/>
       <c r="AL49" s="93"/>
-      <c r="AM49" s="100"/>
-      <c r="AN49" s="100"/>
-      <c r="AO49" s="100"/>
+      <c r="AM49" s="99"/>
+      <c r="AN49" s="99"/>
+      <c r="AO49" s="99"/>
       <c r="AP49" s="83"/>
-      <c r="AQ49" s="94"/>
-      <c r="AR49" s="95"/>
-      <c r="AS49" s="83"/>
-      <c r="AT49" s="83"/>
-      <c r="AU49" s="95"/>
-      <c r="AV49" s="94"/>
-      <c r="AW49" s="95"/>
+      <c r="AQ49" s="154"/>
+      <c r="AR49" s="110"/>
+      <c r="AS49" s="110"/>
+      <c r="AT49" s="110"/>
+      <c r="AU49" s="110"/>
+      <c r="AV49" s="154"/>
+      <c r="AW49" s="110"/>
       <c r="AX49" s="89"/>
       <c r="AY49" s="89"/>
       <c r="AZ49" s="89"/>
-      <c r="BA49" s="96"/>
+      <c r="BA49" s="89"/>
       <c r="BB49" s="95"/>
-      <c r="BC49" s="89"/>
+      <c r="BC49" s="94"/>
       <c r="BD49" s="89"/>
-      <c r="BE49" s="95"/>
-      <c r="BF49" s="95"/>
+      <c r="BE49" s="89"/>
+      <c r="BF49" s="94"/>
+      <c r="BG49" s="94"/>
     </row>
-    <row r="50" spans="1:58" ht="30" customHeight="1">
+    <row r="50" spans="1:59" ht="30" customHeight="1">
       <c r="A50" s="83"/>
       <c r="B50" s="84"/>
       <c r="C50" s="85"/>
       <c r="D50" s="86"/>
-      <c r="E50" s="143"/>
-      <c r="F50" s="144"/>
-      <c r="G50" s="143"/>
-      <c r="H50" s="145"/>
-      <c r="I50" s="146">
+      <c r="E50" s="110"/>
+      <c r="F50" s="111"/>
+      <c r="G50" s="110"/>
+      <c r="H50" s="112"/>
+      <c r="I50" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J50" s="147">
+      <c r="J50" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K50" s="145"/>
-      <c r="L50" s="145"/>
-      <c r="M50" s="145"/>
-      <c r="N50" s="148"/>
+      <c r="K50" s="112"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="115"/>
       <c r="O50" s="88"/>
-      <c r="P50" s="99"/>
-      <c r="Q50" s="100"/>
+      <c r="P50" s="98"/>
+      <c r="Q50" s="99"/>
       <c r="R50" s="87"/>
       <c r="S50" s="88"/>
       <c r="T50" s="89"/>
-      <c r="U50" s="100"/>
-      <c r="V50" s="100"/>
-      <c r="W50" s="99"/>
+      <c r="U50" s="99"/>
+      <c r="V50" s="99"/>
+      <c r="W50" s="98"/>
       <c r="X50" s="83"/>
       <c r="Y50" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z50" s="110">
+      <c r="Z50" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA50" s="109">
+      <c r="AA50" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB50" s="91"/>
       <c r="AC50" s="90"/>
       <c r="AD50" s="92"/>
-      <c r="AE50" s="150"/>
-      <c r="AF50" s="151"/>
-      <c r="AG50" s="101">
+      <c r="AE50" s="117"/>
+      <c r="AF50" s="118"/>
+      <c r="AG50" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="102"/>
+      <c r="AH50" s="101"/>
       <c r="AI50" s="88"/>
-      <c r="AJ50" s="152"/>
+      <c r="AJ50" s="119"/>
       <c r="AK50" s="93"/>
       <c r="AL50" s="93"/>
-      <c r="AM50" s="100"/>
-      <c r="AN50" s="100"/>
-      <c r="AO50" s="100"/>
+      <c r="AM50" s="99"/>
+      <c r="AN50" s="99"/>
+      <c r="AO50" s="99"/>
       <c r="AP50" s="83"/>
-      <c r="AQ50" s="94"/>
-      <c r="AR50" s="95"/>
-      <c r="AS50" s="83"/>
-      <c r="AT50" s="83"/>
-      <c r="AU50" s="95"/>
-      <c r="AV50" s="94"/>
-      <c r="AW50" s="95"/>
+      <c r="AQ50" s="154"/>
+      <c r="AR50" s="110"/>
+      <c r="AS50" s="110"/>
+      <c r="AT50" s="110"/>
+      <c r="AU50" s="110"/>
+      <c r="AV50" s="154"/>
+      <c r="AW50" s="110"/>
       <c r="AX50" s="89"/>
       <c r="AY50" s="89"/>
       <c r="AZ50" s="89"/>
-      <c r="BA50" s="96"/>
+      <c r="BA50" s="89"/>
       <c r="BB50" s="95"/>
-      <c r="BC50" s="89"/>
+      <c r="BC50" s="94"/>
       <c r="BD50" s="89"/>
-      <c r="BE50" s="95"/>
-      <c r="BF50" s="95"/>
+      <c r="BE50" s="89"/>
+      <c r="BF50" s="94"/>
+      <c r="BG50" s="94"/>
     </row>
-    <row r="51" spans="1:58" ht="30" customHeight="1">
+    <row r="51" spans="1:59" ht="30" customHeight="1">
       <c r="A51" s="83"/>
       <c r="B51" s="84"/>
       <c r="C51" s="85"/>
       <c r="D51" s="86"/>
-      <c r="E51" s="143"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="143"/>
-      <c r="H51" s="145"/>
-      <c r="I51" s="146">
+      <c r="E51" s="110"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="110"/>
+      <c r="H51" s="112"/>
+      <c r="I51" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J51" s="147">
+      <c r="J51" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K51" s="145"/>
-      <c r="L51" s="145"/>
-      <c r="M51" s="145"/>
-      <c r="N51" s="148"/>
+      <c r="K51" s="112"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="115"/>
       <c r="O51" s="88"/>
-      <c r="P51" s="99"/>
-      <c r="Q51" s="100"/>
+      <c r="P51" s="98"/>
+      <c r="Q51" s="99"/>
       <c r="R51" s="87"/>
       <c r="S51" s="88"/>
       <c r="T51" s="89"/>
-      <c r="U51" s="100"/>
-      <c r="V51" s="100"/>
-      <c r="W51" s="99"/>
+      <c r="U51" s="99"/>
+      <c r="V51" s="99"/>
+      <c r="W51" s="98"/>
       <c r="X51" s="83"/>
       <c r="Y51" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z51" s="110">
+      <c r="Z51" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="109">
+      <c r="AA51" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB51" s="91"/>
       <c r="AC51" s="90"/>
       <c r="AD51" s="92"/>
-      <c r="AE51" s="150"/>
-      <c r="AF51" s="151"/>
-      <c r="AG51" s="101">
+      <c r="AE51" s="117"/>
+      <c r="AF51" s="118"/>
+      <c r="AG51" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH51" s="102"/>
+      <c r="AH51" s="101"/>
       <c r="AI51" s="88"/>
-      <c r="AJ51" s="152"/>
+      <c r="AJ51" s="119"/>
       <c r="AK51" s="93"/>
       <c r="AL51" s="93"/>
-      <c r="AM51" s="100"/>
-      <c r="AN51" s="100"/>
-      <c r="AO51" s="100"/>
+      <c r="AM51" s="99"/>
+      <c r="AN51" s="99"/>
+      <c r="AO51" s="99"/>
       <c r="AP51" s="83"/>
-      <c r="AQ51" s="94"/>
-      <c r="AR51" s="95"/>
-      <c r="AS51" s="83"/>
-      <c r="AT51" s="83"/>
-      <c r="AU51" s="95"/>
-      <c r="AV51" s="94"/>
-      <c r="AW51" s="95"/>
+      <c r="AQ51" s="154"/>
+      <c r="AR51" s="110"/>
+      <c r="AS51" s="110"/>
+      <c r="AT51" s="110"/>
+      <c r="AU51" s="110"/>
+      <c r="AV51" s="154"/>
+      <c r="AW51" s="110"/>
       <c r="AX51" s="89"/>
       <c r="AY51" s="89"/>
       <c r="AZ51" s="89"/>
-      <c r="BA51" s="96"/>
+      <c r="BA51" s="89"/>
       <c r="BB51" s="95"/>
-      <c r="BC51" s="89"/>
+      <c r="BC51" s="94"/>
       <c r="BD51" s="89"/>
-      <c r="BE51" s="95"/>
-      <c r="BF51" s="95"/>
+      <c r="BE51" s="89"/>
+      <c r="BF51" s="94"/>
+      <c r="BG51" s="94"/>
     </row>
-    <row r="52" spans="1:58" ht="30" customHeight="1">
+    <row r="52" spans="1:59" ht="30" customHeight="1">
       <c r="A52" s="83"/>
       <c r="B52" s="84"/>
       <c r="C52" s="85"/>
       <c r="D52" s="86"/>
-      <c r="E52" s="143"/>
-      <c r="F52" s="144"/>
-      <c r="G52" s="143"/>
-      <c r="H52" s="145"/>
-      <c r="I52" s="146">
+      <c r="E52" s="110"/>
+      <c r="F52" s="111"/>
+      <c r="G52" s="110"/>
+      <c r="H52" s="112"/>
+      <c r="I52" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J52" s="147">
+      <c r="J52" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K52" s="145"/>
-      <c r="L52" s="145"/>
-      <c r="M52" s="145"/>
-      <c r="N52" s="148"/>
+      <c r="K52" s="112"/>
+      <c r="L52" s="112"/>
+      <c r="M52" s="112"/>
+      <c r="N52" s="115"/>
       <c r="O52" s="88"/>
-      <c r="P52" s="99"/>
-      <c r="Q52" s="100"/>
+      <c r="P52" s="98"/>
+      <c r="Q52" s="99"/>
       <c r="R52" s="87"/>
       <c r="S52" s="88"/>
       <c r="T52" s="89"/>
-      <c r="U52" s="100"/>
-      <c r="V52" s="100"/>
-      <c r="W52" s="99"/>
+      <c r="U52" s="99"/>
+      <c r="V52" s="99"/>
+      <c r="W52" s="98"/>
       <c r="X52" s="83"/>
       <c r="Y52" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z52" s="110">
+      <c r="Z52" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA52" s="109">
+      <c r="AA52" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB52" s="91"/>
       <c r="AC52" s="90"/>
       <c r="AD52" s="92"/>
-      <c r="AE52" s="150"/>
-      <c r="AF52" s="151"/>
-      <c r="AG52" s="101">
+      <c r="AE52" s="117"/>
+      <c r="AF52" s="118"/>
+      <c r="AG52" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH52" s="102"/>
+      <c r="AH52" s="101"/>
       <c r="AI52" s="88"/>
-      <c r="AJ52" s="152"/>
+      <c r="AJ52" s="119"/>
       <c r="AK52" s="93"/>
       <c r="AL52" s="93"/>
-      <c r="AM52" s="100"/>
-      <c r="AN52" s="100"/>
-      <c r="AO52" s="100"/>
+      <c r="AM52" s="99"/>
+      <c r="AN52" s="99"/>
+      <c r="AO52" s="99"/>
       <c r="AP52" s="83"/>
-      <c r="AQ52" s="94"/>
-      <c r="AR52" s="95"/>
-      <c r="AS52" s="83"/>
-      <c r="AT52" s="83"/>
-      <c r="AU52" s="95"/>
-      <c r="AV52" s="94"/>
-      <c r="AW52" s="95"/>
+      <c r="AQ52" s="154"/>
+      <c r="AR52" s="110"/>
+      <c r="AS52" s="110"/>
+      <c r="AT52" s="110"/>
+      <c r="AU52" s="110"/>
+      <c r="AV52" s="154"/>
+      <c r="AW52" s="110"/>
       <c r="AX52" s="89"/>
       <c r="AY52" s="89"/>
       <c r="AZ52" s="89"/>
-      <c r="BA52" s="96"/>
+      <c r="BA52" s="89"/>
       <c r="BB52" s="95"/>
-      <c r="BC52" s="89"/>
+      <c r="BC52" s="94"/>
       <c r="BD52" s="89"/>
-      <c r="BE52" s="95"/>
-      <c r="BF52" s="95"/>
+      <c r="BE52" s="89"/>
+      <c r="BF52" s="94"/>
+      <c r="BG52" s="94"/>
     </row>
-    <row r="53" spans="1:58" ht="30" customHeight="1">
+    <row r="53" spans="1:59" ht="30" customHeight="1">
       <c r="A53" s="83"/>
       <c r="B53" s="84"/>
       <c r="C53" s="85"/>
       <c r="D53" s="86"/>
-      <c r="E53" s="143"/>
-      <c r="F53" s="144"/>
-      <c r="G53" s="143"/>
-      <c r="H53" s="145"/>
-      <c r="I53" s="146">
+      <c r="E53" s="110"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="110"/>
+      <c r="H53" s="112"/>
+      <c r="I53" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J53" s="147">
+      <c r="J53" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K53" s="145"/>
-      <c r="L53" s="145"/>
-      <c r="M53" s="145"/>
-      <c r="N53" s="148"/>
+      <c r="K53" s="112"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="115"/>
       <c r="O53" s="88"/>
-      <c r="P53" s="99"/>
-      <c r="Q53" s="100"/>
+      <c r="P53" s="98"/>
+      <c r="Q53" s="99"/>
       <c r="R53" s="87"/>
       <c r="S53" s="88"/>
       <c r="T53" s="89"/>
-      <c r="U53" s="100"/>
-      <c r="V53" s="100"/>
-      <c r="W53" s="99"/>
+      <c r="U53" s="99"/>
+      <c r="V53" s="99"/>
+      <c r="W53" s="98"/>
       <c r="X53" s="83"/>
       <c r="Y53" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z53" s="110">
+      <c r="Z53" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA53" s="109">
+      <c r="AA53" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB53" s="91"/>
       <c r="AC53" s="90"/>
       <c r="AD53" s="92"/>
-      <c r="AE53" s="150"/>
-      <c r="AF53" s="151"/>
-      <c r="AG53" s="101">
+      <c r="AE53" s="117"/>
+      <c r="AF53" s="118"/>
+      <c r="AG53" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="102"/>
+      <c r="AH53" s="101"/>
       <c r="AI53" s="88"/>
-      <c r="AJ53" s="152"/>
+      <c r="AJ53" s="119"/>
       <c r="AK53" s="93"/>
       <c r="AL53" s="93"/>
-      <c r="AM53" s="100"/>
-      <c r="AN53" s="100"/>
-      <c r="AO53" s="100"/>
+      <c r="AM53" s="99"/>
+      <c r="AN53" s="99"/>
+      <c r="AO53" s="99"/>
       <c r="AP53" s="83"/>
-      <c r="AQ53" s="94"/>
-      <c r="AR53" s="95"/>
-      <c r="AS53" s="83"/>
-      <c r="AT53" s="83"/>
-      <c r="AU53" s="95"/>
-      <c r="AV53" s="94"/>
-      <c r="AW53" s="95"/>
+      <c r="AQ53" s="154"/>
+      <c r="AR53" s="110"/>
+      <c r="AS53" s="110"/>
+      <c r="AT53" s="110"/>
+      <c r="AU53" s="110"/>
+      <c r="AV53" s="154"/>
+      <c r="AW53" s="110"/>
       <c r="AX53" s="89"/>
       <c r="AY53" s="89"/>
       <c r="AZ53" s="89"/>
-      <c r="BA53" s="96"/>
+      <c r="BA53" s="89"/>
       <c r="BB53" s="95"/>
-      <c r="BC53" s="89"/>
+      <c r="BC53" s="94"/>
       <c r="BD53" s="89"/>
-      <c r="BE53" s="95"/>
-      <c r="BF53" s="95"/>
+      <c r="BE53" s="89"/>
+      <c r="BF53" s="94"/>
+      <c r="BG53" s="94"/>
     </row>
-    <row r="54" spans="1:58" ht="30.75" customHeight="1">
+    <row r="54" spans="1:59" ht="30.75" customHeight="1">
       <c r="A54" s="83"/>
       <c r="B54" s="84"/>
       <c r="C54" s="83"/>
-      <c r="D54" s="97"/>
-      <c r="E54" s="143"/>
-      <c r="F54" s="144"/>
-      <c r="G54" s="143"/>
-      <c r="H54" s="149"/>
-      <c r="I54" s="146">
+      <c r="D54" s="96"/>
+      <c r="E54" s="110"/>
+      <c r="F54" s="111"/>
+      <c r="G54" s="110"/>
+      <c r="H54" s="116"/>
+      <c r="I54" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J54" s="147">
+      <c r="J54" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K54" s="149"/>
-      <c r="L54" s="149"/>
-      <c r="M54" s="149"/>
-      <c r="N54" s="148"/>
+      <c r="K54" s="116"/>
+      <c r="L54" s="116"/>
+      <c r="M54" s="116"/>
+      <c r="N54" s="115"/>
       <c r="O54" s="88"/>
-      <c r="P54" s="99"/>
-      <c r="Q54" s="100"/>
+      <c r="P54" s="98"/>
+      <c r="Q54" s="99"/>
       <c r="R54" s="87"/>
       <c r="S54" s="88"/>
       <c r="T54" s="89"/>
-      <c r="U54" s="100"/>
-      <c r="V54" s="100"/>
-      <c r="W54" s="99"/>
+      <c r="U54" s="99"/>
+      <c r="V54" s="99"/>
+      <c r="W54" s="98"/>
       <c r="X54" s="83"/>
       <c r="Y54" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z54" s="110">
+      <c r="Z54" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="109">
+      <c r="AA54" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB54" s="91"/>
       <c r="AC54" s="90"/>
       <c r="AD54" s="92"/>
-      <c r="AE54" s="153"/>
-      <c r="AF54" s="154"/>
-      <c r="AG54" s="101">
+      <c r="AE54" s="120"/>
+      <c r="AF54" s="121"/>
+      <c r="AG54" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="103"/>
+      <c r="AH54" s="102"/>
       <c r="AI54" s="88"/>
-      <c r="AJ54" s="152"/>
+      <c r="AJ54" s="119"/>
       <c r="AK54" s="93"/>
       <c r="AL54" s="93"/>
-      <c r="AM54" s="100"/>
-      <c r="AN54" s="100"/>
-      <c r="AO54" s="100"/>
+      <c r="AM54" s="99"/>
+      <c r="AN54" s="99"/>
+      <c r="AO54" s="99"/>
       <c r="AP54" s="83"/>
-      <c r="AQ54" s="94"/>
-      <c r="AR54" s="95"/>
-      <c r="AS54" s="83"/>
-      <c r="AT54" s="83"/>
-      <c r="AU54" s="95"/>
-      <c r="AV54" s="94"/>
-      <c r="AW54" s="95"/>
+      <c r="AQ54" s="154"/>
+      <c r="AR54" s="110"/>
+      <c r="AS54" s="110"/>
+      <c r="AT54" s="110"/>
+      <c r="AU54" s="110"/>
+      <c r="AV54" s="154"/>
+      <c r="AW54" s="110"/>
       <c r="AX54" s="89"/>
       <c r="AY54" s="89"/>
       <c r="AZ54" s="89"/>
-      <c r="BA54" s="96"/>
+      <c r="BA54" s="89"/>
       <c r="BB54" s="95"/>
-      <c r="BC54" s="89"/>
+      <c r="BC54" s="94"/>
       <c r="BD54" s="89"/>
-      <c r="BE54" s="95"/>
-      <c r="BF54" s="95"/>
+      <c r="BE54" s="89"/>
+      <c r="BF54" s="94"/>
+      <c r="BG54" s="94"/>
     </row>
-    <row r="55" spans="1:58" ht="30" customHeight="1">
+    <row r="55" spans="1:59" ht="30" customHeight="1">
       <c r="A55" s="83"/>
       <c r="B55" s="84"/>
       <c r="C55" s="83"/>
       <c r="D55" s="86"/>
-      <c r="E55" s="143"/>
-      <c r="F55" s="144"/>
-      <c r="G55" s="143"/>
-      <c r="H55" s="145"/>
-      <c r="I55" s="146">
+      <c r="E55" s="110"/>
+      <c r="F55" s="111"/>
+      <c r="G55" s="110"/>
+      <c r="H55" s="112"/>
+      <c r="I55" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J55" s="147">
+      <c r="J55" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K55" s="145"/>
-      <c r="L55" s="145"/>
-      <c r="M55" s="145"/>
-      <c r="N55" s="148"/>
+      <c r="K55" s="112"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="115"/>
       <c r="O55" s="88"/>
-      <c r="P55" s="99"/>
-      <c r="Q55" s="100"/>
+      <c r="P55" s="98"/>
+      <c r="Q55" s="99"/>
       <c r="R55" s="87"/>
       <c r="S55" s="88"/>
       <c r="T55" s="89"/>
-      <c r="U55" s="100"/>
-      <c r="V55" s="100"/>
-      <c r="W55" s="99"/>
+      <c r="U55" s="99"/>
+      <c r="V55" s="99"/>
+      <c r="W55" s="98"/>
       <c r="X55" s="83"/>
       <c r="Y55" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z55" s="110">
+      <c r="Z55" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA55" s="109">
+      <c r="AA55" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB55" s="91"/>
       <c r="AC55" s="90"/>
       <c r="AD55" s="92"/>
-      <c r="AE55" s="153"/>
-      <c r="AF55" s="154"/>
-      <c r="AG55" s="101">
+      <c r="AE55" s="120"/>
+      <c r="AF55" s="121"/>
+      <c r="AG55" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH55" s="103"/>
+      <c r="AH55" s="102"/>
       <c r="AI55" s="88"/>
-      <c r="AJ55" s="152"/>
+      <c r="AJ55" s="119"/>
       <c r="AK55" s="93"/>
       <c r="AL55" s="93"/>
-      <c r="AM55" s="100"/>
-      <c r="AN55" s="100"/>
-      <c r="AO55" s="100"/>
+      <c r="AM55" s="99"/>
+      <c r="AN55" s="99"/>
+      <c r="AO55" s="99"/>
       <c r="AP55" s="83"/>
-      <c r="AQ55" s="94"/>
-      <c r="AR55" s="95"/>
-      <c r="AS55" s="83"/>
-      <c r="AT55" s="83"/>
-      <c r="AU55" s="95"/>
-      <c r="AV55" s="94"/>
-      <c r="AW55" s="95"/>
+      <c r="AQ55" s="154"/>
+      <c r="AR55" s="110"/>
+      <c r="AS55" s="110"/>
+      <c r="AT55" s="110"/>
+      <c r="AU55" s="110"/>
+      <c r="AV55" s="154"/>
+      <c r="AW55" s="110"/>
       <c r="AX55" s="89"/>
       <c r="AY55" s="89"/>
       <c r="AZ55" s="89"/>
-      <c r="BA55" s="96"/>
+      <c r="BA55" s="89"/>
       <c r="BB55" s="95"/>
-      <c r="BC55" s="89"/>
+      <c r="BC55" s="94"/>
       <c r="BD55" s="89"/>
-      <c r="BE55" s="95"/>
-      <c r="BF55" s="95"/>
+      <c r="BE55" s="89"/>
+      <c r="BF55" s="94"/>
+      <c r="BG55" s="94"/>
     </row>
-    <row r="56" spans="1:58" ht="30" customHeight="1">
+    <row r="56" spans="1:59" ht="30" customHeight="1">
       <c r="A56" s="83"/>
       <c r="B56" s="84"/>
       <c r="C56" s="83"/>
-      <c r="D56" s="98"/>
-      <c r="E56" s="143"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="143"/>
-      <c r="H56" s="145"/>
-      <c r="I56" s="146">
+      <c r="D56" s="97"/>
+      <c r="E56" s="110"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="110"/>
+      <c r="H56" s="112"/>
+      <c r="I56" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J56" s="147">
+      <c r="J56" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K56" s="145"/>
-      <c r="L56" s="145"/>
-      <c r="M56" s="145"/>
-      <c r="N56" s="148"/>
+      <c r="K56" s="112"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="115"/>
       <c r="O56" s="88"/>
-      <c r="P56" s="99"/>
-      <c r="Q56" s="100"/>
+      <c r="P56" s="98"/>
+      <c r="Q56" s="99"/>
       <c r="R56" s="87"/>
       <c r="S56" s="88"/>
       <c r="T56" s="89"/>
-      <c r="U56" s="100"/>
-      <c r="V56" s="100"/>
-      <c r="W56" s="99"/>
+      <c r="U56" s="99"/>
+      <c r="V56" s="99"/>
+      <c r="W56" s="98"/>
       <c r="X56" s="83"/>
       <c r="Y56" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z56" s="110">
+      <c r="Z56" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA56" s="109">
+      <c r="AA56" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB56" s="91"/>
       <c r="AC56" s="90"/>
       <c r="AD56" s="92"/>
-      <c r="AE56" s="153"/>
-      <c r="AF56" s="154"/>
-      <c r="AG56" s="101">
+      <c r="AE56" s="120"/>
+      <c r="AF56" s="121"/>
+      <c r="AG56" s="100">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH56" s="103"/>
+      <c r="AH56" s="102"/>
       <c r="AI56" s="88"/>
-      <c r="AJ56" s="152"/>
+      <c r="AJ56" s="119"/>
       <c r="AK56" s="93"/>
       <c r="AL56" s="93"/>
-      <c r="AM56" s="100"/>
-      <c r="AN56" s="100"/>
-      <c r="AO56" s="100"/>
+      <c r="AM56" s="99"/>
+      <c r="AN56" s="99"/>
+      <c r="AO56" s="99"/>
       <c r="AP56" s="83"/>
-      <c r="AQ56" s="94"/>
-      <c r="AR56" s="95"/>
-      <c r="AS56" s="83"/>
-      <c r="AT56" s="83"/>
-      <c r="AU56" s="95"/>
-      <c r="AV56" s="94"/>
-      <c r="AW56" s="95"/>
+      <c r="AQ56" s="154"/>
+      <c r="AR56" s="110"/>
+      <c r="AS56" s="110"/>
+      <c r="AT56" s="110"/>
+      <c r="AU56" s="110"/>
+      <c r="AV56" s="154"/>
+      <c r="AW56" s="110"/>
       <c r="AX56" s="89"/>
       <c r="AY56" s="89"/>
-      <c r="AZ56" s="83"/>
-      <c r="BA56" s="96"/>
+      <c r="AZ56" s="89"/>
+      <c r="BA56" s="83"/>
       <c r="BB56" s="95"/>
-      <c r="BC56" s="89"/>
+      <c r="BC56" s="94"/>
       <c r="BD56" s="89"/>
-      <c r="BE56" s="95"/>
-      <c r="BF56" s="95"/>
+      <c r="BE56" s="89"/>
+      <c r="BF56" s="94"/>
+      <c r="BG56" s="94"/>
     </row>
-    <row r="57" spans="1:58" ht="30" customHeight="1">
+    <row r="57" spans="1:59" ht="30" customHeight="1">
       <c r="A57" s="83"/>
       <c r="B57" s="84"/>
       <c r="C57" s="83"/>
-      <c r="D57" s="98"/>
-      <c r="E57" s="143"/>
-      <c r="F57" s="144"/>
-      <c r="G57" s="143"/>
-      <c r="H57" s="149"/>
-      <c r="I57" s="146">
+      <c r="D57" s="97"/>
+      <c r="E57" s="110"/>
+      <c r="F57" s="111"/>
+      <c r="G57" s="110"/>
+      <c r="H57" s="116"/>
+      <c r="I57" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J57" s="147">
+      <c r="J57" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K57" s="149"/>
-      <c r="L57" s="149"/>
-      <c r="M57" s="149"/>
-      <c r="N57" s="148"/>
+      <c r="K57" s="116"/>
+      <c r="L57" s="116"/>
+      <c r="M57" s="116"/>
+      <c r="N57" s="115"/>
       <c r="O57" s="88"/>
-      <c r="P57" s="99"/>
-      <c r="Q57" s="100"/>
+      <c r="P57" s="98"/>
+      <c r="Q57" s="99"/>
       <c r="R57" s="87"/>
       <c r="S57" s="88"/>
       <c r="T57" s="89"/>
-      <c r="U57" s="100"/>
-      <c r="V57" s="100"/>
-      <c r="W57" s="99"/>
+      <c r="U57" s="99"/>
+      <c r="V57" s="99"/>
+      <c r="W57" s="98"/>
       <c r="X57" s="83"/>
       <c r="Y57" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z57" s="110">
+      <c r="Z57" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA57" s="109">
+      <c r="AA57" s="108">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB57" s="91"/>
       <c r="AC57" s="90"/>
       <c r="AD57" s="92"/>
-      <c r="AE57" s="153"/>
-      <c r="AF57" s="154"/>
-      <c r="AG57" s="99">
+      <c r="AE57" s="120"/>
+      <c r="AF57" s="121"/>
+      <c r="AG57" s="98">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH57" s="103"/>
+      <c r="AH57" s="102"/>
       <c r="AI57" s="88"/>
-      <c r="AJ57" s="152"/>
+      <c r="AJ57" s="119"/>
       <c r="AK57" s="93"/>
       <c r="AL57" s="93"/>
-      <c r="AM57" s="100"/>
-      <c r="AN57" s="100"/>
-      <c r="AO57" s="100"/>
+      <c r="AM57" s="99"/>
+      <c r="AN57" s="99"/>
+      <c r="AO57" s="99"/>
       <c r="AP57" s="83"/>
-      <c r="AQ57" s="94"/>
-      <c r="AR57" s="95"/>
-      <c r="AS57" s="83"/>
-      <c r="AT57" s="83"/>
-      <c r="AU57" s="95"/>
-      <c r="AV57" s="94"/>
-      <c r="AW57" s="95"/>
+      <c r="AQ57" s="154"/>
+      <c r="AR57" s="110"/>
+      <c r="AS57" s="110"/>
+      <c r="AT57" s="110"/>
+      <c r="AU57" s="110"/>
+      <c r="AV57" s="154"/>
+      <c r="AW57" s="110"/>
       <c r="AX57" s="89"/>
       <c r="AY57" s="89"/>
-      <c r="AZ57" s="83"/>
-      <c r="BA57" s="96"/>
+      <c r="AZ57" s="89"/>
+      <c r="BA57" s="83"/>
       <c r="BB57" s="95"/>
-      <c r="BC57" s="89"/>
+      <c r="BC57" s="94"/>
       <c r="BD57" s="89"/>
-      <c r="BE57" s="95"/>
-      <c r="BF57" s="95"/>
+      <c r="BE57" s="89"/>
+      <c r="BF57" s="94"/>
+      <c r="BG57" s="94"/>
     </row>
-    <row r="58" spans="1:58" ht="24.9" customHeight="1">
-      <c r="A58" s="125"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="126"/>
-      <c r="D58" s="126"/>
-      <c r="E58" s="126"/>
-      <c r="F58" s="126"/>
-      <c r="G58" s="126"/>
-      <c r="H58" s="126"/>
-      <c r="I58" s="126"/>
-      <c r="J58" s="126"/>
-      <c r="K58" s="126"/>
-      <c r="L58" s="126"/>
-      <c r="M58" s="126"/>
-      <c r="N58" s="126"/>
-      <c r="O58" s="126"/>
-      <c r="P58" s="126"/>
-      <c r="Q58" s="126"/>
-      <c r="R58" s="126"/>
-      <c r="S58" s="126"/>
-      <c r="T58" s="126"/>
-      <c r="U58" s="126"/>
-      <c r="V58" s="126"/>
-      <c r="W58" s="126"/>
-      <c r="X58" s="126"/>
-      <c r="Y58" s="126"/>
-      <c r="Z58" s="126"/>
-      <c r="AA58" s="126"/>
-      <c r="AB58" s="126"/>
-      <c r="AC58" s="126"/>
-      <c r="AD58" s="126"/>
-      <c r="AE58" s="126"/>
-      <c r="AF58" s="126"/>
-      <c r="AG58" s="126"/>
-      <c r="AH58" s="126"/>
-      <c r="AI58" s="126"/>
-      <c r="AJ58" s="126"/>
-      <c r="AK58" s="126"/>
-      <c r="AL58" s="126"/>
-      <c r="AM58" s="126"/>
-      <c r="AN58" s="126"/>
-      <c r="AO58" s="126"/>
-      <c r="AP58" s="127"/>
-      <c r="AQ58" s="94"/>
-      <c r="AR58" s="95">
-        <v>2</v>
-      </c>
-      <c r="AS58" s="83">
-        <v>25</v>
-      </c>
-      <c r="AT58" s="83">
-        <f t="shared" ref="AT58" si="6">AR58*AS58</f>
-        <v>50</v>
-      </c>
-      <c r="AU58" s="95"/>
-      <c r="AV58" s="94"/>
-      <c r="AW58" s="95"/>
+    <row r="58" spans="1:59" ht="24.9" customHeight="1">
+      <c r="A58" s="130"/>
+      <c r="B58" s="131"/>
+      <c r="C58" s="131"/>
+      <c r="D58" s="131"/>
+      <c r="E58" s="131"/>
+      <c r="F58" s="131"/>
+      <c r="G58" s="131"/>
+      <c r="H58" s="131"/>
+      <c r="I58" s="131"/>
+      <c r="J58" s="131"/>
+      <c r="K58" s="131"/>
+      <c r="L58" s="131"/>
+      <c r="M58" s="131"/>
+      <c r="N58" s="131"/>
+      <c r="O58" s="131"/>
+      <c r="P58" s="131"/>
+      <c r="Q58" s="131"/>
+      <c r="R58" s="131"/>
+      <c r="S58" s="131"/>
+      <c r="T58" s="131"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="131"/>
+      <c r="W58" s="131"/>
+      <c r="X58" s="131"/>
+      <c r="Y58" s="131"/>
+      <c r="Z58" s="131"/>
+      <c r="AA58" s="131"/>
+      <c r="AB58" s="131"/>
+      <c r="AC58" s="131"/>
+      <c r="AD58" s="131"/>
+      <c r="AE58" s="131"/>
+      <c r="AF58" s="131"/>
+      <c r="AG58" s="131"/>
+      <c r="AH58" s="131"/>
+      <c r="AI58" s="131"/>
+      <c r="AJ58" s="131"/>
+      <c r="AK58" s="131"/>
+      <c r="AL58" s="131"/>
+      <c r="AM58" s="131"/>
+      <c r="AN58" s="131"/>
+      <c r="AO58" s="131"/>
+      <c r="AP58" s="132"/>
+      <c r="AQ58" s="154"/>
+      <c r="AR58" s="110"/>
+      <c r="AS58" s="110"/>
+      <c r="AT58" s="110"/>
+      <c r="AU58" s="110"/>
+      <c r="AV58" s="154"/>
+      <c r="AW58" s="110"/>
       <c r="AX58" s="89"/>
       <c r="AY58" s="89"/>
       <c r="AZ58" s="89"/>
-      <c r="BA58" s="96"/>
+      <c r="BA58" s="89"/>
       <c r="BB58" s="95"/>
-      <c r="BC58" s="89"/>
+      <c r="BC58" s="94"/>
       <c r="BD58" s="89"/>
-      <c r="BE58" s="95"/>
-      <c r="BF58" s="95"/>
+      <c r="BE58" s="89"/>
+      <c r="BF58" s="94"/>
+      <c r="BG58" s="94"/>
     </row>
-    <row r="59" spans="1:58" ht="17.100000000000001" customHeight="1"/>
-    <row r="60" spans="1:58" ht="17.100000000000001" customHeight="1"/>
-    <row r="61" spans="1:58" ht="17.100000000000001" customHeight="1"/>
-    <row r="62" spans="1:58" ht="17.100000000000001" customHeight="1"/>
-    <row r="63" spans="1:58" ht="17.100000000000001" customHeight="1"/>
-    <row r="64" spans="1:58" ht="17.100000000000001" customHeight="1"/>
+    <row r="59" spans="1:59" ht="17.100000000000001" customHeight="1"/>
+    <row r="60" spans="1:59" ht="17.100000000000001" customHeight="1"/>
+    <row r="61" spans="1:59" ht="17.100000000000001" customHeight="1"/>
+    <row r="62" spans="1:59" ht="17.100000000000001" customHeight="1"/>
+    <row r="63" spans="1:59" ht="17.100000000000001" customHeight="1"/>
+    <row r="64" spans="1:59" ht="17.100000000000001" customHeight="1"/>
     <row r="65" ht="17.100000000000001" customHeight="1"/>
     <row r="66" ht="17.100000000000001" customHeight="1"/>
     <row r="67" ht="17.100000000000001" customHeight="1"/>
@@ -24257,9 +24325,14 @@
     <row r="149" ht="17.100000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AQ7:AZ7"/>
-    <mergeCell ref="BA7:BD7"/>
-    <mergeCell ref="BE7:BF7"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="AQ7:BA7"/>
+    <mergeCell ref="BB7:BE7"/>
+    <mergeCell ref="BF7:BG7"/>
     <mergeCell ref="AE7:AO7"/>
     <mergeCell ref="A58:AP58"/>
     <mergeCell ref="AP7:AP8"/>
@@ -24269,11 +24342,6 @@
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AA7:AD7"/>
     <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="X9 X50:X57">
@@ -24347,7 +24415,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35433070866141736" right="0.27559055118110237" top="0.59055118110236227" bottom="0.59055118110236227" header="0.43307086614173229" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -24396,34 +24464,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27">
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="M2" s="141" t="s">
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="M2" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
+      <c r="R2" s="152"/>
       <c r="S2" s="22"/>
       <c r="T2" s="22"/>
-      <c r="V2" s="142" t="s">
+      <c r="V2" s="153" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="142"/>
-      <c r="X2" s="142"/>
-      <c r="Y2" s="142"/>
-      <c r="Z2" s="142"/>
+      <c r="W2" s="153"/>
+      <c r="X2" s="153"/>
+      <c r="Y2" s="153"/>
+      <c r="Z2" s="153"/>
     </row>
     <row r="3" spans="2:27" ht="48.6">
       <c r="B3" s="23" t="s">
@@ -25285,12 +25353,12 @@
       <c r="T17" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="V17" s="142" t="s">
+      <c r="V17" s="153" t="s">
         <v>82</v>
       </c>
-      <c r="W17" s="142"/>
-      <c r="X17" s="142"/>
-      <c r="Y17" s="142"/>
+      <c r="W17" s="153"/>
+      <c r="X17" s="153"/>
+      <c r="Y17" s="153"/>
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="26" t="s">
